--- a/reports/thinking_agent/report.xlsx
+++ b/reports/thinking_agent/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="174">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc59-e481-7d80-9c7c-caa502ee8373</t>
+    <t>01a0cce3-3ae4-7503-a0ab-5727ccb269e0</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc59-e48b-73a3-ac12-00713f25857d</t>
+    <t>01a0cce3-3af0-7023-bfe7-9ecff221724c</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -345,10 +345,10 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b39bc6aa975b4c9006ab34a374a4887d2aacd56f4c43fa631", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0o3FpjSECpif6ZFpi17eTW-UbK1G-K7ycRZqAjmDLRqCL7vUOy1EOk22a5ZOzcX73_ESlpZs4GxcuEGAd3CvZiSTpmS9opPay594SvfOKOCUpvGPTIuxagQibMF56VALTZPYCDQ7075tAcYhJXhm2MPhBjEZu3KtCAt4yedQhbth0lLZJuW8N3j0ERpcCL70ia4ZNpEDEAPJnnHysIveq603ioLMNA4MlXZbsLlzZE2UJUy8CWhqB8MeMlCv3i6okx-WZX4UqJ-QsoGf94KXtg2nutkzFTiGhJQaUY_fWlyh0LnnhzVg2JcYHbrIGd-SWM8qeoL1gUb-WzsC1kFVLUqt5KKgvYWyg3sctncIy2ZH0ca64M_u08lFMgMx6kWKegflbZYOraWkAsploAjiWOdue_Ohc1BQsYk3KFbd-4A3D3Ob4NGxjyfEulDr03XIDgNe68i9zd473_vRJrCehnPWRl07VgkwRWL6r01id-fOc1vN4aD5Qxfks-2UDKyG1I1VbVh768H35oQ4PmqCAjkSUTS6AxI1OwgAtuf58iuZsk2MBqbZp4dTu33awK7gW8_cWMaDJGx05OQ_SeDTVJdxB-otYPa_lmEYpV0kE-ZM8fGFWwPGgXTSTNUZbD5RqndqdQMWdOX83fzmFj_DZg9VfV-CMJiyjUzFBL0zkOtpS-NM7F7ZWcEBsXEewgsUMa2YvvaFtCP4lTVAHzjD_goa0io8L0CVlbBTptZtblL4tpaN-J-GyUQ2MmUAckQY0rEaj9V5Srzi76EgPUPL3e4ckQSGl8UQ6vcxfl8LZtWXlkcaLXjm-IQsLLj-0b_c9xhsE3q0-wJwG7mqxBV02tLWgW7-IhtkZestRuRPKDRJJm1ykbQ7V1KHlnnwM2l_p3CTLFK5hKIj9nI5z0H_jdKBzdm4tKLaLHnbAdG8UW3IeP8GA1hy-8CCpjtDeSaO5npzOcHb7wLQbQPtoMeb1dZXzRn4vWQFfkg4d4HYwmeMrEGyEn1bkV-0FYHVh-_cDAjDlfpkxa7AgSm9riwBMY5Syb_DLCCu8y5I04VJc5x8ALjIf9vCwyhLXvC2APSpQgcX2ibgU0SXEFYZy1uaIVyfZqUz-FFwpSNFEHCOf630AxwP8W53AG2BMKYxfbqhrc5wnsnMTdyjPvoHMurCq4mlR479Ay-gwQVyRWkbzPySSQ80IgsqkyUsxCb_FxVkTG0vtJGVmK1Bzf0wIlo7CWlO8RC2C1f1uVOrWBRHB2585odZm3mZBKCjE7XIehRepfmfLUCdl0w0kdzxct6-A3d5A=="}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_AavHUqHUzSDM1ErAsyuwFzX3", "id": "fc_0b39bc6aa975b4c9006ab34a37e76887d28c4987e65780d2ff", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_VKmgGA17R8561XCUbWYbpjNT", "id": "fc_0b39bc6aa975b4c9006ab34a37e78087d2a9db0107e195b8f7", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_oL74jGxhGwB65wCfUp971Tke", "id": "fc_0b39bc6aa975b4c9006ab34a37e78c87d2a3db7e9d5b42d85c", "index": 3}]
-{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_AavHUqHUzSDM1ErAsyuwFzX3", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "database"}, "id": "call_VKmgGA17R8561XCUbWYbpjNT", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_oL74jGxhGwB65wCfUp971Tke", "type": "tool_call"}</t>
+    <t>[{"id": "rs_087fe8fbe0369434006ab36d6021c087d28b8d40d79a9347bb", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21hyxqpZcQG_HQjOdXHAYprN7-gn12RjKOj6CkDF1WjbYdl8-YkBWPJnBwcPA5GNdT9KW496EiI4fiulNaDvjwwkJDmZxO3cFg2tgeefpqM4X52unRjo09eL-V-8YOgvHO6iddrJQwmYmoKiSrUQ_Qtak0k458fyIPToL9IpBMaEf7Nn99W6NDzifjf4iwFmdf6_1mIVvoAz_I7h0qGE1WA_8Z8obUtoYq5Wx0KgpCCOG79lpoHHX18j-f1Er24TZMIVCVIhSdOsMydGzYM3ybB-I5sw065zH1NnjGB56CDaHMl8c1P6DaZgwHZz9BTslCoINyPCpm0lsUIjiiKYIKbBMrF3vcQHIXisEPVU5snAD1HTL2QhYlgvItLqDxNQyKftWJq-RXOjCvlK3hL3L6EUbm0ithgKb2gDnYzZzhMDttIWewfKKqrNQEOiI48eRjB0dmQvRflVl32JNDmag1Tyoj_y6QQ5OCuw7Pwh73CZdmOGqDiUC09RathS50RU8CRSYn0i_c6ypVGCV-kWq9Atljq1_58UBWaenvmodb7-CYWFYzBAODfkJ3zDArYWxjv_Wu6JiMrP_vVKO6r6FptPcLuMjZowwnt54HuFFPXb12Nq9CAwWQIJ4XMT3cpBASb8N7tcxeqtsc3iemSVerFb11GbRYi8VFLjMlXs80XS7exizfFWSSUOjIs0gPSuWspCBPDDwEJLQc07Z0RDHZZLkw8c2B9wC9asOYui_HkG39kx9Ym_uv63T5KCIoYlZFiSIF2lkduuDeqD7HePa5qrcc0KThlihYxeBciCx27pYmylUd18auXbuMjTvQZnkKDxYivUiADUKSOn-DrlcYsbL5YADD3JicXZLtNN_i-MPbp2HDkFz6NQGKFRKKe95RdpA-xzA-0kByKWn8CuPgtrvzdI9u1MZ_mUlBwBlV61f922bmQZpWYQl-vx_G2CZJCynDj0MSeO5q8TtOQFSV7W_v-_JCCt4s5iqA7e6YSvcK-_I3LM9XY0u4x-pvQkvj9njMEhspS01A--1z4PrAC-YHorOrUwedbo-YOeP1aiiWpVoJqBhhODwP-OzNr28VyhnZdhE5eJMcMfuC98HZEjqHjs526InBfZ_KJPALOR7tEcko247qVpCT4LlxtwpTawsEtmtz8Tw9R_f4SV5n7IEmooup2_zjHWjojI4mC9Vd5r_NEaLL-wolikYiD157hSvNAUUBWKe9hLFs_ekuF94t4YF1j77_zYbg7Cd2c6Y81Rhvod6ZyFntD_MkOdPnX5LJNr5zY4G-SdStTv8UYO0d2v1wvzB16Bnd9S8cgXPose_7Werto78oaNNNiDDq3O_gOEGHbWuFVevcEUsWDFSVENPDwRs7nPm80fWGc8bc6umwtPzvbJPpb_X8fp2aEj9O6CaxcNqLQmOUFGxJGGzbxKpQ4nGwBpncEPiXDs-5l_3zRTWLvITFA9PP8TslW90EyJLvkaFLzNXcfO8jei8Ghw4TwCuZPEk9XY_q9uXvI32GhqCtENqlU34xxqHgi"}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_aVaOvXFe3x2okTXOSttMNEhB", "id": "fc_087fe8fbe0369434006ab36d61f17887d2ba98a391b40b6112", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_O2BYZEY6v8ipZUlcnWiOVtDw", "id": "fc_087fe8fbe0369434006ab36d61f19087d29539413fdfbb3774", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_wKjW8pSc1KbpgIpvSi66llf4", "id": "fc_087fe8fbe0369434006ab36d61f19c87d28f99f8d4567bd0f3", "index": 3}]
+{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_aVaOvXFe3x2okTXOSttMNEhB", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "database"}, "id": "call_O2BYZEY6v8ipZUlcnWiOVtDw", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_wKjW8pSc1KbpgIpvSi66llf4", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -360,7 +360,7 @@
     <t>Tool · inspect_service</t>
   </si>
   <si>
-    <t>01a0cc59-eb2e-7df1-877f-162292309caa</t>
+    <t>01a0cce3-479a-7693-900f-e4a69b9f4b5a</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -375,7 +375,7 @@
     <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
   </si>
   <si>
-    <t>01a0cc59-eb2f-77a1-b0a1-8ee6bf5f06c6</t>
+    <t>01a0cce3-479a-7693-900f-e4b1f6eabbb5</t>
   </si>
   <si>
     <t>{'section': 'database'}</t>
@@ -384,7 +384,7 @@
     <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
   </si>
   <si>
-    <t>01a0cc59-eb30-7f40-a814-6ed3da533fdb</t>
+    <t>01a0cce3-479a-7693-900f-e4cb7e4f4396</t>
   </si>
   <si>
     <t>{'section': 'constraints'}</t>
@@ -396,7 +396,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc59-eb37-7c12-9bb6-fde922bcb9bd</t>
+    <t>01a0cce3-47a0-7503-98b1-efea8452af33</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -410,16 +410,16 @@
 Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b39bc6aa975b4c9006ab34a38ef3c87d287320f9ef811247c", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0o5BmjYKaYZNqQOQeNFzkTpnGS-tnPjjMnX9Z4aahx049PvUSr3-PSKzCNXYgTSsy8woc-NLNYl7T6sn4OkNwylisqF7-O95MQLPvWke3GA-qowLZCMc7A05wWBT4rEcU5wX2_txiTl16gL757weKhVV6iwQWG5Bi1hQ-_f6KKqVLwsv3q8ndHAz4x9jH9ghLy28ZcNaOWZfFWSKjrtqu11va4uuZwqumUFrVhKG9xm-KUEnwzc8qLuCT44QIdM0NmDn6XdZr3poI2rSgja1NJZOsWgEgyApnJb9cRkCdOaGxhGavfwnhrjIR05eRdy-qTQSIiOkvPIX1zj5Z2zWAWGcBju688L0xXvMnoBIH-NSpI8eERBQsPY-2HC4-HTYdgBHW6QX17HCk1ZHMqlbiwnCAd9xGYfkEt5aGNRV4hYei649P8CBWCJdGFTjRKgnudToyPev7Xhd9us3eF1MqZFLPO0StHHpOP6Y8PGvqHxhrlJi1p2GaBlvMvJ9COKU3cjTceWBl0WcHPVYVKNDogGnQZq7FsY0LqeHgvDyuW0XBwJiSMF0wInZEozR8ncpvmV0CQZZxivK7C7ChFOKextC2XQPaYgRIrhL1Lhlt6BRERMlP_bbQmTkcx05EOxEbqoEQ_7fz0gJW1koYeO2fFq_WDtr1jv5a8FK0xLotQJ2gtUnnfzdl_7nrikEkWyvsjW5Fz1DFRdS15U33YfF5hAr3mOQ6oBNFL8r0ruRMo-dNVOeHzrzT_F2Pt3Cn-t4xx7uMkyhUdymqgvY7K1418LplA11lvtPSG-qUflCyMsMAQvGfwdT_6cLrfefoGi-YoMhp36zDapJ_77sdzRaWu-DDMnnq4e1REZj5AEUJ2wE_lt87gUIEH3uwzPExXyy1WxbjiqQIqap6x0H_F2VAfqI0f-AqvrruQFXhCSAWTWaBzkqyOmx5SKb9F4Em-KJpx009QT4xUxNxnDuybn9B8G2FbWvqhlz4IFcIhbUaeoGhFcJD1IIuY6MDv8qmtGCCQCxzNqnGB6WCAlLq2H1CG98USQ9jn8QHq6-m8XNhDiejXlZmwOyLOsKnRYM_wsE1NJp3J-Lbpbd5yo1UFbjnTtAm_6I9X6RGssZlAHLzNaqWrX_p5ptvSgiWxudLYpaHJOuDf0arA8Yzkvvrf7xzMiXBCDVZQZHIbv2FT-zh_AFo_8UVXQnTjQKQt43T0_nFFSalxkQyhFQxGi23OdOYxjnc99WSt0_ZughpENdb_AlgoumH7qJ5t98lmzpB2_iT7oHdR7_wQzTqNfJOgd609lts9Th_CffFoIsbpdxUCnmRymm5oGqt6PeN26t7qqHpiiQE8RZgHJfRKeEu4jlrB1KhewtHY4k2qc5k0l6JTY1UNDeNN-oJUlVpemK5o-LMeE"}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_XbfhkVD7WPJDfAuzSJ2jEs8M", "id": "fc_0b39bc6aa975b4c9006ab34a39c15487d2a7a94b925d6c856a", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_KCJmngQO2TlJ4c8w1cx8jV9O", "id": "fc_0b39bc6aa975b4c9006ab34a39c16487d2a5ea8b5e6d23aba9", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_3Kl3UGEphADmYbsgmHChXuLL", "id": "fc_0b39bc6aa975b4c9006ab34a39c17087d28666561372a23bf4", "index": 3}]
-{"name": "test_plan", "args": {"check": "load"}, "id": "call_XbfhkVD7WPJDfAuzSJ2jEs8M", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_KCJmngQO2TlJ4c8w1cx8jV9O", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_3Kl3UGEphADmYbsgmHChXuLL", "type": "tool_call"}</t>
+    <t>[{"id": "rs_087fe8fbe0369434006ab36d631a4087d28d50aeb78b2f6371", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21kJIVlJHpeTwk4ZJDpJV7OZ_ffnsIoiCREsrK2drmHuk_E4YnGujhm9At-X-nI_ZbBdVZYadkx0jweBH0_vekc9BQHkeLyFa7n_9rHgbET5_1uHRt65DxKRknQQD-q6q35Qg6mmRV-SjgIUv0UqYRhCcMKAgOkK5ohvu1gcsCTfOMS7Tv1Z8XUwRH6K_yMhBUzpMD0tf4o-JPizHrwTUeff1F82NSliDathjcS4OY9GnlBp5TrVBUud5TC4E_WAmCJufoW3PKv2gyzAfCWLAbaI28UB22ENFDWUyMIN4j6qSm0Ou6-HlNu9ZyNM6JpgOguqVJg-EPbw1xzAbuxtB2XF3lNGMhhsS6I3FTqtKsHSWGEdsaZx5gMck1w3GPCmoCSvSKIf9n3Ke-reL5KiH1zCrw2Ia8sOmIIxr9VyeH6I0SuTeYw2Y0AHBdE_KOALtNg9S4_91MSII-N0pdeKd-bkipmVR8B6Y-pO5qSqw-AVP80SEF6kpaiSXRnFXqKZikFpvydBmf8vCjCNwW5FprtQrf0stcbXE2xCodL0MceWwc0I2EPHEztEVjL8ao_EoAyRmUyfNaPA9lwF0Ka229y8UitHDGMrnMDjAe5vZX7bvzCgk7v0INFLaqCLcuJFDLTGsjLGzRcc3g9yilQrI-So459WZLq2ojlqS8dExpM_USMeYc-E2w2GpQMh3B6PWVWFLn1dDP1nW6xQNW7K28nppdmP6wCB2yAez-NRPRm_uXGsyJURMZlMxCU--6qXRiLGtsWAuf_bpM8z9VN-nmuUsgcf4GMu_nemJMF8zERjuQ2pKjZMMTeUz_bceiXegkKbO1rj9mgEHN_TmkI3XZuyIdAhkpHrjWGy12kGZKpOb6XSQyMOwmXX1pKH-zrcqih6LpVaBrh9YcCPp8gxH0eR2h4mKJL5GIjAklhXET2V879fcpp-5qxZPH7N2ya6LxmHTk88kBQZKlFyCGKO6TxYsOFkkBQjN4rcZnUm1JCNYDigvAAVrTb3-yRA0KLi8yq6fe_1PqN276nMALpfcScBOQsvi5DVA7mOjdii5gLACqtwQZtVclaf1ngTG5e-qH-vyUUh6uoDMflDGS8xY_p0oL0M2KUaUKYUoQWSjDVsZRKaxLeE02lkgK0G7WTyXxVhrRATAwaRVeghQfM6ZwIFhNVGRtSackEiwYZov-Ygk8-NBLblvXX184oKZQCPjBunWroC92ZHEsbAeDiAcs0kltmGeJER8qXU4yA-27RKvSFhTgH4mZ4nGCkH8fvuV62X_oR1pBtc0XN2KVdlOHN_S79-eXVD4pEnGNeNeOo--y0x89w7W0avca0-hlAManlV9EjSuX7h0UB1ZgIK3qRCw=="}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_M2OPB63aVbgX7r0hBUo65DWL", "id": "fc_087fe8fbe0369434006ab36d646a8487d2a5d5b5b99a3d0989", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_BU4MeNXeL7IyMj29Oylb2289", "id": "fc_087fe8fbe0369434006ab36d646a9c87d29e58ce0ca9299df7", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_5wm6GO9yXwMhVZAWQV8uF8qO", "id": "fc_087fe8fbe0369434006ab36d646aa487d2a9bfb5f459a3ebbe", "index": 3}]
+{"name": "test_plan", "args": {"check": "load"}, "id": "call_M2OPB63aVbgX7r0hBUo65DWL", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_BU4MeNXeL7IyMj29Oylb2289", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_5wm6GO9yXwMhVZAWQV8uF8qO", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · test_plan</t>
   </si>
   <si>
-    <t>01a0cc59-f2d9-75d1-af63-e2efaf6f74e6</t>
+    <t>01a0cce3-5150-7812-b362-4d2a602aacbc</t>
   </si>
   <si>
     <t>{'check': 'load'}</t>
@@ -428,7 +428,7 @@
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.</t>
   </si>
   <si>
-    <t>01a0cc59-f2da-7ce0-96d4-bc2a5d0a5567</t>
+    <t>01a0cce3-5151-7f42-8455-57981b16d65f</t>
   </si>
   <si>
     <t>{'check': 'freshness'}</t>
@@ -437,7 +437,7 @@
     <t>PASS: account changes invalidate cached values; maximum fallback age is 30s.</t>
   </si>
   <si>
-    <t>01a0cc59-f2db-75c2-9079-520356abc7fd</t>
+    <t>01a0cce3-5151-7f42-8455-57a6f5433517</t>
   </si>
   <si>
     <t>{'check': 'rollback'}</t>
@@ -449,7 +449,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cc59-f2e6-7dc0-a80f-692cbfb76fd8</t>
+    <t>01a0cce3-5156-7441-abb7-b632fcf0baf1</t>
   </si>
   <si>
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.
@@ -457,7 +457,7 @@
 PASS: feature flag restores original lookup path; no schema migration required.</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "## Findings\n\n- **Traffic:** Peak load is 240 requests/s, with p95 latency at 1.8s. Latency increases during database bursts despite 12 workers.\n- **Database:** The connection pool is capped at 12. Queries have an 80ms median but a 900ms p95. Requests perform duplicate account lookups, increasing contention.\n- **Constraints:** Reduce p95 below 500ms, add no database nodes, and keep cache lifetime at or below 60 seconds.\n\n## Proposed latency plan\n\n1. **Deduplicate account lookups per request** so repeated accesses share one in-flight result.\n2. **Add a short-lived account cache** with a 30-second TTL.\n3. **Invalidate cached account data on account changes** to preserve freshness.\n4. **Roll out behind a feature flag** and monitor p95 latency, pool occupancy, cache hit rate, and error rate.\n5. **Roll back by disabling the flag** if latency, correctness, or error metrics regress.\n\n## Validation\n\nThe plan check passed:\n\n- At **240 requests/s**, deduplicated lookups plus a **30-second cache** achieved **410ms p95 latency**, below the 500ms target.\n- Database pool occupancy was **65%**, leaving capacity below the pool limit of 12.\n- Account changes invalidate cached values, and maximum fallback age is **30 seconds**.\n- The feature flag restores the original lookup path, with **no schema migration required**.\n\nThis plan meets the latency, database-capacity, freshness, and rollback constraints.", "phase": "final_answer", "index": 0, "id": "msg_0b39bc6aa975b4c9006ab34a3acbb887d2ac7c31225163ccc7"}]</t>
+    <t>[{"id": "rs_087fe8fbe0369434006ab36d661aa887d2b04f749228fc66d4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21mkanf4m_IV5w8_10TUN5GejPfkAkErHTzrFImKR7h5YP_mb2F9Gb_l-VxY5oO7YvU6bb--DoxSa5_bCJWunkMmd5KqcNiTgn6sWYGjdw8NlpLrXLdMgKgdN8vRNYDWXxyUCDZGAGkiWQXo0uUs2ws-rgXiOQmpZqsrgMi_TPYXdKgyIvosbGJjbM3omyyyhzX1U1c7ATp7LtIGatfunQ06McUDXplzaioOE5bc8-_IgzjCZLO5X3XCaalJnq1zzfWsPJcYpornU9-JViQxB_JOl_L0rwdHEEBv2hra_8-V9lDQlgzhFxCrRO9x3z8kXkynS837hXKQnitTv8V0909HHIFh3qSGzIqdqDKq7ryOCPz2C2p3Mj9VWrsS8XW6oepXhigiGAZLFc4AUyB6lQHeeyTN5cToJ3k_oTt_jEzUODJuWDmot7llR0f7ps6OjVKzJOqof4NKDiPJoKTuRTZJOVaG7Q4vtjgKB7Rz9Vi_DYkGm2q-kyRPpZcFgSuV4djTDa_J--RGymXc9wfCRKTfx-S29o9-jem_9JlGtYDFJdVoSJ6BIwO1Ad4vVd9020QEi5K0_bu8OiwfrYUYD_nyifZnwogWEhoz5N_R6wFDsuUh8Qkhu_rJtSSPoHjb_1_7Vt6uF0bxYBoMvB91uu3jA3DDvU1AApz-md9sh8iSRGwKuqO7BhysbVJVQix8poxIsz9cbLQlcwMh_B8QxBvajlR66oRj28xekroHxWvE3_QFyUlXN9CsK2MhoqAc0gMotqrvXyAOzaL7PS-27-OriDV9cxODp7vRPaShjSm-4tu3UmaURt__-a9-9JHDuT0Xngt7RRb82m2PTKL-4F6D7SaDmNr8pvdgvj8zfSt_YYe6E1SXEXPQocB0V6BP9roHraFeHD4d41c8zY29iSjvuPmBgZzwhZyU0Z8Em_A6-2t6kfx9E8IFLMHRujQxn3PazL-Vv3fqrEmEgqIAnGc7krHz0kxqn_NSL2sJyI6YgZ5sCN-Y8Hi-RsxOnjiLqhb48y57bec8JFNz36olNPePQf_EB_v3YbVYBKwK08Z9c_6pj98ujxh6n09hthvGcLh6usghLZoYwGRVfwoMLkJScQC_SThLXAWdMSjinYUaCZ7kTZon4NGlEqsv1uk4o7wHvTjNc7chFbh8gP14Mr_jQL2BQmpWbdfvnwK-SFDA0gIZfpbpvUagtRtP9rJY4jm7_-UndsjV9E3LuihRkzYjAhag-ARcdEhE2JXBtlZOJIJMUjEq10VA6YkuPkpuLwFYBukWoJ1yZg9bwteR6tJ_fIr_oPWhvXenvzc9KH0fjg="}, {"type": "text", "text": "## Findings\n\n- **Traffic:** Peak load is **240 requests/s** with current **p95 latency of 1.8 s**. Latency increases during database bursts.\n- **Database:** The connection pool is limited to **12**. Query median latency is **80 ms**, but p95 reaches **900 ms**. Requests perform duplicate account lookups.\n- **Constraints:**\n  - Target p95: **under 500 ms**\n  - No additional database nodes\n  - Cache lifetime: **no more than 60 s**\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so repeated access to the same account uses one in-flight/result lookup.\n2. Add a short-lived account cache with a **30-second TTL**.\n3. **Invalidate cached account values when account data changes**.\n4. Roll out behind a **feature flag**, retaining the original lookup path for rollback.\n5. Monitor p95 latency, database pool occupancy, cache hit rate, and account-data freshness.\n\nThis avoids adding database capacity while reducing duplicate queries and database-burst contention.\n\n## Validation\n\n- **Load check: PASS**\n  - At **240 requests/s**, deduplicated lookups plus the 30-second cache achieved **410 ms p95**.\n  - Connection-pool occupancy was **65%**, below the pool limit of 12.\n\n- **Freshness check: PASS**\n  - Account changes invalidate cached values.\n  - Maximum fallback age is **30 seconds**, within the 60-second constraint.\n\n- **Rollback check: PASS**\n  - The feature flag restores the original lookup path.\n  - No schema migration is required.\n\nThe plan meets the latency target and all stated constraints.", "phase": "final_answer", "index": 1, "id": "msg_087fe8fbe0369434006ab36d669c8087d2aaa9293b762ff873"}]</t>
   </si>
   <si>
     <t>investigation_agent</t>
@@ -478,7 +478,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cc59-e484-7d41-8325-533933342666</t>
+    <t>01a0cce3-3ae7-75a0-a9ad-6ff075ea5e6c</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -490,7 +490,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc59-e485-7153-bdec-68c4f5aed784</t>
+    <t>01a0cce3-3ae9-7c22-9033-cd94353ec929</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -511,7 +511,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc59-eb2c-7872-9455-6fc683c521a2</t>
+    <t>01a0cce3-4798-7120-9457-da096458d7aa</t>
   </si>
   <si>
     <t xml:space="preserve">        inspect_service</t>
@@ -523,16 +523,16 @@
     <t>Read fictional service evidence; no live service is inspected.</t>
   </si>
   <si>
-    <t>01a0cc59-eb2c-7872-9455-6fdb1e34cdcd</t>
-  </si>
-  <si>
-    <t>01a0cc59-eb2c-7872-9455-6fe26b1d412f</t>
-  </si>
-  <si>
-    <t>01a0cc59-eb35-7812-b954-589b69d576e8</t>
-  </si>
-  <si>
-    <t>01a0cc59-f2d7-71b1-af92-a3553aa6f716</t>
+    <t>01a0cce3-4798-7120-9457-da1c6e8013fd</t>
+  </si>
+  <si>
+    <t>01a0cce3-4798-7120-9457-da2a91e54816</t>
+  </si>
+  <si>
+    <t>01a0cce3-479e-7492-9e97-4dd3f7af5644</t>
+  </si>
+  <si>
+    <t>01a0cce3-514f-7322-bfd1-a2c0371ca2ca</t>
   </si>
   <si>
     <t xml:space="preserve">        test_plan</t>
@@ -541,13 +541,13 @@
     <t>Return a fixed fictional plan-check result; no real test is executed.</t>
   </si>
   <si>
-    <t>01a0cc59-f2d7-71b1-af92-a36d57b0dd68</t>
-  </si>
-  <si>
-    <t>01a0cc59-f2d7-71b1-af92-a3752f4a6ffb</t>
-  </si>
-  <si>
-    <t>01a0cc59-f2e2-77d0-a96f-6bbfb2a05385</t>
+    <t>01a0cce3-514f-7322-bfd1-a2d02cc51e2e</t>
+  </si>
+  <si>
+    <t>01a0cce3-514f-7322-bfd1-a2e1d074a0ec</t>
+  </si>
+  <si>
+    <t>01a0cce3-5154-7001-8956-e317466c003b</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1014,20 +1014,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011492166195</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
+        <v>0.0012350752749</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00131735</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
+        <v>0.00141577</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>115.0</v>
+        <v>124.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>132.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1038,20 +1038,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011492166195</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
+        <v>0.0012350752749</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00131735</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
+        <v>0.00141577</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>115.0</v>
+        <v>124.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>132.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1195,7 +1195,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1209,23 +1209,23 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.64e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1306,19 +1306,19 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.0005483281635</v>
+        <v>0.0005755461075</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.00062855</v>
+        <v>0.00065975</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>111</v>
@@ -1443,7 +1443,7 @@
         <v>94</v>
       </c>
       <c r="D27" s="4">
-        <v>2289</v>
+        <v>2315</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>95</v>
@@ -1537,19 +1537,19 @@
         <v>103</v>
       </c>
       <c r="D31" s="5">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E31" s="2">
         <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>4.64537025e-05</v>
       </c>
       <c r="F31" s="2">
         <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!D17),D31*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.675e-05</v>
+        <v>5.325e-05</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1578,7 +1578,7 @@
         <v>105</v>
       </c>
       <c r="D33" s="4">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1">
@@ -1592,19 +1592,19 @@
         <v>106</v>
       </c>
       <c r="D34" s="5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2">
         <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.140532e-05</v>
       </c>
       <c r="F34" s="2">
         <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!F17),D34*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>4.08e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="G34" s="5">
         <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H34" s="5">
         <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1689,11 +1689,11 @@
       </c>
       <c r="E39" s="2">
         <f>IF(COUNT('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35)=5,SUM('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35),"Unknown")</f>
-        <v>0.0001815663681</v>
+        <v>0.0001830493971</v>
       </c>
       <c r="F39" s="2">
         <f>IF(COUNT('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35)=5,SUM('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35),"Unknown")</f>
-        <v>0.00020813</v>
+        <v>0.00020983</v>
       </c>
       <c r="G39" s="5">
         <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1826,7 +1826,7 @@
         <v>94</v>
       </c>
       <c r="D49" s="4">
-        <v>2476</v>
+        <v>2498</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>95</v>
@@ -1846,15 +1846,15 @@
         <v>126</v>
       </c>
       <c r="D50" s="5">
-        <v>2286</v>
+        <v>2312</v>
       </c>
       <c r="E50" s="2">
         <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.98847564e-05</v>
+        <v>4.03383888e-05</v>
       </c>
       <c r="F50" s="2">
         <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.572e-05</v>
+        <v>4.624e-05</v>
       </c>
       <c r="G50" s="5">
         <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1920,15 +1920,15 @@
         <v>103</v>
       </c>
       <c r="D53" s="5">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E53" s="2">
         <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>3.99109275e-05</v>
       </c>
       <c r="F53" s="2">
         <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.675e-05</v>
+        <v>4.575e-05</v>
       </c>
       <c r="G53" s="5">
         <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1961,7 +1961,7 @@
         <v>105</v>
       </c>
       <c r="D55" s="4">
-        <v>323</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="24" customHeight="1">
@@ -1972,29 +1972,29 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D56" s="5">
-        <v>323</v>
+        <v>22</v>
       </c>
       <c r="E56" s="2">
         <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000338130612</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!E17),D56*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0003876</v>
+        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!F17),D56*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>2.64e-05</v>
       </c>
       <c r="G56" s="5">
         <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>34.0</v>
+        <v>2.0</v>
       </c>
       <c r="H56" s="5">
         <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="242" customHeight="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -2002,13 +2002,29 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D57" s="5">
+        <v>356</v>
+      </c>
+      <c r="E57" s="2">
+        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000372676464</v>
+      </c>
+      <c r="F57" s="2">
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0004272</v>
+      </c>
+      <c r="G57" s="5">
+        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>37.0</v>
+      </c>
+      <c r="H57" s="5">
+        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>43.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="409" customHeight="1">
       <c r="A58" t="s">
         <v>140</v>
       </c>
@@ -2016,7 +2032,10 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="24" customHeight="1">
@@ -2027,41 +2046,52 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="24" customHeight="1">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A60" s="4" t="s">
+    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A61" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4" t="s">
+      <c r="B61" s="4">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E60" s="2">
-        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56)=4,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56),"Unknown")</f>
-        <v>0.0004193220879</v>
-      </c>
-      <c r="F60" s="2">
-        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56)=4,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56),"Unknown")</f>
-        <v>0.00048067</v>
-      </c>
-      <c r="G60" s="5">
-        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
-      </c>
-      <c r="H60" s="5">
-        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E61" s="2">
+        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56,'Turns'!E57)=5,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56,'Turns'!E57),"Unknown")</f>
+        <v>0.0004764797703</v>
+      </c>
+      <c r="F61" s="2">
+        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56,'Turns'!F57)=5,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56,'Turns'!F57),"Unknown")</f>
+        <v>0.00054619</v>
+      </c>
+      <c r="G61" s="5">
+        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
         <v>48.0</v>
       </c>
-      <c r="K60" s="4" t="s">
+      <c r="H61" s="5">
+        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>55.0</v>
+      </c>
+      <c r="K61" s="4" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE60">
+  <conditionalFormatting sqref="A2:AE61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2216,70 +2246,70 @@
       </c>
       <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D28,'Turns'!D50)=2,SUM('Turns'!D28,'Turns'!D50),"Unknown")</f>
-        <v>4385.0</v>
+        <v>4411.0</v>
       </c>
       <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E28,'Turns'!E50)=2,SUM('Turns'!E28,'Turns'!E50),"Unknown")</f>
-        <v>7.6506849e-05</v>
+        <v>7.69604814e-05</v>
       </c>
       <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F28,'Turns'!F50)=2,SUM('Turns'!F28,'Turns'!F50),"Unknown")</f>
-        <v>8.77e-05</v>
+        <v>8.822e-05</v>
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D9,'Turns'!D31,'Turns'!D53)=3,SUM('Turns'!D9,'Turns'!D31,'Turns'!D53),"Unknown")</f>
-        <v>2473.0</v>
+        <v>2495.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E9,'Turns'!E31,'Turns'!E53)=3,SUM('Turns'!E9,'Turns'!E31,'Turns'!E53),"Unknown")</f>
-        <v>0.0005393427525</v>
+        <v>0.0005441407875</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F9,'Turns'!F31,'Turns'!F53)=3,SUM('Turns'!F9,'Turns'!F31,'Turns'!F53),"Unknown")</f>
-        <v>0.00061825</v>
+        <v>0.00062375</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D56)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D56),"Unknown")</f>
-        <v>452.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D57)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D57),"Unknown")</f>
+        <v>485.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E56)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E56),"Unknown")</f>
-        <v>0.000473173488</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E57)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E57),"Unknown")</f>
+        <v>0.00050771934</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F56)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F56),"Unknown")</f>
-        <v>0.0005424</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F57)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F57),"Unknown")</f>
+        <v>0.000582</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D34)=2,SUM('Turns'!D12,'Turns'!D34),"Unknown")</f>
-        <v>56.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D34,'Turns'!D56)=3,SUM('Turns'!D12,'Turns'!D34,'Turns'!D56),"Unknown")</f>
+        <v>100.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E34)=2,SUM('Turns'!E12,'Turns'!E34),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E34,'Turns'!E56)=3,SUM('Turns'!E12,'Turns'!E34,'Turns'!E56),"Unknown")</f>
+        <v>0.0001046844</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F34)=2,SUM('Turns'!F12,'Turns'!F34),"Unknown")</f>
-        <v>6.72e-05</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F34,'Turns'!F56)=3,SUM('Turns'!F12,'Turns'!F34,'Turns'!F56),"Unknown")</f>
+        <v>0.00012</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011492166195</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
+        <v>0.0012350752749</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00131735</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
+        <v>0.00141577</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>115.0</v>
+        <v>124.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>132.0</v>
+        <v>142.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>7351.705</v>
+        <v>12621.976</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>147</v>
@@ -2311,7 +2341,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.5610000000000001</v>
+        <v>0.517</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>151</v>
@@ -2389,34 +2419,34 @@
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>22.0</v>
+        <v>48.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005483281635</v>
+        <v>0.0005755461075</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062855</v>
+        <v>0.00065975</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1700.229</v>
+        <v>3245.623</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>147</v>
@@ -2497,37 +2527,37 @@
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>22.0</v>
+        <v>48.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005483281635</v>
+        <v>0.0005755461075</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062855</v>
+        <v>0.00065975</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1692.764</v>
+        <v>3238.117</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>158</v>
@@ -2559,7 +2589,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>7.721</v>
+        <v>4.438</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>151</v>
@@ -2591,7 +2621,7 @@
         <v>161</v>
       </c>
       <c r="AD7" s="1">
-        <v>2.647</v>
+        <v>0.977</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>151</v>
@@ -2623,7 +2653,7 @@
         <v>49</v>
       </c>
       <c r="AD8" s="1">
-        <v>7.324</v>
+        <v>4.56</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>151</v>
@@ -2655,7 +2685,7 @@
         <v>165</v>
       </c>
       <c r="AD9" s="1">
-        <v>2.85</v>
+        <v>1.112</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>151</v>
@@ -2687,7 +2717,7 @@
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>7.176</v>
+        <v>4.745</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>151</v>
@@ -2719,7 +2749,7 @@
         <v>166</v>
       </c>
       <c r="AD11" s="1">
-        <v>2.242</v>
+        <v>1.332</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>151</v>
@@ -2776,15 +2806,15 @@
       </c>
       <c r="P12" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>187.0</v>
+        <v>213.0</v>
       </c>
       <c r="Q12" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>4.64537025e-05</v>
       </c>
       <c r="R12" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>5.325e-05</v>
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -2800,23 +2830,23 @@
       </c>
       <c r="V12" s="2">
         <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.140532e-05</v>
       </c>
       <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0001815663681</v>
+        <v>0.0001830493971</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00020813</v>
+        <v>0.00020983</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2827,7 +2857,7 @@
         <v>21.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1952.003</v>
+        <v>2480.394</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>147</v>
@@ -2850,7 +2880,7 @@
         <v>111</v>
       </c>
       <c r="F13" s="1">
-        <v>2289</v>
+        <v>2315</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>157</v>
@@ -2887,15 +2917,15 @@
       </c>
       <c r="P13" s="2">
         <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>187.0</v>
+        <v>213.0</v>
       </c>
       <c r="Q13" s="2">
         <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>4.64537025e-05</v>
       </c>
       <c r="R13" s="2">
         <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>5.325e-05</v>
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -2911,23 +2941,23 @@
       </c>
       <c r="V13" s="2">
         <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.140532e-05</v>
       </c>
       <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>3.6e-05</v>
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0001815663681</v>
+        <v>0.0001830493971</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00020813</v>
+        <v>0.00020983</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2941,7 +2971,7 @@
         <v>124</v>
       </c>
       <c r="AD13" s="1">
-        <v>1947.127</v>
+        <v>2476.851</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>158</v>
@@ -2973,7 +3003,7 @@
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>8.000999999999999</v>
+        <v>3.626</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>151</v>
@@ -3005,7 +3035,7 @@
         <v>168</v>
       </c>
       <c r="AD15" s="1">
-        <v>2.777</v>
+        <v>1.142</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>151</v>
@@ -3037,7 +3067,7 @@
         <v>49</v>
       </c>
       <c r="AD16" s="1">
-        <v>8.769</v>
+        <v>4.027</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>151</v>
@@ -3069,7 +3099,7 @@
         <v>171</v>
       </c>
       <c r="AD17" s="1">
-        <v>2.677</v>
+        <v>1.059</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>151</v>
@@ -3101,7 +3131,7 @@
         <v>49</v>
       </c>
       <c r="AD18" s="1">
-        <v>9.285</v>
+        <v>3.819</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>151</v>
@@ -3133,7 +3163,7 @@
         <v>172</v>
       </c>
       <c r="AD19" s="1">
-        <v>2.539</v>
+        <v>1.223</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>151</v>
@@ -3178,67 +3208,70 @@
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2286.0</v>
+        <v>2312.0</v>
       </c>
       <c r="N20" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>3.98847564e-05</v>
+        <v>4.03383888e-05</v>
       </c>
       <c r="O20" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.572e-05</v>
+        <v>4.624e-05</v>
       </c>
       <c r="P20" s="2">
         <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>187.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q20" s="2">
         <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>3.99109275e-05</v>
       </c>
       <c r="R20" s="2">
         <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>4.575e-05</v>
       </c>
       <c r="S20" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>356.0</v>
+      </c>
+      <c r="T20" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>0.000372676464</v>
+      </c>
+      <c r="U20" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>0.0004272</v>
+      </c>
+      <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>323.0</v>
-      </c>
-      <c r="T20" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>0.000338130612</v>
-      </c>
-      <c r="U20" s="2">
+        <v>2.3030568e-05</v>
+      </c>
+      <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>0.0003876</v>
-      </c>
-      <c r="V20" s="2">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2">
-        <v>0</v>
-      </c>
-      <c r="X20" s="2">
-        <v>0</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0004193220879</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>0.0004764797703</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00048067</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>0.00054619</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>55.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>3669.734</v>
+        <v>6878.567</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>147</v>
@@ -3261,7 +3294,7 @@
         <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>2476</v>
+        <v>2498</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>157</v>
@@ -3286,70 +3319,73 @@
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2286.0</v>
+        <v>2312.0</v>
       </c>
       <c r="N21" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>3.98847564e-05</v>
+        <v>4.03383888e-05</v>
       </c>
       <c r="O21" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.572e-05</v>
+        <v>4.624e-05</v>
       </c>
       <c r="P21" s="2">
         <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>187.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q21" s="2">
         <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>4.07832975e-05</v>
+        <v>3.99109275e-05</v>
       </c>
       <c r="R21" s="2">
         <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.675e-05</v>
+        <v>4.575e-05</v>
       </c>
       <c r="S21" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>356.0</v>
+      </c>
+      <c r="T21" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>0.000372676464</v>
+      </c>
+      <c r="U21" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>0.0004272</v>
+      </c>
+      <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>323.0</v>
-      </c>
-      <c r="T21" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>0.000338130612</v>
-      </c>
-      <c r="U21" s="2">
+        <v>2.3030568e-05</v>
+      </c>
+      <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>0.0003876</v>
-      </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2">
-        <v>0</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0004193220879</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>0.0004764797703</v>
       </c>
       <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00048067</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>0.00054619</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>48.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>55.0</v>
       </c>
       <c r="AC21" s="1" t="s">
         <v>140</v>
       </c>
       <c r="AD21" s="1">
-        <v>3661.868</v>
+        <v>6874.66</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>158</v>

--- a/reports/thinking_agent/report.xlsx
+++ b/reports/thinking_agent/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="174">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce3-3ae4-7503-a0ab-5727ccb269e0</t>
+    <t>01a0d143-04ca-7260-9315-3e47f7d31f06</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,13 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce3-3af0-7023-bfe7-9ecff221724c</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d143-04d6-7b93-8151-5656978a48b1</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -345,10 +348,10 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_087fe8fbe0369434006ab36d6021c087d28b8d40d79a9347bb", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21hyxqpZcQG_HQjOdXHAYprN7-gn12RjKOj6CkDF1WjbYdl8-YkBWPJnBwcPA5GNdT9KW496EiI4fiulNaDvjwwkJDmZxO3cFg2tgeefpqM4X52unRjo09eL-V-8YOgvHO6iddrJQwmYmoKiSrUQ_Qtak0k458fyIPToL9IpBMaEf7Nn99W6NDzifjf4iwFmdf6_1mIVvoAz_I7h0qGE1WA_8Z8obUtoYq5Wx0KgpCCOG79lpoHHX18j-f1Er24TZMIVCVIhSdOsMydGzYM3ybB-I5sw065zH1NnjGB56CDaHMl8c1P6DaZgwHZz9BTslCoINyPCpm0lsUIjiiKYIKbBMrF3vcQHIXisEPVU5snAD1HTL2QhYlgvItLqDxNQyKftWJq-RXOjCvlK3hL3L6EUbm0ithgKb2gDnYzZzhMDttIWewfKKqrNQEOiI48eRjB0dmQvRflVl32JNDmag1Tyoj_y6QQ5OCuw7Pwh73CZdmOGqDiUC09RathS50RU8CRSYn0i_c6ypVGCV-kWq9Atljq1_58UBWaenvmodb7-CYWFYzBAODfkJ3zDArYWxjv_Wu6JiMrP_vVKO6r6FptPcLuMjZowwnt54HuFFPXb12Nq9CAwWQIJ4XMT3cpBASb8N7tcxeqtsc3iemSVerFb11GbRYi8VFLjMlXs80XS7exizfFWSSUOjIs0gPSuWspCBPDDwEJLQc07Z0RDHZZLkw8c2B9wC9asOYui_HkG39kx9Ym_uv63T5KCIoYlZFiSIF2lkduuDeqD7HePa5qrcc0KThlihYxeBciCx27pYmylUd18auXbuMjTvQZnkKDxYivUiADUKSOn-DrlcYsbL5YADD3JicXZLtNN_i-MPbp2HDkFz6NQGKFRKKe95RdpA-xzA-0kByKWn8CuPgtrvzdI9u1MZ_mUlBwBlV61f922bmQZpWYQl-vx_G2CZJCynDj0MSeO5q8TtOQFSV7W_v-_JCCt4s5iqA7e6YSvcK-_I3LM9XY0u4x-pvQkvj9njMEhspS01A--1z4PrAC-YHorOrUwedbo-YOeP1aiiWpVoJqBhhODwP-OzNr28VyhnZdhE5eJMcMfuC98HZEjqHjs526InBfZ_KJPALOR7tEcko247qVpCT4LlxtwpTawsEtmtz8Tw9R_f4SV5n7IEmooup2_zjHWjojI4mC9Vd5r_NEaLL-wolikYiD157hSvNAUUBWKe9hLFs_ekuF94t4YF1j77_zYbg7Cd2c6Y81Rhvod6ZyFntD_MkOdPnX5LJNr5zY4G-SdStTv8UYO0d2v1wvzB16Bnd9S8cgXPose_7Werto78oaNNNiDDq3O_gOEGHbWuFVevcEUsWDFSVENPDwRs7nPm80fWGc8bc6umwtPzvbJPpb_X8fp2aEj9O6CaxcNqLQmOUFGxJGGzbxKpQ4nGwBpncEPiXDs-5l_3zRTWLvITFA9PP8TslW90EyJLvkaFLzNXcfO8jei8Ghw4TwCuZPEk9XY_q9uXvI32GhqCtENqlU34xxqHgi"}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_aVaOvXFe3x2okTXOSttMNEhB", "id": "fc_087fe8fbe0369434006ab36d61f17887d2ba98a391b40b6112", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_O2BYZEY6v8ipZUlcnWiOVtDw", "id": "fc_087fe8fbe0369434006ab36d61f19087d29539413fdfbb3774", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_wKjW8pSc1KbpgIpvSi66llf4", "id": "fc_087fe8fbe0369434006ab36d61f19c87d28f99f8d4567bd0f3", "index": 3}]
-{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_aVaOvXFe3x2okTXOSttMNEhB", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "database"}, "id": "call_O2BYZEY6v8ipZUlcnWiOVtDw", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_wKjW8pSc1KbpgIpvSi66llf4", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0f5f50232162cf94006ab48c0af67887d2bb051366b44ed5a8", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwLMH_SkaR3ymZharpbhRD_aKLl_Y_HDMbwHDeesHxEsQAs4pCxvcJvh-W0mctNdu4PPlcBBuMCBacU3O8laWretOD-U3USibq9M7fVZ-G-rCaQs_FtvVmznvXo4ay8nECDY8zJUqwYs-IXiZIiL75L2wUjsu3mamrOC-MnBGlqAJufRVA4upw4jR1WSWQ7WTtfTd9gfCRXbiv31Byv6AgLK3NvbproKl7ofdJdI2jLMs4syWbGdMpIqm8g2KYfQPjxZp_TucYOa6zUBfKbDxAaslRX-g-9KdR7CvNIACfsC4m49Bc4aFfCYVVrABav5ED9BaVw-pHC4qBcWu-9lyqglnISMyakzMItr4HrXYinnClcyxK9CztWRN1IEjfdv8VrdVCT9fX8xKF8Rnf2DSkeehFZ1ccNix868PJX7x6yxICCBhXMm2uwzkQYZlSV3lOhL17v0Htl4Uebl6QhNRylsrBqql8-MwYITYEirFrHuNdz2EMu5c-JuoxZNyvcnMkVbqYyhGbMKwZK1PpxdXgBbgRiAG8ZLXoGarc5nIswOtgHE743jZBE6k1hC9N8Obne-SjCRPivocWWPzZ1bKokCOf06M6a0IW_xab-cx4z8TCYoEgNxfVzGxIaS6KqjPdnppLyTiFBVX0jFalsYTg3MJyJlzcFARYoL2kb-LSpYowP-7caC6-sAvfpmv2xB6EnLnxlzhkquUpVAylmTuQrg1xePfhNq2TA2m0mghAOAM6navdux3OBSKlhKibjvdXbwrNh6Cb3K3mM_Qz1bLjv2NMgPzj4C412jgARy-M2sn7HGHiByXRdQOiQcbXDOxXXsxEZ_zidOmFjSHA3t-PuH0w6e9DYZ-l3KqC0sClWf8dR7xG3sJe4rtK6O6jV6YsBpFivBSOZZiaAkuE9W5eDEjGGJbsLn0c-t46kZJr5kHxjD9oign7I83Lw5u6AxQrCkkLnmXJnj9iPin8XAla3aqQHfIcqK438VdbIt0D3jTek2vFLQo6vayW4UpsnrGpSRlEUw4LJXjKfcRgHUURGSc0Sm9xCGXW5i9BEFvt4VhQ9LMqiGxmNvdB3bgXVlpD3YN8yDpsItpZ_vszdwJ3sKb3s4kMuNI7_yLaLy4YjuqrMMvh0WSGIMnimdC3dVucJxqT37UECmz3NJYfhQSxjliubP4IeigJzl9etsDCm7kGQF-zHFoCPeyLNR7kMj-zhKbjW9FO8kGpTqZtWoYHWkqfHX9Uc_Kw9np-VDcmy9iPNiSb1lR5ufrH7BNWa9c5j793Kzgm8b71KBZx96gNLosXqFJo1sxD209UNCLWJ0fqUPhgwGSmMh71wPLDQRG23bPmTtiqIRCkbo8rXTFx1Bc_WEzhiKVANl904o0VaRaR6ZMT5BIfLhUdJN6LIvOAz"}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_LdCImJLOwPLmHCQOIpDRORCU", "id": "fc_0f5f50232162cf94006ab48c0b963487d28c6e9e2f0b7af92f", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_I568VFsb8CIxRYCciO9yryjA", "id": "fc_0f5f50232162cf94006ab48c0b964887d2babc260d724e3fb8", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_rQraeSaQjBZIVWFRFCAnsXUO", "id": "fc_0f5f50232162cf94006ab48c0b965087d28173ad72667c35a3", "index": 3}]
+{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_LdCImJLOwPLmHCQOIpDRORCU", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "database"}, "id": "call_I568VFsb8CIxRYCciO9yryjA", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_rQraeSaQjBZIVWFRFCAnsXUO", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -360,7 +363,7 @@
     <t>Tool · inspect_service</t>
   </si>
   <si>
-    <t>01a0cce3-479a-7693-900f-e4a69b9f4b5a</t>
+    <t>01a0d143-0e22-76c3-a765-a051b0cd1a26</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -375,7 +378,7 @@
     <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
   </si>
   <si>
-    <t>01a0cce3-479a-7693-900f-e4b1f6eabbb5</t>
+    <t>01a0d143-0e23-7700-857b-e646dc6b85ec</t>
   </si>
   <si>
     <t>{'section': 'database'}</t>
@@ -384,7 +387,7 @@
     <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
   </si>
   <si>
-    <t>01a0cce3-479a-7693-900f-e4cb7e4f4396</t>
+    <t>01a0d143-0e24-7b31-9020-64c9c804d81e</t>
   </si>
   <si>
     <t>{'section': 'constraints'}</t>
@@ -396,10 +399,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce3-47a0-7503-98b1-efea8452af33</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0d143-0e2c-70e1-8f36-ddc7c938fe14</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
@@ -410,16 +410,16 @@
 Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
   </si>
   <si>
-    <t>[{"id": "rs_087fe8fbe0369434006ab36d631a4087d28d50aeb78b2f6371", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21kJIVlJHpeTwk4ZJDpJV7OZ_ffnsIoiCREsrK2drmHuk_E4YnGujhm9At-X-nI_ZbBdVZYadkx0jweBH0_vekc9BQHkeLyFa7n_9rHgbET5_1uHRt65DxKRknQQD-q6q35Qg6mmRV-SjgIUv0UqYRhCcMKAgOkK5ohvu1gcsCTfOMS7Tv1Z8XUwRH6K_yMhBUzpMD0tf4o-JPizHrwTUeff1F82NSliDathjcS4OY9GnlBp5TrVBUud5TC4E_WAmCJufoW3PKv2gyzAfCWLAbaI28UB22ENFDWUyMIN4j6qSm0Ou6-HlNu9ZyNM6JpgOguqVJg-EPbw1xzAbuxtB2XF3lNGMhhsS6I3FTqtKsHSWGEdsaZx5gMck1w3GPCmoCSvSKIf9n3Ke-reL5KiH1zCrw2Ia8sOmIIxr9VyeH6I0SuTeYw2Y0AHBdE_KOALtNg9S4_91MSII-N0pdeKd-bkipmVR8B6Y-pO5qSqw-AVP80SEF6kpaiSXRnFXqKZikFpvydBmf8vCjCNwW5FprtQrf0stcbXE2xCodL0MceWwc0I2EPHEztEVjL8ao_EoAyRmUyfNaPA9lwF0Ka229y8UitHDGMrnMDjAe5vZX7bvzCgk7v0INFLaqCLcuJFDLTGsjLGzRcc3g9yilQrI-So459WZLq2ojlqS8dExpM_USMeYc-E2w2GpQMh3B6PWVWFLn1dDP1nW6xQNW7K28nppdmP6wCB2yAez-NRPRm_uXGsyJURMZlMxCU--6qXRiLGtsWAuf_bpM8z9VN-nmuUsgcf4GMu_nemJMF8zERjuQ2pKjZMMTeUz_bceiXegkKbO1rj9mgEHN_TmkI3XZuyIdAhkpHrjWGy12kGZKpOb6XSQyMOwmXX1pKH-zrcqih6LpVaBrh9YcCPp8gxH0eR2h4mKJL5GIjAklhXET2V879fcpp-5qxZPH7N2ya6LxmHTk88kBQZKlFyCGKO6TxYsOFkkBQjN4rcZnUm1JCNYDigvAAVrTb3-yRA0KLi8yq6fe_1PqN276nMALpfcScBOQsvi5DVA7mOjdii5gLACqtwQZtVclaf1ngTG5e-qH-vyUUh6uoDMflDGS8xY_p0oL0M2KUaUKYUoQWSjDVsZRKaxLeE02lkgK0G7WTyXxVhrRATAwaRVeghQfM6ZwIFhNVGRtSackEiwYZov-Ygk8-NBLblvXX184oKZQCPjBunWroC92ZHEsbAeDiAcs0kltmGeJER8qXU4yA-27RKvSFhTgH4mZ4nGCkH8fvuV62X_oR1pBtc0XN2KVdlOHN_S79-eXVD4pEnGNeNeOo--y0x89w7W0avca0-hlAManlV9EjSuX7h0UB1ZgIK3qRCw=="}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_M2OPB63aVbgX7r0hBUo65DWL", "id": "fc_087fe8fbe0369434006ab36d646a8487d2a5d5b5b99a3d0989", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_BU4MeNXeL7IyMj29Oylb2289", "id": "fc_087fe8fbe0369434006ab36d646a9c87d29e58ce0ca9299df7", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_5wm6GO9yXwMhVZAWQV8uF8qO", "id": "fc_087fe8fbe0369434006ab36d646aa487d2a9bfb5f459a3ebbe", "index": 3}]
-{"name": "test_plan", "args": {"check": "load"}, "id": "call_M2OPB63aVbgX7r0hBUo65DWL", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_BU4MeNXeL7IyMj29Oylb2289", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_5wm6GO9yXwMhVZAWQV8uF8qO", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0f5f50232162cf94006ab48c0c714887d298f20be716932472", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwNy-BIVdkDz2CK4_ZxHBfVcoo6HlclZ4CtmdZlgy3vJSLm4yzT0eOwn2dYT8FFNWR4Qeh8W04_2FV4ibnreMFzYyGHaLO94w_HWCGJodoUyPk2CyrbPd40KPxAhVo3mIHlTd-Oe8I_mqE9c1H4V3CracWis1VT8ftuRbw4zoG_j3Evkql7y8nPa24umb8_iAan4WdaL7MBngoyfO-AxpeKbCJfFMz9jNQBiY1tuBFlbYiqfrj0r71vTCHN1v2om4AR6ZpBmprBlhgQ3QM2JO5KRqFGVMKtcD2X73TdFM6yFvw0uXkTQesu3PF06RVMhaUQVQOS37jVAhzTzBC8Gn2-O-PIdnaU6TXKmZq0hpv03M3cZ9L2dz-qIPIKqbWC15ZKzontfcxSba8M3piiBbks2IIVcxqTL6CSAII7Y9X8k8nNUxZwGEaxYIbu4WQGxqS-9lPol18BJuI_VTXj91_Qr0ySaWegd21BoPIig6ZWLtErExbz0QQ2cfY5bSeLK-98OV_UMwfHfWsOk1_48tDy3WIlUMWrLX9PKTFSHgM_WqBStcHy1Ivjy-P83btjHY_6u_tVfcvC7PAXofvhBA-W47A7thm44QWEqzKWAkFsTUUtiCKEpX2sCpGZfQ9HlaldsOAhYsECybPewpZFUd_dCAhnbcmI3-GMGQjSDqxQRTTV_cBKwUwIl8seovcpczs7xUIyV8klXyH8obUuvMSUDCM1RyNWlcSvLKqPbpmVmSJCsd5tsYEa8rDaS-wL5Q3ReJWi6R0ADPSetzSNnQr1HKSv52Qse8g448FZJYSjOa7Uua7qki6pe2hGryST5s3dhuDAGR2lYfgP32eZjW788zoN03aaA7MKFGnfVzdR8zsxSTYcSLrPjuV853BeMpX4Jv6e6YDB3qr0xN1d8k03LdwiqFwBIuvIspA8-vBQ9yF5r7S1N0VZ7L0BKTPCK2oHMSIqBMtteh4sHPNMDop8my0j-u8dP8Trnexp2O_N6qsmzlUSYhCT2DXDM1C-AiOQZHIqqxxDZcbIPMAn_WptTUfmKtzR-Mg21EuENnxFBLdHkVrXYUMtU7hBddKO0j5JbhsrC7cc6oV6dzWyHD9Uaa1pbExvlWql5o69F9pScETPVjOBuSPRKMTpCbkIsx9F595L96gj54UD8-Sq57qALX9mCg8T0U2NpRowV6oHpxV7DVD0U_IRcuplSTLHQQmW6gkiqwraU1d64QN60cN4pUS2BGde4871t6QGW6gucJkgNNK9tUgVyPoDO33LO1U8jemEiGa9Ap5MIlEand-gfbFEQhCkQGlGqmHeH4eVb0j5j_8pnmzDrCO14ijw1By0"}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_GuYDPVzsFwjAQytgTrE5coMh", "id": "fc_0f5f50232162cf94006ab48c0dba4087d2bc77c552fcd18f73", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_FDoVOsudmPB3oVVnxucmKH3O", "id": "fc_0f5f50232162cf94006ab48c0dba5c87d2be58a77f867478f4", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_O6uE6kt3giwNqsTGObqvanK3", "id": "fc_0f5f50232162cf94006ab48c0dba6c87d2bdabc9584034452a", "index": 3}]
+{"name": "test_plan", "args": {"check": "load"}, "id": "call_GuYDPVzsFwjAQytgTrE5coMh", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_FDoVOsudmPB3oVVnxucmKH3O", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_O6uE6kt3giwNqsTGObqvanK3", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · test_plan</t>
   </si>
   <si>
-    <t>01a0cce3-5150-7812-b362-4d2a602aacbc</t>
+    <t>01a0d143-16fb-70b0-8904-5d3f80cad912</t>
   </si>
   <si>
     <t>{'check': 'load'}</t>
@@ -428,7 +428,7 @@
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.</t>
   </si>
   <si>
-    <t>01a0cce3-5151-7f42-8455-57981b16d65f</t>
+    <t>01a0d143-16fb-70b0-8904-5d4acefdfeaf</t>
   </si>
   <si>
     <t>{'check': 'freshness'}</t>
@@ -437,7 +437,7 @@
     <t>PASS: account changes invalidate cached values; maximum fallback age is 30s.</t>
   </si>
   <si>
-    <t>01a0cce3-5151-7f42-8455-57a6f5433517</t>
+    <t>01a0d143-16fc-78e1-946c-8c3a79b0aa9f</t>
   </si>
   <si>
     <t>{'check': 'rollback'}</t>
@@ -449,7 +449,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cce3-5156-7441-abb7-b632fcf0baf1</t>
+    <t>01a0d143-170b-7dc3-b425-7a26dcb11ef8</t>
   </si>
   <si>
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.
@@ -457,7 +457,7 @@
 PASS: feature flag restores original lookup path; no schema migration required.</t>
   </si>
   <si>
-    <t>[{"id": "rs_087fe8fbe0369434006ab36d661aa887d2b04f749228fc66d4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21mkanf4m_IV5w8_10TUN5GejPfkAkErHTzrFImKR7h5YP_mb2F9Gb_l-VxY5oO7YvU6bb--DoxSa5_bCJWunkMmd5KqcNiTgn6sWYGjdw8NlpLrXLdMgKgdN8vRNYDWXxyUCDZGAGkiWQXo0uUs2ws-rgXiOQmpZqsrgMi_TPYXdKgyIvosbGJjbM3omyyyhzX1U1c7ATp7LtIGatfunQ06McUDXplzaioOE5bc8-_IgzjCZLO5X3XCaalJnq1zzfWsPJcYpornU9-JViQxB_JOl_L0rwdHEEBv2hra_8-V9lDQlgzhFxCrRO9x3z8kXkynS837hXKQnitTv8V0909HHIFh3qSGzIqdqDKq7ryOCPz2C2p3Mj9VWrsS8XW6oepXhigiGAZLFc4AUyB6lQHeeyTN5cToJ3k_oTt_jEzUODJuWDmot7llR0f7ps6OjVKzJOqof4NKDiPJoKTuRTZJOVaG7Q4vtjgKB7Rz9Vi_DYkGm2q-kyRPpZcFgSuV4djTDa_J--RGymXc9wfCRKTfx-S29o9-jem_9JlGtYDFJdVoSJ6BIwO1Ad4vVd9020QEi5K0_bu8OiwfrYUYD_nyifZnwogWEhoz5N_R6wFDsuUh8Qkhu_rJtSSPoHjb_1_7Vt6uF0bxYBoMvB91uu3jA3DDvU1AApz-md9sh8iSRGwKuqO7BhysbVJVQix8poxIsz9cbLQlcwMh_B8QxBvajlR66oRj28xekroHxWvE3_QFyUlXN9CsK2MhoqAc0gMotqrvXyAOzaL7PS-27-OriDV9cxODp7vRPaShjSm-4tu3UmaURt__-a9-9JHDuT0Xngt7RRb82m2PTKL-4F6D7SaDmNr8pvdgvj8zfSt_YYe6E1SXEXPQocB0V6BP9roHraFeHD4d41c8zY29iSjvuPmBgZzwhZyU0Z8Em_A6-2t6kfx9E8IFLMHRujQxn3PazL-Vv3fqrEmEgqIAnGc7krHz0kxqn_NSL2sJyI6YgZ5sCN-Y8Hi-RsxOnjiLqhb48y57bec8JFNz36olNPePQf_EB_v3YbVYBKwK08Z9c_6pj98ujxh6n09hthvGcLh6usghLZoYwGRVfwoMLkJScQC_SThLXAWdMSjinYUaCZ7kTZon4NGlEqsv1uk4o7wHvTjNc7chFbh8gP14Mr_jQL2BQmpWbdfvnwK-SFDA0gIZfpbpvUagtRtP9rJY4jm7_-UndsjV9E3LuihRkzYjAhag-ARcdEhE2JXBtlZOJIJMUjEq10VA6YkuPkpuLwFYBukWoJ1yZg9bwteR6tJ_fIr_oPWhvXenvzc9KH0fjg="}, {"type": "text", "text": "## Findings\n\n- **Traffic:** Peak load is **240 requests/s** with current **p95 latency of 1.8 s**. Latency increases during database bursts.\n- **Database:** The connection pool is limited to **12**. Query median latency is **80 ms**, but p95 reaches **900 ms**. Requests perform duplicate account lookups.\n- **Constraints:**\n  - Target p95: **under 500 ms**\n  - No additional database nodes\n  - Cache lifetime: **no more than 60 s**\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so repeated access to the same account uses one in-flight/result lookup.\n2. Add a short-lived account cache with a **30-second TTL**.\n3. **Invalidate cached account values when account data changes**.\n4. Roll out behind a **feature flag**, retaining the original lookup path for rollback.\n5. Monitor p95 latency, database pool occupancy, cache hit rate, and account-data freshness.\n\nThis avoids adding database capacity while reducing duplicate queries and database-burst contention.\n\n## Validation\n\n- **Load check: PASS**\n  - At **240 requests/s**, deduplicated lookups plus the 30-second cache achieved **410 ms p95**.\n  - Connection-pool occupancy was **65%**, below the pool limit of 12.\n\n- **Freshness check: PASS**\n  - Account changes invalidate cached values.\n  - Maximum fallback age is **30 seconds**, within the 60-second constraint.\n\n- **Rollback check: PASS**\n  - The feature flag restores the original lookup path.\n  - No schema migration is required.\n\nThe plan meets the latency target and all stated constraints.", "phase": "final_answer", "index": 1, "id": "msg_087fe8fbe0369434006ab36d669c8087d2aaa9293b762ff873"}]</t>
+    <t>[{"id": "rs_0f5f50232162cf94006ab48c0efaac87d28f0f4da572b3b767", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwPalmAL5JJatDhVidJRa_O0ewgYd-Q5EckSLx8GTVw37G3uUyp9XuN6nUay4POxBamY0tb_tWW4VDpVY_7i4zqsP_ORy0VveQsjXOmuUWzRefnMKF1QyAliyzRn6tQPYNWIf30ZqPaGjzLE1ce6EGU7Qa_PWQ_F_pfdApgI5TZGdEFsyhBytynQRFzRjxW8WvU9Wc-xwmoBV08Wz7tediaON20DHIJIPiF2Iad9D_AHhcw1eFTLB9uwTYLja5HX0tv8T5V8cz2z3qUDb2c0aWnExPcsT0KuN8eBldz2eWVrHDSGS4_a3SLcSNvQLKCPBTvadg6UeV1bpmm7VxwDZZhca9Kif7OSTNZJDh-F2gyB3RS49HQ4_stHjcLjko8qHwlyGRIvww0kDEByehiN2faVyLHYyelcxAdiSRqRdKgxjpFxuJLjGMQ9piE2J0b10faiwT-ok-KFvBVYgtTVCKdEDStmQrE56StvWbCs4to4P4GHhbJClZW-f2QTneyf-HorjK09bjwtl9jOaXoAIPwuqfT9pXUVwQecSNJMshJ154kRtC8ctX8K3k1Fxo4ogYhMs5BRk2WV7ow7sr1rlXxBSaQXNBb4YL4ARwsOFWGBP0GvdtJckS3Vb6vkslGpQ35eC4L41vZN9k_6BAFqp94xDHoQeegSiuJ-VtAwBgmTmza29NyaA9q6gtAkepzOBj2M4S8ReGLCNhgxxjKKRrD1Naqg35-G6s3UxzHNE6nJWJqC-WN-rX09HtoYdM6-_ZJYDCxdnOBILS-0PZf-rv7ueZAbSNgf1tnEmre5ckcppzs4KdtMQrw5PFH4dCZbOqfkQ931eRs_yBs0Q3tkYiGpa_GjRjFVv4o3sui98SaYqTF67K-VRVHw0_PO0gJLkWTBVmTB1koBYlAfpCxi1hzis3Ojs0zjXjr9N9sIe8SsNnR2PVn9y5feMOk8emyB4TTES-fBZkW9aiFtiVur1IIXX4gPd2BK9H-vUpsIa20MRyITIK_5G9fSGh1fyhklmPWwZfMsR65QRhUMBRm8kpGnXHwMf6ts4N3hZbUaEikyK9B_CteLAI78eknbUmDkhrqJZkqICj_iA2654nDEFVVoOgja0F0FfeE50yt9_XZjqGY2D0DFAxMW4vO2iVqOL9uzXynflqOAEmOrecvXcVKdo1YCqpEU_sdqHFQLyH-FabveBIfTrToBhhYWNWLQva_dZ961IVIG7gxEwC3XFrHY_bq3kiJKnl6t2smR9_9MscxvSUDvAOvpilKR7I_Y1RQS_TNvJfCTUUKoOoj2chLG6WnLQQ-Q1JDFRnKtZd5U0NBgjVOB80V0glEtL_66Jj45693jhWvFK7T25Dtl6QcQpRVRcTQfFsz-sPDOUfTPIktgRstJCPZofqdUF3W09bcUuUmQ210GzUJrGfw9qbYW72i6gAcT6J1fU4IDGK4PqfwV1sixOXFc1_56DhkJXac"}, {"type": "text", "text": "## Findings\n\n- **Traffic:** Peak **240 requests/s**, with **p95 latency of 1.8 s**. Latency increases during database bursts.\n- **Database:** Query median is **80 ms**, but p95 reaches **900 ms**. Each request performs duplicate account lookups.\n- **Capacity:** The connection pool is limited to **12**, so duplicate queries amplify contention.\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so the same account is fetched once.\n2. Add a **per-account cache with a 30-second TTL**.\n3. **Invalidate cached entries when account data changes** rather than waiting for expiry.\n4. Roll out behind a **feature flag**, preserving the existing lookup path for rollback.\n\nThis requires no additional database nodes or schema migration.\n\n## Validation\n\nThe plan check passed:\n\n- At **240 requests/s**, deduplication plus the 30-second cache achieved **410 ms p95 latency**.\n- Pool occupancy fell to **65%**.\n- Cache freshness is bounded: updates invalidate entries, and fallback data is never older than **30 seconds**.\n- The feature flag restores the original lookup path if problems occur.\n\nThe plan meets the target of **p95 under 500 ms**, stays within the **60-second cache lifetime constraint**, and has a reversible rollout.", "phase": "final_answer", "index": 1, "id": "msg_0f5f50232162cf94006ab48c0ff95487d29fc9b5b84bf25aae"}]</t>
   </si>
   <si>
     <t>investigation_agent</t>
@@ -478,7 +478,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cce3-3ae7-75a0-a9ad-6ff075ea5e6c</t>
+    <t>01a0d143-04cf-7273-8789-195635b8e332</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -490,7 +490,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce3-3ae9-7c22-9033-cd94353ec929</t>
+    <t>01a0d143-04d0-7793-92a8-9b3f8d03e42d</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -511,7 +511,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce3-4798-7120-9457-da096458d7aa</t>
+    <t>01a0d143-0e20-71a2-ae50-be97fc78337e</t>
   </si>
   <si>
     <t xml:space="preserve">        inspect_service</t>
@@ -523,16 +523,16 @@
     <t>Read fictional service evidence; no live service is inspected.</t>
   </si>
   <si>
-    <t>01a0cce3-4798-7120-9457-da1c6e8013fd</t>
-  </si>
-  <si>
-    <t>01a0cce3-4798-7120-9457-da2a91e54816</t>
-  </si>
-  <si>
-    <t>01a0cce3-479e-7492-9e97-4dd3f7af5644</t>
-  </si>
-  <si>
-    <t>01a0cce3-514f-7322-bfd1-a2c0371ca2ca</t>
+    <t>01a0d143-0e20-71a2-ae50-bea24b080c00</t>
+  </si>
+  <si>
+    <t>01a0d143-0e20-71a2-ae50-bebd9abe0314</t>
+  </si>
+  <si>
+    <t>01a0d143-0e29-7f91-b83b-4cd56b84abd6</t>
+  </si>
+  <si>
+    <t>01a0d143-16f7-72a3-8630-755408a9036e</t>
   </si>
   <si>
     <t xml:space="preserve">        test_plan</t>
@@ -541,13 +541,13 @@
     <t>Return a fixed fictional plan-check result; no real test is executed.</t>
   </si>
   <si>
-    <t>01a0cce3-514f-7322-bfd1-a2d02cc51e2e</t>
-  </si>
-  <si>
-    <t>01a0cce3-514f-7322-bfd1-a2e1d074a0ec</t>
-  </si>
-  <si>
-    <t>01a0cce3-5154-7001-8956-e317466c003b</t>
+    <t>01a0d143-16f7-72a3-8630-7569611e9968</t>
+  </si>
+  <si>
+    <t>01a0d143-16f7-72a3-8630-757d9b91667f</t>
+  </si>
+  <si>
+    <t>01a0d143-1706-7b00-a671-00ef4e5c4926</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1014,20 +1014,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
-        <v>0.0012350752749</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
+        <v>0.0007385614895</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
-        <v>0.00141577</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
+        <v>0.00084277</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>124.0</v>
+        <v>74.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>142.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1038,20 +1038,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
-        <v>0.0012350752749</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
+        <v>0.0007385614895</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
-        <v>0.00141577</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
+        <v>0.00084277</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>124.0</v>
+        <v>74.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>142.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1085,23 +1085,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>2099</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.6789173e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.198e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1114,8 +1114,27 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="34" customHeight="1">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1125,11 +1144,8 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="34" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1137,10 +1153,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1151,26 +1167,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2099</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0004577761575</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00052475</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1184,48 +1184,29 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="4">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" t="s">
+    </row>
+    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="5">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.0248512e-05</v>
-      </c>
-      <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>5.76e-05</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+      <c r="D12" s="4">
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1239,26 +1220,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.6998016e-05</v>
+        <v>3.575508e-05</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.68e-05</v>
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>4.08e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="409" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1268,11 +1249,27 @@
       <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24" customHeight="1">
+      <c r="D14" s="5">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.730368e-05</v>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.68e-05</v>
+      </c>
+      <c r="G14" s="5">
+        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H14" s="5">
+        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="409" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1280,7 +1277,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
@@ -1294,59 +1294,59 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:13" ht="24" customHeight="1">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.0005755461075</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.00065975</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="E18" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
+        <v>0.000140373743</v>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
+        <v>0.00016018</v>
+      </c>
+      <c r="G18" s="5">
+        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1">
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="K19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1">
@@ -1354,137 +1354,118 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="I21" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="24" customHeight="1">
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="6" t="s">
+      <c r="M22" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="34" customHeight="1">
+    <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B24" s="4">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="s">
+    <row r="24" spans="1:13" ht="34" customHeight="1">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B25" s="4">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K25" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="24" customHeight="1">
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="M25" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="34" customHeight="1">
+    <row r="26" spans="1:13" ht="24" customHeight="1">
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:13" ht="34" customHeight="1">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    </row>
+    <row r="28" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="4">
-        <v>2315</v>
-      </c>
-      <c r="J27" s="4" t="s">
+      <c r="D28" s="4">
+        <v>2301</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
-      <c r="A28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="M28" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2099</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.66220926e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!C17),D28*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.198e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1493,72 +1474,72 @@
         <v>97</v>
       </c>
       <c r="D29" s="5">
-        <v>3</v>
+        <v>2099</v>
       </c>
       <c r="E29" s="2">
         <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.6789173e-05</v>
       </c>
       <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!B17),D29*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!C17),D29*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.198e-05</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1">
+      <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="5">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
+        <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F30" s="2">
+        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!B17),D30*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
         <v>0.0</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="73" customHeight="1">
-      <c r="A30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="H30" s="5">
+        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="73" customHeight="1">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>127</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="5">
-        <v>213</v>
-      </c>
-      <c r="E31" s="2">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.64537025e-05</v>
-      </c>
-      <c r="F31" s="2">
-        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!D17),D31*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>5.325e-05</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H31" s="5">
-        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1566,54 +1547,54 @@
       <c r="C32" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="D32" s="5">
+        <v>199</v>
+      </c>
+      <c r="E32" s="2">
+        <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.35984125e-05</v>
+      </c>
+      <c r="F32" s="2">
+        <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!D17),D32*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.975e-05</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="4">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1">
-      <c r="A34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="5">
-        <v>30</v>
-      </c>
-      <c r="E34" s="2">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.140532e-05</v>
-      </c>
-      <c r="F34" s="2">
-        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!F17),D34*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.6e-05</v>
-      </c>
-      <c r="G34" s="5">
-        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H34" s="5">
-        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+      <c r="D34" s="4">
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1622,28 +1603,28 @@
         <v>107</v>
       </c>
       <c r="D35" s="5">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E35" s="2">
         <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.804486e-05</v>
+        <v>2.62905e-05</v>
       </c>
       <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!E17),D35*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.8e-05</v>
+        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!F17),D35*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>3e-05</v>
       </c>
       <c r="G35" s="5">
         <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H35" s="5">
         <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="409" customHeight="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1651,24 +1632,43 @@
       <c r="C36" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="D36" s="5">
+        <v>65</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.83553e-05</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!E17),D36*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.8e-05</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="409" customHeight="1">
+      <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="24" customHeight="1">
-      <c r="A37" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1677,95 +1677,95 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35)=5,SUM('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35),"Unknown")</f>
-        <v>0.0001830493971</v>
-      </c>
-      <c r="F39" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35)=5,SUM('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35),"Unknown")</f>
-        <v>0.00020983</v>
-      </c>
-      <c r="G39" s="5">
-        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
+    <row r="39" spans="1:13" ht="24" customHeight="1">
+      <c r="A39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="2">
+        <f>IF(COUNT('Turns'!E29,'Turns'!E30,'Turns'!E32,'Turns'!E35,'Turns'!E36)=5,SUM('Turns'!E29,'Turns'!E30,'Turns'!E32,'Turns'!E35,'Turns'!E36),"Unknown")</f>
+        <v>0.0001755591955</v>
+      </c>
+      <c r="F40" s="2">
+        <f>IF(COUNT('Turns'!F29,'Turns'!F30,'Turns'!F32,'Turns'!F35,'Turns'!F36)=5,SUM('Turns'!F29,'Turns'!F30,'Turns'!F32,'Turns'!F35,'Turns'!F36),"Unknown")</f>
+        <v>0.00020033</v>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
         <v>18.0</v>
       </c>
-      <c r="H39" s="5">
-        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B40" s="4">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="H40" s="5">
+        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K40" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M40" s="4" t="s">
+      <c r="K41" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="6" t="s">
+    <row r="42" spans="1:13" ht="24" customHeight="1">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="34" customHeight="1">
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="I42" s="6" t="s">
+    <row r="43" spans="1:13" ht="34" customHeight="1">
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="s">
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K43" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M43" s="4" t="s">
+      <c r="K44" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M44" s="4" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="24" customHeight="1">
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
@@ -1773,35 +1773,35 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I45" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="24" customHeight="1">
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>117</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="s">
+    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K46" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M46" s="4" t="s">
+      <c r="K47" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="24" customHeight="1">
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
@@ -1809,60 +1809,41 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I48" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="24" customHeight="1">
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>117</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A49" s="4" t="s">
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A50" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="4">
-        <v>2498</v>
-      </c>
-      <c r="J49" s="4" t="s">
+      <c r="D50" s="4">
+        <v>2479</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="M50" s="4" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24" customHeight="1">
-      <c r="A50" t="s">
-        <v>140</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" s="5">
-        <v>2312</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.03383888e-05</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.624e-05</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="24" customHeight="1">
@@ -1876,26 +1857,26 @@
         <v>97</v>
       </c>
       <c r="D51" s="5">
-        <v>3</v>
+        <v>2298</v>
       </c>
       <c r="E51" s="2">
         <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>4.0277046e-05</v>
       </c>
       <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!B17),D51*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.596e-05</v>
       </c>
       <c r="G51" s="5">
         <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H51" s="5">
         <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="60" customHeight="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="24" customHeight="1">
       <c r="A52" t="s">
         <v>140</v>
       </c>
@@ -1903,13 +1884,29 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="D52" s="5">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2">
+        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F52" s="2">
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G52" s="5">
+        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="60" customHeight="1">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -1917,26 +1914,10 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="5">
-        <v>183</v>
-      </c>
-      <c r="E53" s="2">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.99109275e-05</v>
-      </c>
-      <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.575e-05</v>
-      </c>
-      <c r="G53" s="5">
-        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H53" s="5">
-        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>127</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="24" customHeight="1">
@@ -1949,49 +1930,49 @@
       <c r="C54" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A55" s="4" t="s">
+      <c r="D54" s="5">
+        <v>178</v>
+      </c>
+      <c r="E54" s="2">
+        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.8997575e-05</v>
+      </c>
+      <c r="F54" s="2">
+        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.45e-05</v>
+      </c>
+      <c r="G54" s="5">
+        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="24" customHeight="1">
+      <c r="A55" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>105</v>
       </c>
-      <c r="D55" s="4">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
-      <c r="A56" t="s">
+    </row>
+    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A56" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" s="4">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="5">
-        <v>22</v>
-      </c>
-      <c r="E56" s="2">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.3030568e-05</v>
-      </c>
-      <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!F17),D56*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.64e-05</v>
-      </c>
-      <c r="G56" s="5">
-        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H56" s="5">
-        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+      <c r="D56" s="4">
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="24" customHeight="1">
@@ -2005,26 +1986,26 @@
         <v>107</v>
       </c>
       <c r="D57" s="5">
-        <v>356</v>
+        <v>46</v>
       </c>
       <c r="E57" s="2">
         <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000372676464</v>
+        <v>4.837452e-05</v>
       </c>
       <c r="F57" s="2">
-        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0004272</v>
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!F17),D57*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>5.52e-05</v>
       </c>
       <c r="G57" s="5">
         <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>37.0</v>
+        <v>5.0</v>
       </c>
       <c r="H57" s="5">
         <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="409" customHeight="1">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="24" customHeight="1">
       <c r="A58" t="s">
         <v>140</v>
       </c>
@@ -2034,11 +2015,27 @@
       <c r="C58" t="s">
         <v>108</v>
       </c>
-      <c r="I58" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
+      <c r="D58" s="5">
+        <v>280</v>
+      </c>
+      <c r="E58" s="2">
+        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0002944536</v>
+      </c>
+      <c r="F58" s="2">
+        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.000336</v>
+      </c>
+      <c r="G58" s="5">
+        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>29.0</v>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="409" customHeight="1">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -2046,7 +2043,10 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
@@ -2060,38 +2060,49 @@
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A61" s="4" t="s">
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="4">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E61" s="2">
-        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56,'Turns'!E57)=5,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56,'Turns'!E57),"Unknown")</f>
-        <v>0.0004764797703</v>
-      </c>
-      <c r="F61" s="2">
-        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56,'Turns'!F57)=5,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56,'Turns'!F57),"Unknown")</f>
-        <v>0.00054619</v>
-      </c>
-      <c r="G61" s="5">
-        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="4">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="2">
+        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57,'Turns'!E58)=5,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57,'Turns'!E58),"Unknown")</f>
+        <v>0.000422628551</v>
+      </c>
+      <c r="F62" s="2">
+        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57,'Turns'!F58)=5,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57,'Turns'!F58),"Unknown")</f>
+        <v>0.00048226</v>
+      </c>
+      <c r="G62" s="5">
+        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>42.0</v>
+      </c>
+      <c r="H62" s="5">
+        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
         <v>48.0</v>
       </c>
-      <c r="H61" s="5">
-        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>111</v>
+      <c r="K62" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE61">
+  <conditionalFormatting sqref="A2:AE62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2224,7 +2235,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>146</v>
@@ -2233,83 +2244,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
+        <f>IF(COUNT('Turns'!D6,'Turns'!D30,'Turns'!D52)=3,SUM('Turns'!D6,'Turns'!D30,'Turns'!D52),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="K2" s="2">
+        <f>IF(COUNT('Turns'!E6,'Turns'!E30,'Turns'!E52)=3,SUM('Turns'!E6,'Turns'!E30,'Turns'!E52),"Unknown")</f>
+        <v>1.57743e-06</v>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(COUNT('Turns'!F6,'Turns'!F30,'Turns'!F52)=3,SUM('Turns'!F6,'Turns'!F30,'Turns'!F52),"Unknown")</f>
+        <v>1.8e-06</v>
+      </c>
+      <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D29,'Turns'!D51)=3,SUM('Turns'!D5,'Turns'!D29,'Turns'!D51),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="K2" s="2">
+        <v>6496.0</v>
+      </c>
+      <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E29,'Turns'!E51)=3,SUM('Turns'!E5,'Turns'!E29,'Turns'!E51),"Unknown")</f>
-        <v>1.570266e-06</v>
-      </c>
-      <c r="L2" s="2">
+        <v>0.000113855392</v>
+      </c>
+      <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F29,'Turns'!F51)=3,SUM('Turns'!F5,'Turns'!F29,'Turns'!F51),"Unknown")</f>
-        <v>1.8e-06</v>
-      </c>
-      <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D28,'Turns'!D50)=2,SUM('Turns'!D28,'Turns'!D50),"Unknown")</f>
-        <v>4411.0</v>
-      </c>
-      <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E50)=2,SUM('Turns'!E28,'Turns'!E50),"Unknown")</f>
-        <v>7.69604814e-05</v>
-      </c>
-      <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F50)=2,SUM('Turns'!F28,'Turns'!F50),"Unknown")</f>
-        <v>8.822e-05</v>
+        <v>0.00012992</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D31,'Turns'!D53)=3,SUM('Turns'!D9,'Turns'!D31,'Turns'!D53),"Unknown")</f>
-        <v>2495.0</v>
+        <f>IF(COUNT('Turns'!D32,'Turns'!D54)=2,SUM('Turns'!D32,'Turns'!D54),"Unknown")</f>
+        <v>377.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E31,'Turns'!E53)=3,SUM('Turns'!E9,'Turns'!E31,'Turns'!E53),"Unknown")</f>
-        <v>0.0005441407875</v>
+        <f>IF(COUNT('Turns'!E32,'Turns'!E54)=2,SUM('Turns'!E32,'Turns'!E54),"Unknown")</f>
+        <v>8.25959875e-05</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F31,'Turns'!F53)=3,SUM('Turns'!F9,'Turns'!F31,'Turns'!F53),"Unknown")</f>
-        <v>0.00062375</v>
+        <f>IF(COUNT('Turns'!F32,'Turns'!F54)=2,SUM('Turns'!F32,'Turns'!F54),"Unknown")</f>
+        <v>9.425e-05</v>
       </c>
       <c r="S2" s="2">
+        <f>IF(COUNT('Turns'!D14,'Turns'!D36,'Turns'!D58)=3,SUM('Turns'!D14,'Turns'!D36,'Turns'!D58),"Unknown")</f>
+        <v>409.0</v>
+      </c>
+      <c r="T2" s="2">
+        <f>IF(COUNT('Turns'!E14,'Turns'!E36,'Turns'!E58)=3,SUM('Turns'!E14,'Turns'!E36,'Turns'!E58),"Unknown")</f>
+        <v>0.00043011258</v>
+      </c>
+      <c r="U2" s="2">
+        <f>IF(COUNT('Turns'!F14,'Turns'!F36,'Turns'!F58)=3,SUM('Turns'!F14,'Turns'!F36,'Turns'!F58),"Unknown")</f>
+        <v>0.0004908</v>
+      </c>
+      <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D57)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D57),"Unknown")</f>
-        <v>485.0</v>
-      </c>
-      <c r="T2" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E57)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E57),"Unknown")</f>
-        <v>0.00050771934</v>
-      </c>
-      <c r="U2" s="2">
+        <v>0.0001104201</v>
+      </c>
+      <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F57)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F57),"Unknown")</f>
-        <v>0.000582</v>
-      </c>
-      <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D34,'Turns'!D56)=3,SUM('Turns'!D12,'Turns'!D34,'Turns'!D56),"Unknown")</f>
-        <v>100.0</v>
-      </c>
-      <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E34,'Turns'!E56)=3,SUM('Turns'!E12,'Turns'!E34,'Turns'!E56),"Unknown")</f>
-        <v>0.0001046844</v>
-      </c>
-      <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F34,'Turns'!F56)=3,SUM('Turns'!F12,'Turns'!F34,'Turns'!F56),"Unknown")</f>
-        <v>0.00012</v>
+        <v>0.000126</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E61)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E61),"Unknown")</f>
-        <v>0.0012350752749</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
+        <v>0.0007385614895</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F61)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F61),"Unknown")</f>
-        <v>0.00141577</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
+        <v>0.00084277</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>124.0</v>
+        <v>74.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>142.0</v>
+        <v>84.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>12621.976</v>
+        <v>8530.688</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>147</v>
@@ -2329,7 +2340,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>149</v>
@@ -2341,7 +2352,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.517</v>
+        <v>0.426</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>151</v>
@@ -2361,7 +2372,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>153</v>
@@ -2373,80 +2384,80 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K4" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L4" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K4" s="2">
+        <v>2099.0</v>
+      </c>
+      <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L4" s="2">
+        <v>3.6789173e-05</v>
+      </c>
+      <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M4" s="2">
+        <v>4.198e-05</v>
+      </c>
+      <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="N4" s="2">
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0004577761575</v>
-      </c>
-      <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00052475</v>
-      </c>
       <c r="S4" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>64.0</v>
+      </c>
+      <c r="T4" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>6.730368e-05</v>
+      </c>
+      <c r="U4" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>7.68e-05</v>
+      </c>
+      <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>64.0</v>
-      </c>
-      <c r="T4" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>6.6998016e-05</v>
-      </c>
-      <c r="U4" s="2">
+        <v>3.575508e-05</v>
+      </c>
+      <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>7.68e-05</v>
-      </c>
-      <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.0248512e-05</v>
-      </c>
-      <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005755461075</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>0.000140373743</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00065975</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>0.00016018</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>16.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>3245.623</v>
+        <v>2382.967</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>147</v>
@@ -2466,7 +2477,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1">
         <v>2102</v>
@@ -2481,83 +2492,83 @@
         <v>154</v>
       </c>
       <c r="J5" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L5" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2099.0</v>
+      </c>
+      <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L5" s="2">
+        <v>3.6789173e-05</v>
+      </c>
+      <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
+        <v>4.198e-05</v>
+      </c>
+      <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="N5" s="2">
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="O5" s="2">
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0004577761575</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00052475</v>
-      </c>
       <c r="S5" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>64.0</v>
+      </c>
+      <c r="T5" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>6.730368e-05</v>
+      </c>
+      <c r="U5" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>7.68e-05</v>
+      </c>
+      <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>64.0</v>
-      </c>
-      <c r="T5" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>6.6998016e-05</v>
-      </c>
-      <c r="U5" s="2">
+        <v>3.575508e-05</v>
+      </c>
+      <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>7.68e-05</v>
-      </c>
-      <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.0248512e-05</v>
-      </c>
-      <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005755461075</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>0.000140373743</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00065975</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>0.00016018</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>16.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>3238.117</v>
+        <v>2375.866</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>158</v>
@@ -2577,7 +2588,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>160</v>
@@ -2589,7 +2600,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>4.438</v>
+        <v>6.799</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>151</v>
@@ -2609,19 +2620,19 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" t="s">
         <v>161</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.977</v>
+        <v>2.474</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>151</v>
@@ -2641,7 +2652,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>160</v>
@@ -2653,7 +2664,7 @@
         <v>49</v>
       </c>
       <c r="AD8" s="1">
-        <v>4.56</v>
+        <v>6.945</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>151</v>
@@ -2673,19 +2684,19 @@
         <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I9" t="s">
         <v>165</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.112</v>
+        <v>2.015</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>151</v>
@@ -2705,7 +2716,7 @@
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>160</v>
@@ -2717,7 +2728,7 @@
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>4.745</v>
+        <v>6.075</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>151</v>
@@ -2737,19 +2748,19 @@
         <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I11" t="s">
         <v>166</v>
       </c>
       <c r="AD11" s="1">
-        <v>1.332</v>
+        <v>0.915</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>151</v>
@@ -2769,7 +2780,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>153</v>
@@ -2781,72 +2792,72 @@
         <v>49</v>
       </c>
       <c r="J12" s="2">
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K12" s="2">
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L12" s="2">
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M12" s="2">
         <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K12" s="2">
+        <v>2099.0</v>
+      </c>
+      <c r="N12" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L12" s="2">
+        <v>3.6789173e-05</v>
+      </c>
+      <c r="O12" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.66220926e-05</v>
-      </c>
-      <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>4.198e-05</v>
       </c>
       <c r="P12" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>213.0</v>
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>199.0</v>
       </c>
       <c r="Q12" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.64537025e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>4.35984125e-05</v>
       </c>
       <c r="R12" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.325e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>4.975e-05</v>
       </c>
       <c r="S12" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>65.0</v>
+      </c>
+      <c r="T12" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>6.83553e-05</v>
+      </c>
+      <c r="U12" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>7.8e-05</v>
+      </c>
+      <c r="V12" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>65.0</v>
-      </c>
-      <c r="T12" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>6.804486e-05</v>
-      </c>
-      <c r="U12" s="2">
+        <v>2.62905e-05</v>
+      </c>
+      <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>7.8e-05</v>
-      </c>
-      <c r="V12" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>30.0</v>
-      </c>
-      <c r="W12" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.140532e-05</v>
-      </c>
-      <c r="X12" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>3.6e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0001830493971</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>0.0001755591955</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00020983</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>0.00020033</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2854,10 +2865,10 @@
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2480.394</v>
+        <v>2251.859</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>147</v>
@@ -2877,87 +2888,87 @@
         <v>95</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="1">
-        <v>2315</v>
+        <v>2301</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>157</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s">
         <v>167</v>
       </c>
       <c r="J13" s="2">
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K13" s="2">
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L13" s="2">
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M13" s="2">
         <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K13" s="2">
+        <v>2099.0</v>
+      </c>
+      <c r="N13" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L13" s="2">
+        <v>3.6789173e-05</v>
+      </c>
+      <c r="O13" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.66220926e-05</v>
-      </c>
-      <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>4.198e-05</v>
       </c>
       <c r="P13" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>213.0</v>
+        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
+        <v>199.0</v>
       </c>
       <c r="Q13" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.64537025e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>4.35984125e-05</v>
       </c>
       <c r="R13" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>5.325e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>4.975e-05</v>
       </c>
       <c r="S13" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>65.0</v>
+      </c>
+      <c r="T13" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>6.83553e-05</v>
+      </c>
+      <c r="U13" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>7.8e-05</v>
+      </c>
+      <c r="V13" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>65.0</v>
-      </c>
-      <c r="T13" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>6.804486e-05</v>
-      </c>
-      <c r="U13" s="2">
+        <v>2.62905e-05</v>
+      </c>
+      <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>7.8e-05</v>
-      </c>
-      <c r="V13" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>30.0</v>
-      </c>
-      <c r="W13" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>3.140532e-05</v>
-      </c>
-      <c r="X13" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>3.6e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0001830493971</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>0.0001755591955</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00020983</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>0.00020033</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2965,13 +2976,13 @@
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD13" s="1">
-        <v>2476.851</v>
+        <v>2246.332</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>158</v>
@@ -2991,7 +3002,7 @@
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>160</v>
@@ -3003,7 +3014,7 @@
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>3.626</v>
+        <v>11.576</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>151</v>
@@ -3023,7 +3034,7 @@
         <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>170</v>
@@ -3035,7 +3046,7 @@
         <v>168</v>
       </c>
       <c r="AD15" s="1">
-        <v>1.142</v>
+        <v>3.618</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>151</v>
@@ -3055,7 +3066,7 @@
         <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>160</v>
@@ -3067,7 +3078,7 @@
         <v>49</v>
       </c>
       <c r="AD16" s="1">
-        <v>4.027</v>
+        <v>11.756</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>151</v>
@@ -3087,7 +3098,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>170</v>
@@ -3099,7 +3110,7 @@
         <v>171</v>
       </c>
       <c r="AD17" s="1">
-        <v>1.059</v>
+        <v>3.837</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>151</v>
@@ -3119,7 +3130,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>160</v>
@@ -3131,7 +3142,7 @@
         <v>49</v>
       </c>
       <c r="AD18" s="1">
-        <v>3.819</v>
+        <v>12.31</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>151</v>
@@ -3151,7 +3162,7 @@
         <v>47</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>170</v>
@@ -3163,7 +3174,7 @@
         <v>172</v>
       </c>
       <c r="AD19" s="1">
-        <v>1.223</v>
+        <v>4.515</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>151</v>
@@ -3183,7 +3194,7 @@
         <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>153</v>
@@ -3195,83 +3206,83 @@
         <v>49</v>
       </c>
       <c r="J20" s="2">
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K20" s="2">
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L20" s="2">
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K20" s="2">
+        <v>2298.0</v>
+      </c>
+      <c r="N20" s="2">
         <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L20" s="2">
+        <v>4.0277046e-05</v>
+      </c>
+      <c r="O20" s="2">
         <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M20" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2312.0</v>
-      </c>
-      <c r="N20" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>4.03383888e-05</v>
-      </c>
-      <c r="O20" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.624e-05</v>
+        <v>4.596e-05</v>
       </c>
       <c r="P20" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>183.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>178.0</v>
       </c>
       <c r="Q20" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>3.99109275e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>3.8997575e-05</v>
       </c>
       <c r="R20" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.575e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>4.45e-05</v>
       </c>
       <c r="S20" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>280.0</v>
+      </c>
+      <c r="T20" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>0.0002944536</v>
+      </c>
+      <c r="U20" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>0.000336</v>
+      </c>
+      <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>356.0</v>
-      </c>
-      <c r="T20" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>0.000372676464</v>
-      </c>
-      <c r="U20" s="2">
+        <v>4.837452e-05</v>
+      </c>
+      <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>0.0004272</v>
-      </c>
-      <c r="V20" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>22.0</v>
-      </c>
-      <c r="W20" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>2.3030568e-05</v>
-      </c>
-      <c r="X20" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>5.52e-05</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.0004764797703</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.000422628551</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.00054619</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00048226</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>42.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>6878.567</v>
+        <v>3864.516</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>147</v>
@@ -3291,10 +3302,10 @@
         <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F21" s="1">
-        <v>2498</v>
+        <v>2479</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>157</v>
@@ -3306,86 +3317,86 @@
         <v>173</v>
       </c>
       <c r="J21" s="2">
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K21" s="2">
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L21" s="2">
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K21" s="2">
+        <v>2298.0</v>
+      </c>
+      <c r="N21" s="2">
         <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L21" s="2">
+        <v>4.0277046e-05</v>
+      </c>
+      <c r="O21" s="2">
         <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2312.0</v>
-      </c>
-      <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>4.03383888e-05</v>
-      </c>
-      <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.624e-05</v>
+        <v>4.596e-05</v>
       </c>
       <c r="P21" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>183.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>178.0</v>
       </c>
       <c r="Q21" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>3.99109275e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>3.8997575e-05</v>
       </c>
       <c r="R21" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.575e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>4.45e-05</v>
       </c>
       <c r="S21" s="2">
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>280.0</v>
+      </c>
+      <c r="T21" s="2">
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>0.0002944536</v>
+      </c>
+      <c r="U21" s="2">
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>0.000336</v>
+      </c>
+      <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>356.0</v>
-      </c>
-      <c r="T21" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>0.000372676464</v>
-      </c>
-      <c r="U21" s="2">
+        <v>4.837452e-05</v>
+      </c>
+      <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>0.0004272</v>
-      </c>
-      <c r="V21" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>22.0</v>
-      </c>
-      <c r="W21" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>2.3030568e-05</v>
-      </c>
-      <c r="X21" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>5.52e-05</v>
       </c>
       <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.0004764797703</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.000422628551</v>
       </c>
       <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.00054619</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00048226</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>42.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="AC21" s="1" t="s">
         <v>140</v>
       </c>
       <c r="AD21" s="1">
-        <v>6874.66</v>
+        <v>3857.624</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>158</v>
@@ -3443,7 +3454,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/thinking_agent/report.xlsx
+++ b/reports/thinking_agent/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="174">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d143-04ca-7260-9315-3e47f7d31f06</t>
+    <t>01a0d587-b04c-7653-9364-f52a6d7ab108</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,100 +306,100 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d143-04d6-7b93-8151-5656978a48b1</t>
+    <t>01a0d587-b056-7e50-9325-ebc4f08f9161</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    System prompt</t>
+  </si>
+  <si>
+    <t>Use the fictional service evidence to propose and validate a latency improvement. Inspect traffic, database behavior, and constraints before testing the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    User prompt</t>
+  </si>
+  <si>
+    <t>Investigate service latency and validate a plan meeting the constraints.</t>
+  </si>
+  <si>
+    <t>Cache write</t>
+  </si>
+  <si>
+    <t>Context · added / total</t>
+  </si>
+  <si>
+    <t>LLM response</t>
+  </si>
+  <si>
+    <t>Reasoning</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_0dcf4f209eb0e9d6006ab5a3c3768c87d2ae1efb3b110746f4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaPEVFPhPTjMXxWj3Z7ym8YI5XUXqeAo895JGll8xScyxNxdjJHewzEZuyH7e0BdYIpRAWD63w0N50WEidEVLcCF4bZKJIWEZ6vfzxm7KuffgIsdWg_Eqi8vms9sjxMphJla69zX4L7BRCLPmdQlawUrbVkQhUIbhe5yQioVkim92FqVWpR-GAaASCpaFvLW-hGtnRlBj11lvLSlMd1dPaPg9ewntAUEGNO0xGLNljBPOpagoz7_TB3SLAJALN5hqP8wfez8DEAQOzO3fTWEs5-UAwyhE7QLC41jTwA93F2386StQzdlNU7J5I05qJIbeDckOkQ7aLEnrjB9ST88_yQJ1a7c2YrU0ASVviVDg2bgkPJ_IJetsHkmcXUipjh-wz0Us1eUmarc7TbB-TTTlbaw11rG8-LnsEvzxiTviBZ6lVOo3RTUHpJtS3xDxWfs5YhJ_VXp-hKuYhjXbOR6mhIlsNmnd5o9q7Q1yawvAs3h7nHZPbuSleqg21rztXHVqEd0vc1iThRNdrZG7uWgB8Vhwpvhpsdtpr_qlz68n4HqDFdeDcXwafF7BOzyPcHEjhHcQZQqeZNGFLKx0DW2Xuqu87fg2z5dc7t6IZo4i3Yt9VUFZ1MG1Ea0GeOWc11wHYi7ICHa7N8MOWVi1TQCQzXiQSyH7-Kz0wPRnHPXjxepDczFfKgzTBh0R634lYemGXH-G2OLcvniS9W5IOti4s-b-oIWHyo55FAI4vVPnPnird6kqKgjb30lB5gOqndbYotQ9eLgSI5IF0BQxlablFOkVhV-5E0EqghW2zBwdbVGMnERH_ZVbDq7DIDwpHAldyLvkPMndT_f0uq-YT_S6SPOSqIx7v-C5PSAYAYSeNSjdtlI2mwuY3oS-OWFlPSeqDzdV-0V0ay1L1KD3c4WlHTufWZAQB8OG4hk4ZX0Od2uJI4zxUVsOXvA_Dzy3dUlsbX2yxtydEw2tc0LSyp3pGrYnoBc8DftX2qzXHCmDXKxcL6P0fJK47hg9tT4T7t_P8J5yGmV3FJ7MlDDhBmMPLYma6L71V8tXugsGN4oDFqi7peojVFeT-rC5YTusrbcJ-B6SD-ckRQQTu_8tTFbI4XQcfn2ooojfbH07shn0MbOeQH42mYtnrBR_FMd9WglqGsJmfExI6Z1KQaQPSgblfz2uSRq9t27g5C2g7xKXEGYLOYrMtcPSmq_4rCNlRmAWXcCtD6IT21UqOW38KpcJKP0IjvFC5aC8040MORelvuhaXtgK3vLxiykoHTYSxe5GLTvCreSrRLsCOI6mb9_p4Hn6Y0TRo3OGi9PoTZ8m5yP6j0AtaI6vaHKCEarfXROtER6mtUkIZTikLE0w7mhaISGOwNSqnZ4kM2TJ9FEH2svwrk="}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_iG0KdCz7JoKtI9OcodprnaDu", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46c7c87d284a0fda549fcd2ce", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_9qO13mReiXkguzC0Uj0cvC5b", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46c9487d284b40a1d212a5479", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_ogyvwS89SXb1yUrbrWr4U7XC", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46ca087d282694db4158bc12b", "index": 3}]
+{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_iG0KdCz7JoKtI9OcodprnaDu", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "database"}, "id": "call_9qO13mReiXkguzC0Uj0cvC5b", "type": "tool_call"}
+{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_ogyvwS89SXb1yUrbrWr4U7XC", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Tool · inspect_service</t>
+  </si>
+  <si>
+    <t>01a0d587-b866-7871-a128-d5c227c50af3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Arguments</t>
+  </si>
+  <si>
+    <t>{'section': 'traffic'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Result</t>
+  </si>
+  <si>
+    <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
+  </si>
+  <si>
+    <t>01a0d587-b866-7871-a128-d5da40190df4</t>
+  </si>
+  <si>
+    <t>{'section': 'database'}</t>
+  </si>
+  <si>
+    <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
+  </si>
+  <si>
+    <t>01a0d587-b866-7871-a128-d5e4ef0dcfc9</t>
+  </si>
+  <si>
+    <t>{'section': 'constraints'}</t>
+  </si>
+  <si>
+    <t>Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a0d587-b86d-79e0-9ed8-645ca8ae99a9</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
-  </si>
-  <si>
-    <t>Input at standard rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    System prompt</t>
-  </si>
-  <si>
-    <t>Use the fictional service evidence to propose and validate a latency improvement. Inspect traffic, database behavior, and constraints before testing the plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    User prompt</t>
-  </si>
-  <si>
-    <t>Investigate service latency and validate a plan meeting the constraints.</t>
-  </si>
-  <si>
-    <t>Cache write</t>
-  </si>
-  <si>
-    <t>Context · added / total</t>
-  </si>
-  <si>
-    <t>LLM response</t>
-  </si>
-  <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0f5f50232162cf94006ab48c0af67887d2bb051366b44ed5a8", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwLMH_SkaR3ymZharpbhRD_aKLl_Y_HDMbwHDeesHxEsQAs4pCxvcJvh-W0mctNdu4PPlcBBuMCBacU3O8laWretOD-U3USibq9M7fVZ-G-rCaQs_FtvVmznvXo4ay8nECDY8zJUqwYs-IXiZIiL75L2wUjsu3mamrOC-MnBGlqAJufRVA4upw4jR1WSWQ7WTtfTd9gfCRXbiv31Byv6AgLK3NvbproKl7ofdJdI2jLMs4syWbGdMpIqm8g2KYfQPjxZp_TucYOa6zUBfKbDxAaslRX-g-9KdR7CvNIACfsC4m49Bc4aFfCYVVrABav5ED9BaVw-pHC4qBcWu-9lyqglnISMyakzMItr4HrXYinnClcyxK9CztWRN1IEjfdv8VrdVCT9fX8xKF8Rnf2DSkeehFZ1ccNix868PJX7x6yxICCBhXMm2uwzkQYZlSV3lOhL17v0Htl4Uebl6QhNRylsrBqql8-MwYITYEirFrHuNdz2EMu5c-JuoxZNyvcnMkVbqYyhGbMKwZK1PpxdXgBbgRiAG8ZLXoGarc5nIswOtgHE743jZBE6k1hC9N8Obne-SjCRPivocWWPzZ1bKokCOf06M6a0IW_xab-cx4z8TCYoEgNxfVzGxIaS6KqjPdnppLyTiFBVX0jFalsYTg3MJyJlzcFARYoL2kb-LSpYowP-7caC6-sAvfpmv2xB6EnLnxlzhkquUpVAylmTuQrg1xePfhNq2TA2m0mghAOAM6navdux3OBSKlhKibjvdXbwrNh6Cb3K3mM_Qz1bLjv2NMgPzj4C412jgARy-M2sn7HGHiByXRdQOiQcbXDOxXXsxEZ_zidOmFjSHA3t-PuH0w6e9DYZ-l3KqC0sClWf8dR7xG3sJe4rtK6O6jV6YsBpFivBSOZZiaAkuE9W5eDEjGGJbsLn0c-t46kZJr5kHxjD9oign7I83Lw5u6AxQrCkkLnmXJnj9iPin8XAla3aqQHfIcqK438VdbIt0D3jTek2vFLQo6vayW4UpsnrGpSRlEUw4LJXjKfcRgHUURGSc0Sm9xCGXW5i9BEFvt4VhQ9LMqiGxmNvdB3bgXVlpD3YN8yDpsItpZ_vszdwJ3sKb3s4kMuNI7_yLaLy4YjuqrMMvh0WSGIMnimdC3dVucJxqT37UECmz3NJYfhQSxjliubP4IeigJzl9etsDCm7kGQF-zHFoCPeyLNR7kMj-zhKbjW9FO8kGpTqZtWoYHWkqfHX9Uc_Kw9np-VDcmy9iPNiSb1lR5ufrH7BNWa9c5j793Kzgm8b71KBZx96gNLosXqFJo1sxD209UNCLWJ0fqUPhgwGSmMh71wPLDQRG23bPmTtiqIRCkbo8rXTFx1Bc_WEzhiKVANl904o0VaRaR6ZMT5BIfLhUdJN6LIvOAz"}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_LdCImJLOwPLmHCQOIpDRORCU", "id": "fc_0f5f50232162cf94006ab48c0b963487d28c6e9e2f0b7af92f", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_I568VFsb8CIxRYCciO9yryjA", "id": "fc_0f5f50232162cf94006ab48c0b964887d2babc260d724e3fb8", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_rQraeSaQjBZIVWFRFCAnsXUO", "id": "fc_0f5f50232162cf94006ab48c0b965087d28173ad72667c35a3", "index": 3}]
-{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_LdCImJLOwPLmHCQOIpDRORCU", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "database"}, "id": "call_I568VFsb8CIxRYCciO9yryjA", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_rQraeSaQjBZIVWFRFCAnsXUO", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Tool · inspect_service</t>
-  </si>
-  <si>
-    <t>01a0d143-0e22-76c3-a765-a051b0cd1a26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Arguments</t>
-  </si>
-  <si>
-    <t>{'section': 'traffic'}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Result</t>
-  </si>
-  <si>
-    <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
-  </si>
-  <si>
-    <t>01a0d143-0e23-7700-857b-e646dc6b85ec</t>
-  </si>
-  <si>
-    <t>{'section': 'database'}</t>
-  </si>
-  <si>
-    <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
-  </si>
-  <si>
-    <t>01a0d143-0e24-7b31-9020-64c9c804d81e</t>
-  </si>
-  <si>
-    <t>{'section': 'constraints'}</t>
-  </si>
-  <si>
-    <t>Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d143-0e2c-70e1-8f36-ddc7c938fe14</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
@@ -410,16 +410,16 @@
 Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0f5f50232162cf94006ab48c0c714887d298f20be716932472", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwNy-BIVdkDz2CK4_ZxHBfVcoo6HlclZ4CtmdZlgy3vJSLm4yzT0eOwn2dYT8FFNWR4Qeh8W04_2FV4ibnreMFzYyGHaLO94w_HWCGJodoUyPk2CyrbPd40KPxAhVo3mIHlTd-Oe8I_mqE9c1H4V3CracWis1VT8ftuRbw4zoG_j3Evkql7y8nPa24umb8_iAan4WdaL7MBngoyfO-AxpeKbCJfFMz9jNQBiY1tuBFlbYiqfrj0r71vTCHN1v2om4AR6ZpBmprBlhgQ3QM2JO5KRqFGVMKtcD2X73TdFM6yFvw0uXkTQesu3PF06RVMhaUQVQOS37jVAhzTzBC8Gn2-O-PIdnaU6TXKmZq0hpv03M3cZ9L2dz-qIPIKqbWC15ZKzontfcxSba8M3piiBbks2IIVcxqTL6CSAII7Y9X8k8nNUxZwGEaxYIbu4WQGxqS-9lPol18BJuI_VTXj91_Qr0ySaWegd21BoPIig6ZWLtErExbz0QQ2cfY5bSeLK-98OV_UMwfHfWsOk1_48tDy3WIlUMWrLX9PKTFSHgM_WqBStcHy1Ivjy-P83btjHY_6u_tVfcvC7PAXofvhBA-W47A7thm44QWEqzKWAkFsTUUtiCKEpX2sCpGZfQ9HlaldsOAhYsECybPewpZFUd_dCAhnbcmI3-GMGQjSDqxQRTTV_cBKwUwIl8seovcpczs7xUIyV8klXyH8obUuvMSUDCM1RyNWlcSvLKqPbpmVmSJCsd5tsYEa8rDaS-wL5Q3ReJWi6R0ADPSetzSNnQr1HKSv52Qse8g448FZJYSjOa7Uua7qki6pe2hGryST5s3dhuDAGR2lYfgP32eZjW788zoN03aaA7MKFGnfVzdR8zsxSTYcSLrPjuV853BeMpX4Jv6e6YDB3qr0xN1d8k03LdwiqFwBIuvIspA8-vBQ9yF5r7S1N0VZ7L0BKTPCK2oHMSIqBMtteh4sHPNMDop8my0j-u8dP8Trnexp2O_N6qsmzlUSYhCT2DXDM1C-AiOQZHIqqxxDZcbIPMAn_WptTUfmKtzR-Mg21EuENnxFBLdHkVrXYUMtU7hBddKO0j5JbhsrC7cc6oV6dzWyHD9Uaa1pbExvlWql5o69F9pScETPVjOBuSPRKMTpCbkIsx9F595L96gj54UD8-Sq57qALX9mCg8T0U2NpRowV6oHpxV7DVD0U_IRcuplSTLHQQmW6gkiqwraU1d64QN60cN4pUS2BGde4871t6QGW6gucJkgNNK9tUgVyPoDO33LO1U8jemEiGa9Ap5MIlEand-gfbFEQhCkQGlGqmHeH4eVb0j5j_8pnmzDrCO14ijw1By0"}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_GuYDPVzsFwjAQytgTrE5coMh", "id": "fc_0f5f50232162cf94006ab48c0dba4087d2bc77c552fcd18f73", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_FDoVOsudmPB3oVVnxucmKH3O", "id": "fc_0f5f50232162cf94006ab48c0dba5c87d2be58a77f867478f4", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_O6uE6kt3giwNqsTGObqvanK3", "id": "fc_0f5f50232162cf94006ab48c0dba6c87d2bdabc9584034452a", "index": 3}]
-{"name": "test_plan", "args": {"check": "load"}, "id": "call_GuYDPVzsFwjAQytgTrE5coMh", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_FDoVOsudmPB3oVVnxucmKH3O", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_O6uE6kt3giwNqsTGObqvanK3", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0dcf4f209eb0e9d6006ab5a3c56bcc87d29695a2a5fe15cfcc", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaPGmZWpjQ0O1CcqqRAWiZ60TOL9U1-1LE-6WsBX7u9QN2M_TlUh4XqdwUPlSIA92YUkKZokKzVZhBPOiPvn5PkwXVZ9jmuRz4KJwopNjkvpH2q6dg7_zOxu1KpgU7jvqUFgc3Gp_YjtmJ-24mv7DIko3LmqOc3Tjph6xssLQQQqUUy28Z8KNpilIe3WEjEy-FlDp0FDtoF0gR_ddjLdUT3DkZjHjTRBPRNV8doZCXXlgcffb8DoEcJt74kZuCdG8mCa5lmoDgcy2UyQRXgd1GkriQaMaJxclQbWJVzhQKi8Dn9hFmnEMaPtyIOCwKDmF8K6ptzUkUtRv_UajCgWUVIvwMOBy3wpgf8UT-8J8fa7qwCbypk2Lu6aviJ4RTki6EeuxByB7Pga8HINL_tUVjHJp5LoiLiBn1v7BlziwC4PM1mt4fN8lgnPCZvlf7REutF5yr1R1t-Ow82qEYdNmuIhZLQ67_BP5Ze6tmRGilHmoZZakCYVbJ9DVLyj0o65AC3LCxrTUKPc25DWm9x59z3BBRVLgT4KCkeD8oODiT1fPx_itX5R9lZ2B5UcoaOhp9a_Gp9ei1kTKSPfbcyTZMcI6L3HMaHr56hVHBVO3VW6HHw49Rf5y7bXdcE9dxazRaxmN_h8H4hcfvm9GwcxL44LvhwDdxBb_mKo3H7YCBITz51cAUh1XSZVRbq4maBAXQ6LjOQaDKijofNRxLpLbgwt_CCzW917r-mUPc5_BwUmYcWBSlYwIh_RW_zDdpht7vR7pqgFX88GbYLPEYTxzt7GSSnd_DMVreYICUKSE65BWLUc0syZb_DF9Sz7-hTwZKpYvPK8ucWwi-PlGZiA4M3q0atoweSzFJtAQm5MFUzV1Z-0F4pUZMv10M4xy5b-LV3_YM1tgc_WwpxcmPTM2ioi-VTTEHzDOGst-0RUJio9OecDw4SAtJW4jAgn_HkyAvxj-K6CFOWstcn-CfR9UlkmHz2Ri6DVIoyPF8_nA-YqYKgE3KCJJtv7bAKJP-86zq7vCWIIzU_XBSg6_NdFqsfa4d54NT5jxNzh95_yUvGVEkjaZINpgKo0arGiQLVkMa_-mCEB_Bv-nTZBWHUdqgVIINVe1B82noIMFs_1FFqJrtxwXggwYePshvgz1EUfKypU2SUuVzx8mTjVHyRJtkW4TsuPTMH9ux-5pYOwm8WTzlKrAfFqrZpuNpJOZAjtZgkgNzRs638F4AejKHs3uyU6dnaRvS5KT-vPveC59HAVeEOwg_5GaKAgpj0nAZ7_acsmNNrrI43YGyt-hk8_L2HafsZb-YuwmIl-7Jm4LWy5QZ1FYWt0AngTT0d1RqFwfTx4nvMUP-1iPTYYebTnDIuwsJZnLCU4iL1-4W2evky6S8FOUTAVwcLMvftRM4LRixGA8uzY1pNK6rHDv9iBzUqD69DKIbxIsjgoirK7BxDRi-tJYnsN94VVMLp-wvJSyzb-1m5HgsNzUmxjmkAg0Nd5CA=="}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_8B4ENaYezGivImb0tXxJl4zO", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d0887d292d41560302fe6ff", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_jfOQjRwf2fifrW61g61qMSxF", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d1887d2892ea9971e27ec17", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_VOcNhmRnXa2Y9jVrz3iUB1r5", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d2087d284661f6d97db3d86", "index": 3}]
+{"name": "test_plan", "args": {"check": "load"}, "id": "call_8B4ENaYezGivImb0tXxJl4zO", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_jfOQjRwf2fifrW61g61qMSxF", "type": "tool_call"}
+{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_VOcNhmRnXa2Y9jVrz3iUB1r5", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · test_plan</t>
   </si>
   <si>
-    <t>01a0d143-16fb-70b0-8904-5d3f80cad912</t>
+    <t>01a0d587-bfca-7b60-800f-5f032a343158</t>
   </si>
   <si>
     <t>{'check': 'load'}</t>
@@ -428,7 +428,7 @@
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.</t>
   </si>
   <si>
-    <t>01a0d143-16fb-70b0-8904-5d4acefdfeaf</t>
+    <t>01a0d587-bfcb-7493-86c8-066077c37678</t>
   </si>
   <si>
     <t>{'check': 'freshness'}</t>
@@ -437,7 +437,7 @@
     <t>PASS: account changes invalidate cached values; maximum fallback age is 30s.</t>
   </si>
   <si>
-    <t>01a0d143-16fc-78e1-946c-8c3a79b0aa9f</t>
+    <t>01a0d587-bfcb-7493-86c8-06709a8fb298</t>
   </si>
   <si>
     <t>{'check': 'rollback'}</t>
@@ -449,7 +449,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0d143-170b-7dc3-b425-7a26dcb11ef8</t>
+    <t>01a0d587-bfd6-72e2-be75-3da1f2efa6eb</t>
   </si>
   <si>
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.
@@ -457,7 +457,7 @@
 PASS: feature flag restores original lookup path; no schema migration required.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0f5f50232162cf94006ab48c0efaac87d28f0f4da572b3b767", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIwPalmAL5JJatDhVidJRa_O0ewgYd-Q5EckSLx8GTVw37G3uUyp9XuN6nUay4POxBamY0tb_tWW4VDpVY_7i4zqsP_ORy0VveQsjXOmuUWzRefnMKF1QyAliyzRn6tQPYNWIf30ZqPaGjzLE1ce6EGU7Qa_PWQ_F_pfdApgI5TZGdEFsyhBytynQRFzRjxW8WvU9Wc-xwmoBV08Wz7tediaON20DHIJIPiF2Iad9D_AHhcw1eFTLB9uwTYLja5HX0tv8T5V8cz2z3qUDb2c0aWnExPcsT0KuN8eBldz2eWVrHDSGS4_a3SLcSNvQLKCPBTvadg6UeV1bpmm7VxwDZZhca9Kif7OSTNZJDh-F2gyB3RS49HQ4_stHjcLjko8qHwlyGRIvww0kDEByehiN2faVyLHYyelcxAdiSRqRdKgxjpFxuJLjGMQ9piE2J0b10faiwT-ok-KFvBVYgtTVCKdEDStmQrE56StvWbCs4to4P4GHhbJClZW-f2QTneyf-HorjK09bjwtl9jOaXoAIPwuqfT9pXUVwQecSNJMshJ154kRtC8ctX8K3k1Fxo4ogYhMs5BRk2WV7ow7sr1rlXxBSaQXNBb4YL4ARwsOFWGBP0GvdtJckS3Vb6vkslGpQ35eC4L41vZN9k_6BAFqp94xDHoQeegSiuJ-VtAwBgmTmza29NyaA9q6gtAkepzOBj2M4S8ReGLCNhgxxjKKRrD1Naqg35-G6s3UxzHNE6nJWJqC-WN-rX09HtoYdM6-_ZJYDCxdnOBILS-0PZf-rv7ueZAbSNgf1tnEmre5ckcppzs4KdtMQrw5PFH4dCZbOqfkQ931eRs_yBs0Q3tkYiGpa_GjRjFVv4o3sui98SaYqTF67K-VRVHw0_PO0gJLkWTBVmTB1koBYlAfpCxi1hzis3Ojs0zjXjr9N9sIe8SsNnR2PVn9y5feMOk8emyB4TTES-fBZkW9aiFtiVur1IIXX4gPd2BK9H-vUpsIa20MRyITIK_5G9fSGh1fyhklmPWwZfMsR65QRhUMBRm8kpGnXHwMf6ts4N3hZbUaEikyK9B_CteLAI78eknbUmDkhrqJZkqICj_iA2654nDEFVVoOgja0F0FfeE50yt9_XZjqGY2D0DFAxMW4vO2iVqOL9uzXynflqOAEmOrecvXcVKdo1YCqpEU_sdqHFQLyH-FabveBIfTrToBhhYWNWLQva_dZ961IVIG7gxEwC3XFrHY_bq3kiJKnl6t2smR9_9MscxvSUDvAOvpilKR7I_Y1RQS_TNvJfCTUUKoOoj2chLG6WnLQQ-Q1JDFRnKtZd5U0NBgjVOB80V0glEtL_66Jj45693jhWvFK7T25Dtl6QcQpRVRcTQfFsz-sPDOUfTPIktgRstJCPZofqdUF3W09bcUuUmQ210GzUJrGfw9qbYW72i6gAcT6J1fU4IDGK4PqfwV1sixOXFc1_56DhkJXac"}, {"type": "text", "text": "## Findings\n\n- **Traffic:** Peak **240 requests/s**, with **p95 latency of 1.8 s**. Latency increases during database bursts.\n- **Database:** Query median is **80 ms**, but p95 reaches **900 ms**. Each request performs duplicate account lookups.\n- **Capacity:** The connection pool is limited to **12**, so duplicate queries amplify contention.\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so the same account is fetched once.\n2. Add a **per-account cache with a 30-second TTL**.\n3. **Invalidate cached entries when account data changes** rather than waiting for expiry.\n4. Roll out behind a **feature flag**, preserving the existing lookup path for rollback.\n\nThis requires no additional database nodes or schema migration.\n\n## Validation\n\nThe plan check passed:\n\n- At **240 requests/s**, deduplication plus the 30-second cache achieved **410 ms p95 latency**.\n- Pool occupancy fell to **65%**.\n- Cache freshness is bounded: updates invalidate entries, and fallback data is never older than **30 seconds**.\n- The feature flag restores the original lookup path if problems occur.\n\nThe plan meets the target of **p95 under 500 ms**, stays within the **60-second cache lifetime constraint**, and has a reversible rollout.", "phase": "final_answer", "index": 1, "id": "msg_0f5f50232162cf94006ab48c0ff95487d29fc9b5b84bf25aae"}]</t>
+    <t>[{"type": "text", "text": "## Findings\n\n- Traffic peaks at **240 requests/s** with current p95 latency of **1.8 s**.\n- Latency increases during database bursts.\n- The database connection pool is capped at **12** connections.\n- Queries have an **80 ms median** but **900 ms p95** latency.\n- Requests perform duplicate account lookups.\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so repeated references share one in-flight query.\n2. Add a short-lived account cache with a **30-second TTL**.\n3. Invalidate cached account data when account changes occur.\n4. Gate the change behind a feature flag so the existing lookup path can be restored immediately.\n5. Avoid adding database nodes or requiring schema changes.\n\n## Validation\n\n- **Load:** Passed. At 240 requests/s, deduplication plus the 30-second cache produces **410 ms p95 latency**, below the **500 ms target**. Pool occupancy is approximately **65%**.\n- **Freshness:** Passed. Account updates invalidate cached values, and fallback data cannot exceed **30 seconds** old.\n- **Rollback:** Passed. Disabling the feature flag restores the original lookup path, with no schema migration required.\n\nThis plan satisfies all stated constraints and is expected to reduce database burst pressure while meeting the latency target.", "phase": "final_answer", "index": 0, "id": "msg_0dcf4f209eb0e9d6006ab5a3c738f887d2be89b229b6b4b473"}]</t>
   </si>
   <si>
     <t>investigation_agent</t>
@@ -478,7 +478,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0d143-04cf-7273-8789-195635b8e332</t>
+    <t>01a0d587-b04f-7b73-8ae4-d187b3b1b04f</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -490,7 +490,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d143-04d0-7793-92a8-9b3f8d03e42d</t>
+    <t>01a0d587-b050-7ae0-b2c7-51aa65f4e355</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -511,7 +511,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d143-0e20-71a2-ae50-be97fc78337e</t>
+    <t>01a0d587-b863-7430-a472-54ef91260ade</t>
   </si>
   <si>
     <t xml:space="preserve">        inspect_service</t>
@@ -523,16 +523,16 @@
     <t>Read fictional service evidence; no live service is inspected.</t>
   </si>
   <si>
-    <t>01a0d143-0e20-71a2-ae50-bea24b080c00</t>
-  </si>
-  <si>
-    <t>01a0d143-0e20-71a2-ae50-bebd9abe0314</t>
-  </si>
-  <si>
-    <t>01a0d143-0e29-7f91-b83b-4cd56b84abd6</t>
-  </si>
-  <si>
-    <t>01a0d143-16f7-72a3-8630-755408a9036e</t>
+    <t>01a0d587-b863-7430-a472-54f1eab3357e</t>
+  </si>
+  <si>
+    <t>01a0d587-b863-7430-a472-5501eabdde94</t>
+  </si>
+  <si>
+    <t>01a0d587-b86a-77a1-9f8f-0b849486b6ce</t>
+  </si>
+  <si>
+    <t>01a0d587-bfc8-7a62-a7b1-cf0029a244ee</t>
   </si>
   <si>
     <t xml:space="preserve">        test_plan</t>
@@ -541,13 +541,13 @@
     <t>Return a fixed fictional plan-check result; no real test is executed.</t>
   </si>
   <si>
-    <t>01a0d143-16f7-72a3-8630-7569611e9968</t>
-  </si>
-  <si>
-    <t>01a0d143-16f7-72a3-8630-757d9b91667f</t>
-  </si>
-  <si>
-    <t>01a0d143-1706-7b00-a671-00ef4e5c4926</t>
+    <t>01a0d587-bfc8-7a62-a7b1-cf11aabfeeb3</t>
+  </si>
+  <si>
+    <t>01a0d587-bfc8-7a62-a7b1-cf21e87619f1</t>
+  </si>
+  <si>
+    <t>01a0d587-bfd2-7dd1-be10-fa39c04ad4ca</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1014,20 +1014,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
-        <v>0.0007385614895</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
+        <v>0.0011438731376</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
-        <v>0.00084277</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
+        <v>0.00130024</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>114.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>84.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1038,20 +1038,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
-        <v>0.0007385614895</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
+        <v>0.0011438731376</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
-        <v>0.00084277</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
+        <v>0.00130024</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>114.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>84.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1085,23 +1085,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>2099</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6789173e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.198e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1114,27 +1114,8 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1144,8 +1125,11 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="34" customHeight="1">
+      <c r="I7" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1153,10 +1137,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1167,10 +1151,26 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2099</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000461643565</v>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>0.00052475</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>46.0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>52.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1184,29 +1184,48 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="4">
         <v>93</v>
       </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="4">
-        <v>98</v>
+      <c r="D12" s="5">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.0614952e-05</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>3.48e-05</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1220,26 +1239,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.575508e-05</v>
+        <v>6.7564032e-05</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>4.08e-05</v>
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.68e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="409" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1249,27 +1268,11 @@
       <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="5">
-        <v>64</v>
-      </c>
-      <c r="E14" s="2">
-        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.730368e-05</v>
-      </c>
-      <c r="F14" s="2">
-        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.68e-05</v>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H14" s="5">
-        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="409" customHeight="1">
+      <c r="I14" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1277,10 +1280,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
@@ -1294,59 +1294,59 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="24" customHeight="1">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
+        <v>0.000560350393</v>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
+        <v>0.00063695</v>
+      </c>
+      <c r="G17" s="5">
+        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>56.0</v>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>64.0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
-        <v>0.000140373743</v>
-      </c>
-      <c r="F18" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
-        <v>0.00016018</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-      <c r="H18" s="5">
-        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B19" s="4">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="M18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" s="4" t="s">
+    </row>
+    <row r="19" spans="1:13" ht="24" customHeight="1">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>114</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="24" customHeight="1">
@@ -1354,118 +1354,137 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="24" customHeight="1">
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="34" customHeight="1">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="24" customHeight="1">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="24" customHeight="1">
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="34" customHeight="1">
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>117</v>
-      </c>
-      <c r="I24" s="6" t="s">
+    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B24" s="4">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B25" s="4">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M25" s="4" t="s">
+    <row r="25" spans="1:13" ht="24" customHeight="1">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
+    <row r="26" spans="1:13" ht="34" customHeight="1">
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="34" customHeight="1">
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="I27" s="6" t="s">
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A27" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A28" s="4" t="s">
+      <c r="B27" s="4">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2296</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M27" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2301</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M28" s="4" t="s">
+    </row>
+    <row r="28" spans="1:13" ht="24" customHeight="1">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>126</v>
+      </c>
+      <c r="D28" s="5">
+        <v>2099</v>
+      </c>
+      <c r="E28" s="2">
+        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.69314852e-05</v>
+      </c>
+      <c r="F28" s="2">
+        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!C17),D28*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.198e-05</v>
+      </c>
+      <c r="G28" s="5">
+        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1474,72 +1493,72 @@
         <v>97</v>
       </c>
       <c r="D29" s="5">
-        <v>2099</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2">
         <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6789173e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!C17),D29*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.198e-05</v>
+        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!B17),D29*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="73" customHeight="1">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="24" customHeight="1">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="5">
+        <v>194</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.266739e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!D17),D31*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.85e-05</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
         <v>4.0</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="24" customHeight="1">
-      <c r="A30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" s="5">
-        <v>3</v>
-      </c>
-      <c r="E30" s="2">
-        <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F30" s="2">
-        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!B17),D30*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G30" s="5">
-        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="5">
-        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="73" customHeight="1">
-      <c r="A31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>128</v>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1547,54 +1566,54 @@
       <c r="C32" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="5">
-        <v>199</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(AND(ISNUMBER(F32),ISNUMBER('Reference data'!$B$3)),F32*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.35984125e-05</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(D32=0,0,IF(ISNUMBER('Reference data'!D17),D32*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.975e-05</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="24" customHeight="1">
-      <c r="A33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="D33" s="4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="4">
-        <v>90</v>
+      <c r="D34" s="5">
+        <v>54</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.7007152e-05</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!F17),D34*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>6.48e-05</v>
+      </c>
+      <c r="G34" s="5">
+        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H34" s="5">
+        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1603,28 +1622,28 @@
         <v>107</v>
       </c>
       <c r="D35" s="5">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E35" s="2">
         <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.62905e-05</v>
+        <v>6.861972e-05</v>
       </c>
       <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!F17),D35*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3e-05</v>
+        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!E17),D35*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.8e-05</v>
       </c>
       <c r="G35" s="5">
         <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H35" s="5">
         <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="24" customHeight="1">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="409" customHeight="1">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1632,43 +1651,24 @@
       <c r="C36" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="5">
-        <v>65</v>
-      </c>
-      <c r="E36" s="2">
-        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.83553e-05</v>
-      </c>
-      <c r="F36" s="2">
-        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!E17),D36*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.8e-05</v>
-      </c>
-      <c r="G36" s="5">
-        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H36" s="5">
-        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="409" customHeight="1">
+      <c r="I36" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="24" customHeight="1">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="24" customHeight="1">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1677,95 +1677,95 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="24" customHeight="1">
-      <c r="A39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
+    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="2">
+        <f>IF(COUNT('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35)=5,SUM('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35),"Unknown")</f>
+        <v>0.0002057535912</v>
+      </c>
+      <c r="F39" s="2">
+        <f>IF(COUNT('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35)=5,SUM('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35),"Unknown")</f>
+        <v>0.00023388</v>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>21.0</v>
+      </c>
+      <c r="H39" s="5">
+        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="B40" s="4">
         <v>1</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="2">
-        <f>IF(COUNT('Turns'!E29,'Turns'!E30,'Turns'!E32,'Turns'!E35,'Turns'!E36)=5,SUM('Turns'!E29,'Turns'!E30,'Turns'!E32,'Turns'!E35,'Turns'!E36),"Unknown")</f>
-        <v>0.0001755591955</v>
-      </c>
-      <c r="F40" s="2">
-        <f>IF(COUNT('Turns'!F29,'Turns'!F30,'Turns'!F32,'Turns'!F35,'Turns'!F36)=5,SUM('Turns'!F29,'Turns'!F30,'Turns'!F32,'Turns'!F35,'Turns'!F36),"Unknown")</f>
-        <v>0.00020033</v>
-      </c>
-      <c r="G40" s="5">
-        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="H40" s="5">
-        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B41" s="4">
-        <v>1</v>
-      </c>
-      <c r="C41" s="4" t="s">
+      <c r="M40" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="24" customHeight="1">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="34" customHeight="1">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K41" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="24" customHeight="1">
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="34" customHeight="1">
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>117</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B44" s="4">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M44" s="4" t="s">
+      <c r="K43" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1">
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
@@ -1773,35 +1773,35 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="24" customHeight="1">
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I46" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B47" s="4">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4" t="s">
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="K47" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M47" s="4" t="s">
+      <c r="K46" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M46" s="4" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24" customHeight="1">
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
@@ -1809,41 +1809,60 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="24" customHeight="1">
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="I49" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A50" s="4" t="s">
+    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A49" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B49" s="4">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="4">
-        <v>2479</v>
-      </c>
-      <c r="J50" s="4" t="s">
+      <c r="D49" s="4">
+        <v>2503</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="M49" s="4" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="24" customHeight="1">
+      <c r="A50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="5">
+        <v>2293</v>
+      </c>
+      <c r="E50" s="2">
+        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.03448764e-05</v>
+      </c>
+      <c r="F50" s="2">
+        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.586e-05</v>
+      </c>
+      <c r="G50" s="5">
+        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="5">
+        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="24" customHeight="1">
@@ -1857,26 +1876,26 @@
         <v>97</v>
       </c>
       <c r="D51" s="5">
-        <v>2298</v>
+        <v>3</v>
       </c>
       <c r="E51" s="2">
         <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.0277046e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.596e-05</v>
+        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!B17),D51*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G51" s="5">
         <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" s="5">
         <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="60" customHeight="1">
       <c r="A52" t="s">
         <v>140</v>
       </c>
@@ -1884,29 +1903,13 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" s="5">
-        <v>3</v>
-      </c>
-      <c r="E52" s="2">
-        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G52" s="5">
-        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H52" s="5">
-        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="60" customHeight="1">
+        <v>127</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="24" customHeight="1">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -1914,10 +1917,26 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>142</v>
+        <v>103</v>
+      </c>
+      <c r="D53" s="5">
+        <v>207</v>
+      </c>
+      <c r="E53" s="2">
+        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.5526545e-05</v>
+      </c>
+      <c r="F53" s="2">
+        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>5.175e-05</v>
+      </c>
+      <c r="G53" s="5">
+        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H53" s="5">
+        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="24" customHeight="1">
@@ -1930,52 +1949,52 @@
       <c r="C54" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="5">
-        <v>178</v>
-      </c>
-      <c r="E54" s="2">
-        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.8997575e-05</v>
-      </c>
-      <c r="F54" s="2">
-        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.45e-05</v>
-      </c>
-      <c r="G54" s="5">
-        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H54" s="5">
-        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="24" customHeight="1">
-      <c r="A55" t="s">
+    </row>
+    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A55" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" s="4">
+        <v>1</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A56" s="4" t="s">
+      <c r="D55" s="4">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="24" customHeight="1">
+      <c r="A56" t="s">
         <v>140</v>
       </c>
-      <c r="B56" s="4">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" s="4">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="24" customHeight="1">
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="5">
+        <v>276</v>
+      </c>
+      <c r="E56" s="2">
+        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000291369888</v>
+      </c>
+      <c r="F56" s="2">
+        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!E17),D56*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0003312</v>
+      </c>
+      <c r="G56" s="5">
+        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>29.0</v>
+      </c>
+      <c r="H56" s="5">
+        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="229" customHeight="1">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -1983,26 +2002,10 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" s="5">
-        <v>46</v>
-      </c>
-      <c r="E57" s="2">
-        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.837452e-05</v>
-      </c>
-      <c r="F57" s="2">
-        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!F17),D57*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>5.52e-05</v>
-      </c>
-      <c r="G57" s="5">
-        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H57" s="5">
-        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>108</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="24" customHeight="1">
@@ -2013,29 +2016,10 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="5">
-        <v>280</v>
-      </c>
-      <c r="E58" s="2">
-        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0002944536</v>
-      </c>
-      <c r="F58" s="2">
-        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000336</v>
-      </c>
-      <c r="G58" s="5">
-        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="H58" s="5">
-        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>34.0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="409" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="24" customHeight="1">
       <c r="A59" t="s">
         <v>140</v>
       </c>
@@ -2043,66 +2027,41 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="24" customHeight="1">
-      <c r="A60" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A60" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="24" customHeight="1">
-      <c r="A61" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A62" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="s">
+      <c r="B60" s="4">
+        <v>1</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" s="2">
+        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56)=4,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56),"Unknown")</f>
+        <v>0.0003777691534</v>
+      </c>
+      <c r="F60" s="2">
+        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56)=4,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56),"Unknown")</f>
+        <v>0.00042941</v>
+      </c>
+      <c r="G60" s="5">
+        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>38.0</v>
+      </c>
+      <c r="H60" s="5">
+        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>43.0</v>
+      </c>
+      <c r="K60" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E62" s="2">
-        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57,'Turns'!E58)=5,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57,'Turns'!E58),"Unknown")</f>
-        <v>0.000422628551</v>
-      </c>
-      <c r="F62" s="2">
-        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57,'Turns'!F58)=5,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57,'Turns'!F58),"Unknown")</f>
-        <v>0.00048226</v>
-      </c>
-      <c r="G62" s="5">
-        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
-      </c>
-      <c r="H62" s="5">
-        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>112</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE62">
+  <conditionalFormatting sqref="A2:AE60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2235,7 +2194,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>146</v>
@@ -2244,83 +2203,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D30,'Turns'!D52)=3,SUM('Turns'!D6,'Turns'!D30,'Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D29,'Turns'!D51)=3,SUM('Turns'!D5,'Turns'!D29,'Turns'!D51),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E30,'Turns'!E52)=3,SUM('Turns'!E6,'Turns'!E30,'Turns'!E52),"Unknown")</f>
-        <v>1.57743e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E29,'Turns'!E51)=3,SUM('Turns'!E5,'Turns'!E29,'Turns'!E51),"Unknown")</f>
+        <v>1.583532e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F30,'Turns'!F52)=3,SUM('Turns'!F6,'Turns'!F30,'Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F29,'Turns'!F51)=3,SUM('Turns'!F5,'Turns'!F29,'Turns'!F51),"Unknown")</f>
         <v>1.8e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D29,'Turns'!D51)=3,SUM('Turns'!D5,'Turns'!D29,'Turns'!D51),"Unknown")</f>
-        <v>6496.0</v>
+        <f>IF(COUNT('Turns'!D28,'Turns'!D50)=2,SUM('Turns'!D28,'Turns'!D50),"Unknown")</f>
+        <v>4392.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E29,'Turns'!E51)=3,SUM('Turns'!E5,'Turns'!E29,'Turns'!E51),"Unknown")</f>
-        <v>0.000113855392</v>
+        <f>IF(COUNT('Turns'!E28,'Turns'!E50)=2,SUM('Turns'!E28,'Turns'!E50),"Unknown")</f>
+        <v>7.72763616e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F29,'Turns'!F51)=3,SUM('Turns'!F5,'Turns'!F29,'Turns'!F51),"Unknown")</f>
-        <v>0.00012992</v>
+        <f>IF(COUNT('Turns'!F28,'Turns'!F50)=2,SUM('Turns'!F28,'Turns'!F50),"Unknown")</f>
+        <v>8.784e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D32,'Turns'!D54)=2,SUM('Turns'!D32,'Turns'!D54),"Unknown")</f>
-        <v>377.0</v>
+        <f>IF(COUNT('Turns'!D9,'Turns'!D31,'Turns'!D53)=3,SUM('Turns'!D9,'Turns'!D31,'Turns'!D53),"Unknown")</f>
+        <v>2500.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E32,'Turns'!E54)=2,SUM('Turns'!E32,'Turns'!E54),"Unknown")</f>
-        <v>8.25959875e-05</v>
+        <f>IF(COUNT('Turns'!E9,'Turns'!E31,'Turns'!E53)=3,SUM('Turns'!E9,'Turns'!E31,'Turns'!E53),"Unknown")</f>
+        <v>0.0005498375</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F32,'Turns'!F54)=2,SUM('Turns'!F32,'Turns'!F54),"Unknown")</f>
-        <v>9.425e-05</v>
+        <f>IF(COUNT('Turns'!F9,'Turns'!F31,'Turns'!F53)=3,SUM('Turns'!F9,'Turns'!F31,'Turns'!F53),"Unknown")</f>
+        <v>0.000625</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D14,'Turns'!D36,'Turns'!D58)=3,SUM('Turns'!D14,'Turns'!D36,'Turns'!D58),"Unknown")</f>
-        <v>409.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D56)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D56),"Unknown")</f>
+        <v>405.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E14,'Turns'!E36,'Turns'!E58)=3,SUM('Turns'!E14,'Turns'!E36,'Turns'!E58),"Unknown")</f>
-        <v>0.00043011258</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E56)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E56),"Unknown")</f>
+        <v>0.00042755364</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F14,'Turns'!F36,'Turns'!F58)=3,SUM('Turns'!F14,'Turns'!F36,'Turns'!F58),"Unknown")</f>
-        <v>0.0004908</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F56)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F56),"Unknown")</f>
+        <v>0.000486</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D57)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D57),"Unknown")</f>
-        <v>105.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D34)=2,SUM('Turns'!D12,'Turns'!D34),"Unknown")</f>
+        <v>83.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E57)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E57),"Unknown")</f>
-        <v>0.0001104201</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E34)=2,SUM('Turns'!E12,'Turns'!E34),"Unknown")</f>
+        <v>8.7622104e-05</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F57)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F57),"Unknown")</f>
-        <v>0.000126</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F34)=2,SUM('Turns'!F12,'Turns'!F34),"Unknown")</f>
+        <v>9.96e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E40,'Turns'!E62)=3,SUM('Turns'!E18,'Turns'!E40,'Turns'!E62),"Unknown")</f>
-        <v>0.0007385614895</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
+        <v>0.0011438731376</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F40,'Turns'!F62)=3,SUM('Turns'!F18,'Turns'!F40,'Turns'!F62),"Unknown")</f>
-        <v>0.00084277</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
+        <v>0.00130024</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>114.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>84.0</v>
+        <v>130.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>8530.688</v>
+        <v>7627.606</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>147</v>
@@ -2340,7 +2299,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>149</v>
@@ -2352,7 +2311,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.426</v>
+        <v>0.322</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>151</v>
@@ -2372,7 +2331,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>153</v>
@@ -2384,80 +2343,80 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2099.0</v>
       </c>
-      <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.6789173e-05</v>
-      </c>
-      <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.198e-05</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000461643565</v>
       </c>
       <c r="R4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00052475</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>64.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>6.730368e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>6.7564032e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>7.68e-05</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>34.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>29.0</v>
       </c>
       <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.575508e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>3.0614952e-05</v>
       </c>
       <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>4.08e-05</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>3.48e-05</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.000140373743</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000560350393</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00016018</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00063695</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>56.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>64.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2382.967</v>
+        <v>2064.382</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>147</v>
@@ -2477,7 +2436,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1">
         <v>2102</v>
@@ -2492,83 +2451,83 @@
         <v>154</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2099.0</v>
       </c>
-      <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.6789173e-05</v>
-      </c>
-      <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.198e-05</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
       <c r="Q5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000461643565</v>
       </c>
       <c r="R5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00052475</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>64.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>6.730368e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>6.7564032e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>7.68e-05</v>
       </c>
       <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>34.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>29.0</v>
       </c>
       <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.575508e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>3.0614952e-05</v>
       </c>
       <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>4.08e-05</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>3.48e-05</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.000140373743</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000560350393</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00016018</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00063695</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>56.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>64.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2375.866</v>
+        <v>2056.78</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>158</v>
@@ -2588,7 +2547,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>160</v>
@@ -2600,7 +2559,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>6.799</v>
+        <v>5.491</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>151</v>
@@ -2620,19 +2579,19 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I7" t="s">
         <v>161</v>
       </c>
       <c r="AD7" s="1">
-        <v>2.474</v>
+        <v>1.293</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>151</v>
@@ -2652,7 +2611,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>160</v>
@@ -2664,7 +2623,7 @@
         <v>49</v>
       </c>
       <c r="AD8" s="1">
-        <v>6.945</v>
+        <v>5.499</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>151</v>
@@ -2684,19 +2643,19 @@
         <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
         <v>165</v>
       </c>
       <c r="AD9" s="1">
-        <v>2.015</v>
+        <v>0.756</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>151</v>
@@ -2716,7 +2675,7 @@
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>160</v>
@@ -2728,7 +2687,7 @@
         <v>49</v>
       </c>
       <c r="AD10" s="1">
-        <v>6.075</v>
+        <v>5.763</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>151</v>
@@ -2748,19 +2707,19 @@
         <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>164</v>
       </c>
       <c r="H11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I11" t="s">
         <v>166</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.915</v>
+        <v>1.347</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>151</v>
@@ -2780,7 +2739,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>153</v>
@@ -2792,83 +2751,83 @@
         <v>49</v>
       </c>
       <c r="J12" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K12" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L12" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>2099.0</v>
       </c>
       <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>3.6789173e-05</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>3.69314852e-05</v>
       </c>
       <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>4.198e-05</v>
       </c>
       <c r="P12" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>199.0</v>
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>194.0</v>
       </c>
       <c r="Q12" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>4.35984125e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>4.266739e-05</v>
       </c>
       <c r="R12" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>4.975e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>4.85e-05</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
         <v>65.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>6.83553e-05</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>6.861972e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
         <v>7.8e-05</v>
       </c>
       <c r="V12" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>54.0</v>
       </c>
       <c r="W12" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>2.62905e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>5.7007152e-05</v>
       </c>
       <c r="X12" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>6.48e-05</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>0.0001755591955</v>
+        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <v>0.0002057535912</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>0.00020033</v>
+        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <v>0.00023388</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2251.859</v>
+        <v>1884.096</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>147</v>
@@ -2888,101 +2847,101 @@
         <v>95</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F13" s="1">
-        <v>2301</v>
+        <v>2296</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>157</v>
       </c>
       <c r="H13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I13" t="s">
         <v>167</v>
       </c>
       <c r="J13" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K13" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L13" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>2099.0</v>
       </c>
       <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>3.6789173e-05</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>3.69314852e-05</v>
       </c>
       <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>4.198e-05</v>
       </c>
       <c r="P13" s="2">
-        <f>IF(COUNT('Turns'!D32)=1,SUM('Turns'!D32),"Unknown")</f>
-        <v>199.0</v>
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
+        <v>194.0</v>
       </c>
       <c r="Q13" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>4.35984125e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>4.266739e-05</v>
       </c>
       <c r="R13" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>4.975e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>4.85e-05</v>
       </c>
       <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
         <v>65.0</v>
       </c>
       <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>6.83553e-05</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>6.861972e-05</v>
       </c>
       <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
         <v>7.8e-05</v>
       </c>
       <c r="V13" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
+        <v>54.0</v>
       </c>
       <c r="W13" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>2.62905e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>5.7007152e-05</v>
       </c>
       <c r="X13" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>6.48e-05</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>0.0001755591955</v>
+        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <v>0.0002057535912</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>0.00020033</v>
+        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <v>0.00023388</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AD13" s="1">
-        <v>2246.332</v>
+        <v>1878.87</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>158</v>
@@ -3002,7 +2961,7 @@
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>160</v>
@@ -3014,7 +2973,7 @@
         <v>49</v>
       </c>
       <c r="AD14" s="1">
-        <v>11.576</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>151</v>
@@ -3034,7 +2993,7 @@
         <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>170</v>
@@ -3046,7 +3005,7 @@
         <v>168</v>
       </c>
       <c r="AD15" s="1">
-        <v>3.618</v>
+        <v>3.649</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>151</v>
@@ -3066,7 +3025,7 @@
         <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>160</v>
@@ -3078,7 +3037,7 @@
         <v>49</v>
       </c>
       <c r="AD16" s="1">
-        <v>11.756</v>
+        <v>8.26</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>151</v>
@@ -3098,7 +3057,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>170</v>
@@ -3110,7 +3069,7 @@
         <v>171</v>
       </c>
       <c r="AD17" s="1">
-        <v>3.837</v>
+        <v>1.781</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>151</v>
@@ -3130,7 +3089,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>160</v>
@@ -3142,7 +3101,7 @@
         <v>49</v>
       </c>
       <c r="AD18" s="1">
-        <v>12.31</v>
+        <v>7.58</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>151</v>
@@ -3162,7 +3121,7 @@
         <v>47</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>170</v>
@@ -3174,7 +3133,7 @@
         <v>172</v>
       </c>
       <c r="AD19" s="1">
-        <v>4.515</v>
+        <v>2.078</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>151</v>
@@ -3194,7 +3153,7 @@
         <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>153</v>
@@ -3206,83 +3165,80 @@
         <v>49</v>
       </c>
       <c r="J20" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K20" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L20" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M20" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2298.0</v>
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>2293.0</v>
       </c>
       <c r="N20" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>4.0277046e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>4.03448764e-05</v>
       </c>
       <c r="O20" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>4.596e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>4.586e-05</v>
       </c>
       <c r="P20" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>178.0</v>
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <v>207.0</v>
       </c>
       <c r="Q20" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>3.8997575e-05</v>
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
+        <v>4.5526545e-05</v>
       </c>
       <c r="R20" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>4.45e-05</v>
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <v>5.175e-05</v>
       </c>
       <c r="S20" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>280.0</v>
+        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
+        <v>276.0</v>
       </c>
       <c r="T20" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>0.0002944536</v>
+        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
+        <v>0.000291369888</v>
       </c>
       <c r="U20" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>0.000336</v>
+        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
+        <v>0.0003312</v>
       </c>
       <c r="V20" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>46.0</v>
+        <v>0</v>
       </c>
       <c r="W20" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>4.837452e-05</v>
+        <v>0</v>
       </c>
       <c r="X20" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>5.52e-05</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.000422628551</v>
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>0.0003777691534</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00048226</v>
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>0.00042941</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>43.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>3864.516</v>
+        <v>3654.439</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>147</v>
@@ -3302,10 +3258,10 @@
         <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F21" s="1">
-        <v>2479</v>
+        <v>2503</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>157</v>
@@ -3317,86 +3273,83 @@
         <v>173</v>
       </c>
       <c r="J21" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K21" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L21" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2298.0</v>
+        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <v>2293.0</v>
       </c>
       <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>4.0277046e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>4.03448764e-05</v>
       </c>
       <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>4.596e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>4.586e-05</v>
       </c>
       <c r="P21" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>178.0</v>
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <v>207.0</v>
       </c>
       <c r="Q21" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>3.8997575e-05</v>
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
+        <v>4.5526545e-05</v>
       </c>
       <c r="R21" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>4.45e-05</v>
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <v>5.175e-05</v>
       </c>
       <c r="S21" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>280.0</v>
+        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
+        <v>276.0</v>
       </c>
       <c r="T21" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>0.0002944536</v>
+        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
+        <v>0.000291369888</v>
       </c>
       <c r="U21" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>0.000336</v>
+        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
+        <v>0.0003312</v>
       </c>
       <c r="V21" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>46.0</v>
+        <v>0</v>
       </c>
       <c r="W21" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>4.837452e-05</v>
+        <v>0</v>
       </c>
       <c r="X21" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>5.52e-05</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.000422628551</v>
+        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
+        <v>0.0003777691534</v>
       </c>
       <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00048226</v>
+        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
+        <v>0.00042941</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>43.0</v>
       </c>
       <c r="AC21" s="1" t="s">
         <v>140</v>
       </c>
       <c r="AD21" s="1">
-        <v>3857.624</v>
+        <v>3648.979</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>158</v>
@@ -3454,7 +3407,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/thinking_agent/report.xlsx
+++ b/reports/thinking_agent/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="221">
   <si>
     <t>Request</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d587-b04c-7653-9364-f52a6d7ab108</t>
+    <t>01a1143f-6fb3-7ca0-8d46-937eae9c46c0</t>
   </si>
   <si>
     <t>Recording</t>
   </si>
   <si>
-    <t>Provider trace</t>
+    <t>Offline simulation</t>
   </si>
   <si>
     <t>FX reference date</t>
@@ -216,7 +216,7 @@
     <t>Pricing scope</t>
   </si>
   <si>
-    <t>Standard online token rates. Verify rates and model access before use. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. No batch, regional, long-context, tool, or negotiated pricing adjustments are applied.</t>
+    <t>Published online token rates verified 2026-10-05. Copilot uses GitHub rates, including saved long-context tiers, before plan allowances; these are usage estimates, not subscription invoices. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. Direct OpenAI and Anthropic entries use standard rates; no batch, regional, tool, negotiated, or unrecorded context-tier adjustments are applied. Model availability and context capacity require separate verification.</t>
   </si>
   <si>
     <t>Model</t>
@@ -252,7 +252,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>https://developers.openai.com/api/docs/models/gpt-5.5.md</t>
@@ -291,6 +291,99 @@
     <t>Illustrative demo rates based on openai:gpt-5.6-luna; no provider billing</t>
   </si>
   <si>
+    <t>anthropic:claude-haiku-4-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-haiku-4-5-20251001</t>
+  </si>
+  <si>
+    <t>anthropic:claude-opus-5-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-4-6</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-5-5</t>
+  </si>
+  <si>
+    <t>copilot:claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t>https://docs.github.com/en/copilot/reference/copilot-billing/models-and-pricing</t>
+  </si>
+  <si>
+    <t>copilot:claude-opus-5.5</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-5.5</t>
+  </si>
+  <si>
+    <t>copilot:gemini-3.8-flash</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-astra.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-luna.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-sol.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6.1-sol.md</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4 [long context]</t>
+  </si>
+  <si>
+    <t>Above 272,000 input tokens</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol [long context]</t>
+  </si>
+  <si>
     <t>Run total</t>
   </si>
   <si>
@@ -303,10 +396,10 @@
     <t>LLM request</t>
   </si>
   <si>
-    <t>gpt-5.6-luna</t>
-  </si>
-  <si>
-    <t>01a0d587-b056-7e50-9325-ebc4f08f9161</t>
+    <t>scripted-chat</t>
+  </si>
+  <si>
+    <t>01a1143f-6fb7-72c1-ade0-8618aca31160</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -336,90 +429,107 @@
     <t>LLM response</t>
   </si>
   <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>Inspect the traffic evidence.
+{"name": "inspect_service", "args": {"section": "traffic"}, "id": "inspect-0", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Tool · inspect_service</t>
+  </si>
+  <si>
+    <t>01a1143f-7039-72a2-9539-5cdd3f56af5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Arguments</t>
+  </si>
+  <si>
+    <t>{'section': 'traffic'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Result</t>
+  </si>
+  <si>
+    <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a1143f-703b-7053-91dc-e3b7fa6e1526</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool result</t>
+  </si>
+  <si>
+    <t>Inspect the database evidence.
+{"name": "inspect_service", "args": {"section": "database"}, "id": "inspect-1", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a1143f-703f-7790-957a-0826ef48d8d6</t>
+  </si>
+  <si>
+    <t>{'section': 'database'}</t>
+  </si>
+  <si>
+    <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a1143f-7041-7961-9676-f3d146921a51</t>
+  </si>
+  <si>
+    <t>Inspect the constraints evidence.
+{"name": "inspect_service", "args": {"section": "constraints"}, "id": "inspect-2", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a1143f-7044-7150-93d2-7954c9f640c3</t>
+  </si>
+  <si>
+    <t>{'section': 'constraints'}</t>
+  </si>
+  <si>
+    <t>Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>01a1143f-7046-7e13-9013-5323af20f982</t>
+  </si>
+  <si>
     <t>Reasoning</t>
   </si>
   <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0dcf4f209eb0e9d6006ab5a3c3768c87d2ae1efb3b110746f4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaPEVFPhPTjMXxWj3Z7ym8YI5XUXqeAo895JGll8xScyxNxdjJHewzEZuyH7e0BdYIpRAWD63w0N50WEidEVLcCF4bZKJIWEZ6vfzxm7KuffgIsdWg_Eqi8vms9sjxMphJla69zX4L7BRCLPmdQlawUrbVkQhUIbhe5yQioVkim92FqVWpR-GAaASCpaFvLW-hGtnRlBj11lvLSlMd1dPaPg9ewntAUEGNO0xGLNljBPOpagoz7_TB3SLAJALN5hqP8wfez8DEAQOzO3fTWEs5-UAwyhE7QLC41jTwA93F2386StQzdlNU7J5I05qJIbeDckOkQ7aLEnrjB9ST88_yQJ1a7c2YrU0ASVviVDg2bgkPJ_IJetsHkmcXUipjh-wz0Us1eUmarc7TbB-TTTlbaw11rG8-LnsEvzxiTviBZ6lVOo3RTUHpJtS3xDxWfs5YhJ_VXp-hKuYhjXbOR6mhIlsNmnd5o9q7Q1yawvAs3h7nHZPbuSleqg21rztXHVqEd0vc1iThRNdrZG7uWgB8Vhwpvhpsdtpr_qlz68n4HqDFdeDcXwafF7BOzyPcHEjhHcQZQqeZNGFLKx0DW2Xuqu87fg2z5dc7t6IZo4i3Yt9VUFZ1MG1Ea0GeOWc11wHYi7ICHa7N8MOWVi1TQCQzXiQSyH7-Kz0wPRnHPXjxepDczFfKgzTBh0R634lYemGXH-G2OLcvniS9W5IOti4s-b-oIWHyo55FAI4vVPnPnird6kqKgjb30lB5gOqndbYotQ9eLgSI5IF0BQxlablFOkVhV-5E0EqghW2zBwdbVGMnERH_ZVbDq7DIDwpHAldyLvkPMndT_f0uq-YT_S6SPOSqIx7v-C5PSAYAYSeNSjdtlI2mwuY3oS-OWFlPSeqDzdV-0V0ay1L1KD3c4WlHTufWZAQB8OG4hk4ZX0Od2uJI4zxUVsOXvA_Dzy3dUlsbX2yxtydEw2tc0LSyp3pGrYnoBc8DftX2qzXHCmDXKxcL6P0fJK47hg9tT4T7t_P8J5yGmV3FJ7MlDDhBmMPLYma6L71V8tXugsGN4oDFqi7peojVFeT-rC5YTusrbcJ-B6SD-ckRQQTu_8tTFbI4XQcfn2ooojfbH07shn0MbOeQH42mYtnrBR_FMd9WglqGsJmfExI6Z1KQaQPSgblfz2uSRq9t27g5C2g7xKXEGYLOYrMtcPSmq_4rCNlRmAWXcCtD6IT21UqOW38KpcJKP0IjvFC5aC8040MORelvuhaXtgK3vLxiykoHTYSxe5GLTvCreSrRLsCOI6mb9_p4Hn6Y0TRo3OGi9PoTZ8m5yP6j0AtaI6vaHKCEarfXROtER6mtUkIZTikLE0w7mhaISGOwNSqnZ4kM2TJ9FEH2svwrk="}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"traffic\"}", "call_id": "call_iG0KdCz7JoKtI9OcodprnaDu", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46c7c87d284a0fda549fcd2ce", "index": 1}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"database\"}", "call_id": "call_9qO13mReiXkguzC0Uj0cvC5b", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46c9487d284b40a1d212a5479", "index": 2}, {"type": "function_call", "name": "inspect_service", "arguments": "{\"section\":\"constraints\"}", "call_id": "call_ogyvwS89SXb1yUrbrWr4U7XC", "id": "fc_0dcf4f209eb0e9d6006ab5a3c46ca087d282694db4158bc12b", "index": 3}]
-{"name": "inspect_service", "args": {"section": "traffic"}, "id": "call_iG0KdCz7JoKtI9OcodprnaDu", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "database"}, "id": "call_9qO13mReiXkguzC0Uj0cvC5b", "type": "tool_call"}
-{"name": "inspect_service", "args": {"section": "constraints"}, "id": "call_ogyvwS89SXb1yUrbrWr4U7XC", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Tool · inspect_service</t>
-  </si>
-  <si>
-    <t>01a0d587-b866-7871-a128-d5c227c50af3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Arguments</t>
-  </si>
-  <si>
-    <t>{'section': 'traffic'}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Result</t>
-  </si>
-  <si>
-    <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.</t>
-  </si>
-  <si>
-    <t>01a0d587-b866-7871-a128-d5da40190df4</t>
-  </si>
-  <si>
-    <t>{'section': 'database'}</t>
-  </si>
-  <si>
-    <t>Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.</t>
-  </si>
-  <si>
-    <t>01a0d587-b866-7871-a128-d5e4ef0dcfc9</t>
-  </si>
-  <si>
-    <t>{'section': 'constraints'}</t>
-  </si>
-  <si>
-    <t>Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d587-b86d-79e0-9ed8-645ca8ae99a9</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool result</t>
-  </si>
-  <si>
-    <t>Peak 240 requests/s; p95 1.8s; 12 workers. Latency rises during database bursts.
-Pool limit 12. Median query 80ms; p95 900ms. Duplicate account lookups appear per request.
-Target p95 under 500ms. No additional database nodes. Cache lifetime must not exceed 60s.</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_0dcf4f209eb0e9d6006ab5a3c56bcc87d29695a2a5fe15cfcc", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaPGmZWpjQ0O1CcqqRAWiZ60TOL9U1-1LE-6WsBX7u9QN2M_TlUh4XqdwUPlSIA92YUkKZokKzVZhBPOiPvn5PkwXVZ9jmuRz4KJwopNjkvpH2q6dg7_zOxu1KpgU7jvqUFgc3Gp_YjtmJ-24mv7DIko3LmqOc3Tjph6xssLQQQqUUy28Z8KNpilIe3WEjEy-FlDp0FDtoF0gR_ddjLdUT3DkZjHjTRBPRNV8doZCXXlgcffb8DoEcJt74kZuCdG8mCa5lmoDgcy2UyQRXgd1GkriQaMaJxclQbWJVzhQKi8Dn9hFmnEMaPtyIOCwKDmF8K6ptzUkUtRv_UajCgWUVIvwMOBy3wpgf8UT-8J8fa7qwCbypk2Lu6aviJ4RTki6EeuxByB7Pga8HINL_tUVjHJp5LoiLiBn1v7BlziwC4PM1mt4fN8lgnPCZvlf7REutF5yr1R1t-Ow82qEYdNmuIhZLQ67_BP5Ze6tmRGilHmoZZakCYVbJ9DVLyj0o65AC3LCxrTUKPc25DWm9x59z3BBRVLgT4KCkeD8oODiT1fPx_itX5R9lZ2B5UcoaOhp9a_Gp9ei1kTKSPfbcyTZMcI6L3HMaHr56hVHBVO3VW6HHw49Rf5y7bXdcE9dxazRaxmN_h8H4hcfvm9GwcxL44LvhwDdxBb_mKo3H7YCBITz51cAUh1XSZVRbq4maBAXQ6LjOQaDKijofNRxLpLbgwt_CCzW917r-mUPc5_BwUmYcWBSlYwIh_RW_zDdpht7vR7pqgFX88GbYLPEYTxzt7GSSnd_DMVreYICUKSE65BWLUc0syZb_DF9Sz7-hTwZKpYvPK8ucWwi-PlGZiA4M3q0atoweSzFJtAQm5MFUzV1Z-0F4pUZMv10M4xy5b-LV3_YM1tgc_WwpxcmPTM2ioi-VTTEHzDOGst-0RUJio9OecDw4SAtJW4jAgn_HkyAvxj-K6CFOWstcn-CfR9UlkmHz2Ri6DVIoyPF8_nA-YqYKgE3KCJJtv7bAKJP-86zq7vCWIIzU_XBSg6_NdFqsfa4d54NT5jxNzh95_yUvGVEkjaZINpgKo0arGiQLVkMa_-mCEB_Bv-nTZBWHUdqgVIINVe1B82noIMFs_1FFqJrtxwXggwYePshvgz1EUfKypU2SUuVzx8mTjVHyRJtkW4TsuPTMH9ux-5pYOwm8WTzlKrAfFqrZpuNpJOZAjtZgkgNzRs638F4AejKHs3uyU6dnaRvS5KT-vPveC59HAVeEOwg_5GaKAgpj0nAZ7_acsmNNrrI43YGyt-hk8_L2HafsZb-YuwmIl-7Jm4LWy5QZ1FYWt0AngTT0d1RqFwfTx4nvMUP-1iPTYYebTnDIuwsJZnLCU4iL1-4W2evky6S8FOUTAVwcLMvftRM4LRixGA8uzY1pNK6rHDv9iBzUqD69DKIbxIsjgoirK7BxDRi-tJYnsN94VVMLp-wvJSyzb-1m5HgsNzUmxjmkAg0Nd5CA=="}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"load\"}", "call_id": "call_8B4ENaYezGivImb0tXxJl4zO", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d0887d292d41560302fe6ff", "index": 1}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"freshness\"}", "call_id": "call_jfOQjRwf2fifrW61g61qMSxF", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d1887d2892ea9971e27ec17", "index": 2}, {"type": "function_call", "name": "test_plan", "arguments": "{\"check\":\"rollback\"}", "call_id": "call_VOcNhmRnXa2Y9jVrz3iUB1r5", "id": "fc_0dcf4f209eb0e9d6006ab5a3c67d2087d284661f6d97db3d86", "index": 3}]
-{"name": "test_plan", "args": {"check": "load"}, "id": "call_8B4ENaYezGivImb0tXxJl4zO", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "freshness"}, "id": "call_jfOQjRwf2fifrW61g61qMSxF", "type": "tool_call"}
-{"name": "test_plan", "args": {"check": "rollback"}, "id": "call_VOcNhmRnXa2Y9jVrz3iUB1r5", "type": "tool_call"}</t>
+    <t xml:space="preserve">    Reasoning text</t>
+  </si>
+  <si>
+    <t>Compare the evidence against the latency and freshness constraints. Evaluate deduplication and short-lived caching, then verify load, invalidation, and rollback.</t>
+  </si>
+  <si>
+    <t>Proposed plan: deduplicate account lookups and add a 30-second invalidated cache. Validate load, freshness, and rollback.
+{"name": "test_plan", "args": {"check": "load"}, "id": "test-0", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · test_plan</t>
   </si>
   <si>
-    <t>01a0d587-bfca-7b60-800f-5f032a343158</t>
+    <t>01a1143f-7049-7a62-9029-faf1bcce99ac</t>
   </si>
   <si>
     <t>{'check': 'load'}</t>
@@ -428,7 +538,20 @@
     <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.</t>
   </si>
   <si>
-    <t>01a0d587-bfcb-7493-86c8-066077c37678</t>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>01a1143f-704c-73b3-afbc-eceb0e6ed002</t>
+  </si>
+  <si>
+    <t>Review the freshness requirement and select a verification check for the proposed change.</t>
+  </si>
+  <si>
+    <t>Verify freshness before recommending the change.
+{"name": "test_plan", "args": {"check": "freshness"}, "id": "test-1", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a1143f-7051-75b2-969f-16aa797fe63a</t>
   </si>
   <si>
     <t>{'check': 'freshness'}</t>
@@ -437,7 +560,20 @@
     <t>PASS: account changes invalidate cached values; maximum fallback age is 30s.</t>
   </si>
   <si>
-    <t>01a0d587-bfcb-7493-86c8-06709a8fb298</t>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>01a1143f-7053-7d91-83b6-86c8b626333d</t>
+  </si>
+  <si>
+    <t>Review the rollback requirement and select a verification check for the proposed change.</t>
+  </si>
+  <si>
+    <t>Verify rollback before recommending the change.
+{"name": "test_plan", "args": {"check": "rollback"}, "id": "test-2", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a1143f-7057-7130-a82e-f8bc772ed094</t>
   </si>
   <si>
     <t>{'check': 'rollback'}</t>
@@ -446,18 +582,16 @@
     <t>PASS: feature flag restores original lookup path; no schema migration required.</t>
   </si>
   <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0d587-bfd6-72e2-be75-3da1f2efa6eb</t>
-  </si>
-  <si>
-    <t>PASS: deduplicated lookups plus 30s cache yield p95 410ms at 240 requests/s; pool occupancy 65%.
-PASS: account changes invalidate cached values; maximum fallback age is 30s.
-PASS: feature flag restores original lookup path; no schema migration required.</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "## Findings\n\n- Traffic peaks at **240 requests/s** with current p95 latency of **1.8 s**.\n- Latency increases during database bursts.\n- The database connection pool is capped at **12** connections.\n- Queries have an **80 ms median** but **900 ms p95** latency.\n- Requests perform duplicate account lookups.\n\n## Proposed latency improvement\n\n1. **Deduplicate account lookups within each request** so repeated references share one in-flight query.\n2. Add a short-lived account cache with a **30-second TTL**.\n3. Invalidate cached account data when account changes occur.\n4. Gate the change behind a feature flag so the existing lookup path can be restored immediately.\n5. Avoid adding database nodes or requiring schema changes.\n\n## Validation\n\n- **Load:** Passed. At 240 requests/s, deduplication plus the 30-second cache produces **410 ms p95 latency**, below the **500 ms target**. Pool occupancy is approximately **65%**.\n- **Freshness:** Passed. Account updates invalidate cached values, and fallback data cannot exceed **30 seconds** old.\n- **Rollback:** Passed. Disabling the feature flag restores the original lookup path, with no schema migration required.\n\nThis plan satisfies all stated constraints and is expected to reduce database burst pressure while meeting the latency target.", "phase": "final_answer", "index": 0, "id": "msg_0dcf4f209eb0e9d6006ab5a3c738f887d2be89b229b6b4b473"}]</t>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>01a1143f-7059-7c80-a9da-c943371274eb</t>
+  </si>
+  <si>
+    <t>Review the verification results against the acceptance criteria and summarize the recommendation with its rollout controls.</t>
+  </si>
+  <si>
+    <t>Recommend deduplicated lookups and a 30-second invalidated cache. The load test meets the 500ms target at 410ms; freshness and rollback checks pass. Roll out behind the feature flag and monitor latency and pool occupancy.</t>
   </si>
   <si>
     <t>investigation_agent</t>
@@ -472,48 +606,39 @@
     <t>Subtree total</t>
   </si>
   <si>
-    <t xml:space="preserve">    PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>Check message history and repair missing tool responses before the agent starts.</t>
-  </si>
-  <si>
-    <t>01a0d587-b04f-7b73-8ae4-d187b3b1b04f</t>
+    <t xml:space="preserve">    model</t>
+  </si>
+  <si>
+    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
+  </si>
+  <si>
+    <t>01a1143f-6fb5-7a40-a454-bfd2c043d6a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SimulatedModel</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>Investigate evidence and test a hypothesis.</t>
+  </si>
+  <si>
+    <t>Own call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    tools</t>
+  </si>
+  <si>
+    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
+  </si>
+  <si>
+    <t>01a1143f-7038-7493-b25f-5dd3069acde7</t>
   </si>
   <si>
     <t>No model charge</t>
   </si>
   <si>
-    <t xml:space="preserve">    model</t>
-  </si>
-  <si>
-    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
-  </si>
-  <si>
-    <t>01a0d587-b050-7ae0-b2c7-51aa65f4e355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ChatOpenAI</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>Generate the next assistant message or tool request from the current conversation.</t>
-  </si>
-  <si>
-    <t>Own call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    tools</t>
-  </si>
-  <si>
-    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
-  </si>
-  <si>
-    <t>01a0d587-b863-7430-a472-54ef91260ade</t>
-  </si>
-  <si>
     <t xml:space="preserve">        inspect_service</t>
   </si>
   <si>
@@ -523,16 +648,22 @@
     <t>Read fictional service evidence; no live service is inspected.</t>
   </si>
   <si>
-    <t>01a0d587-b863-7430-a472-54f1eab3357e</t>
-  </si>
-  <si>
-    <t>01a0d587-b863-7430-a472-5501eabdde94</t>
-  </si>
-  <si>
-    <t>01a0d587-b86a-77a1-9f8f-0b849486b6ce</t>
-  </si>
-  <si>
-    <t>01a0d587-bfc8-7a62-a7b1-cf0029a244ee</t>
+    <t>01a1143f-703a-7242-9ed2-7056864c3c5d</t>
+  </si>
+  <si>
+    <t>01a1143f-703f-7790-957a-0813924e38da</t>
+  </si>
+  <si>
+    <t>01a1143f-7040-7e31-87f6-de9fe83c1086</t>
+  </si>
+  <si>
+    <t>01a1143f-7043-7101-9b19-abcdd5e8bf96</t>
+  </si>
+  <si>
+    <t>01a1143f-7045-7223-947a-5b966d7a4a77</t>
+  </si>
+  <si>
+    <t>01a1143f-7049-7a62-9029-fae41eb66121</t>
   </si>
   <si>
     <t xml:space="preserve">        test_plan</t>
@@ -541,13 +672,19 @@
     <t>Return a fixed fictional plan-check result; no real test is executed.</t>
   </si>
   <si>
-    <t>01a0d587-bfc8-7a62-a7b1-cf11aabfeeb3</t>
-  </si>
-  <si>
-    <t>01a0d587-bfc8-7a62-a7b1-cf21e87619f1</t>
-  </si>
-  <si>
-    <t>01a0d587-bfd2-7dd1-be10-fa39c04ad4ca</t>
+    <t>01a1143f-704b-7543-8e48-cfb70c01dc2b</t>
+  </si>
+  <si>
+    <t>01a1143f-7050-7833-8614-faff8b3a8045</t>
+  </si>
+  <si>
+    <t>01a1143f-7053-7d91-83b6-86b453c33df4</t>
+  </si>
+  <si>
+    <t>01a1143f-7057-7130-a82e-f8a21b6b344f</t>
+  </si>
+  <si>
+    <t>01a1143f-7059-7c80-a9da-c937acaf0d5c</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1091,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1011,23 +1148,23 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011438731376</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114)=7,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114),"Unknown")</f>
+        <v>0.0164652314348</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00130024</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114)=7,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114),"Unknown")</f>
+        <v>0.01871602</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>114.0</v>
+        <v>1647.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1035,307 +1172,296 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011438731376</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114)=7,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114),"Unknown")</f>
+        <v>0.0164652314348</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00130024</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114)=7,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114),"Unknown")</f>
+        <v>0.01871602</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>114.0</v>
+        <v>1647.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4">
-        <v>2102</v>
+        <v>257</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>4.5218636e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B22),D5*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>5.14e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>129</v>
+      </c>
+      <c r="D6" s="1">
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="34" customHeight="1">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>130</v>
+      </c>
+      <c r="D7" s="1">
+        <v>49</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="1">
+        <v>35</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2099</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000461643565</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00052475</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>52.0</v>
+        <v>134</v>
+      </c>
+      <c r="D9" s="1">
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D10" s="1">
+        <v>257</v>
+      </c>
+      <c r="L10" s="1">
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D11" s="4">
-        <v>93</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D12" s="5">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0614952e-05</v>
+        <v>6.1229904e-05</v>
       </c>
       <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E22),D12*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.96e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="47" customHeight="1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="5">
-        <v>64</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.7564032e-05</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.68e-05</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="409" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="D14" s="1">
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D15" s="1">
+        <v>58</v>
+      </c>
+      <c r="L15" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
+        <v>0.00010644854</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
+        <v>0.000121</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000560350393</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.00063695</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>56.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>64.0</v>
+        <v>142</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>113</v>
+        <v>141</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="24" customHeight="1">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="24" customHeight="1">
@@ -1343,465 +1469,554 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>118</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4">
+        <v>366</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="5">
+        <v>315</v>
+      </c>
+      <c r="E21" s="2">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.542362e-06</v>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C22),D21*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>6.3e-06</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="34" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="D22" s="5">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2">
+        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.973348e-06</v>
+      </c>
+      <c r="F22" s="2">
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B22),D22*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>1.02e-05</v>
+      </c>
+      <c r="G22" s="5">
+        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="24" customHeight="1">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>151</v>
+      </c>
+      <c r="D23" s="1">
+        <v>51</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B24" s="4">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>121</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="24" customHeight="1">
+      <c r="A24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
+      <c r="A25" t="s">
+        <v>148</v>
+      </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="34" customHeight="1">
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="4">
-        <v>2296</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D25" s="1">
+        <v>51</v>
+      </c>
+      <c r="L25" s="1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="5">
+        <v>58</v>
+      </c>
+      <c r="E27" s="2">
+        <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="F27" s="2">
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E22),D27*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="47" customHeight="1">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2099</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.69314852e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!C17),D28*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.198e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>138</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="5">
-        <v>3</v>
-      </c>
-      <c r="E29" s="2">
-        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!B17),D29*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="5">
-        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="73" customHeight="1">
+        <v>134</v>
+      </c>
+      <c r="D29" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="5">
-        <v>194</v>
+        <v>135</v>
+      </c>
+      <c r="D30" s="1">
+        <v>58</v>
+      </c>
+      <c r="L30" s="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="E31" s="2">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.266739e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E27)=3,SUM('Turns'!E21,'Turns'!E22,'Turns'!E27),"Unknown")</f>
+        <v>7.5745614e-05</v>
       </c>
       <c r="F31" s="2">
-        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!D17),D31*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.85e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F27)=3,SUM('Turns'!F21,'Turns'!F22,'Turns'!F27),"Unknown")</f>
+        <v>8.61e-05</v>
       </c>
       <c r="G31" s="5">
         <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="5">
         <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="4">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1">
-      <c r="A34" t="s">
-        <v>124</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="34" customHeight="1">
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="5">
-        <v>54</v>
-      </c>
-      <c r="E34" s="2">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER('Reference data'!$B$3)),F34*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.7007152e-05</v>
-      </c>
-      <c r="F34" s="2">
-        <f>IF(D34=0,0,IF(ISNUMBER('Reference data'!F17),D34*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>6.48e-05</v>
-      </c>
-      <c r="G34" s="5">
-        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H34" s="5">
-        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="24" customHeight="1">
-      <c r="A35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="5">
-        <v>65</v>
-      </c>
-      <c r="E35" s="2">
-        <f>IF(AND(ISNUMBER(F35),ISNUMBER('Reference data'!$B$3)),F35*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.861972e-05</v>
-      </c>
-      <c r="F35" s="2">
-        <f>IF(D35=0,0,IF(ISNUMBER('Reference data'!E17),D35*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.8e-05</v>
-      </c>
-      <c r="G35" s="5">
-        <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H35" s="5">
-        <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="409" customHeight="1">
+        <v>146</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="4">
+        <v>475</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>129</v>
+        <v>150</v>
+      </c>
+      <c r="D36" s="5">
+        <v>424</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.4601952e-06</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!C22),D36*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>8.48e-06</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="24" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="D37" s="5">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.973348e-06</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!B22),D37*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>1.02e-05</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="34" customHeight="1">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35)=5,SUM('Turns'!E28,'Turns'!E29,'Turns'!E31,'Turns'!E34,'Turns'!E35),"Unknown")</f>
-        <v>0.0002057535912</v>
-      </c>
-      <c r="F39" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35)=5,SUM('Turns'!F28,'Turns'!F29,'Turns'!F31,'Turns'!F34,'Turns'!F35),"Unknown")</f>
-        <v>0.00023388</v>
-      </c>
-      <c r="G39" s="5">
-        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="H39" s="5">
-        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B40" s="4">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="34" customHeight="1">
+        <v>151</v>
+      </c>
+      <c r="D38" s="1">
+        <v>51</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1">
+      <c r="A39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="24" customHeight="1">
+      <c r="A40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="1">
+        <v>51</v>
+      </c>
+      <c r="L40" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1">
+      <c r="A42" t="s">
+        <v>156</v>
+      </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M43" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="5">
+        <v>58</v>
+      </c>
+      <c r="E42" s="2">
+        <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="F42" s="2">
+        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E22),D42*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="47" customHeight="1">
+      <c r="A43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>138</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1">
+      <c r="A44" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="24" customHeight="1">
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="I44" s="6" t="s">
+      <c r="D44" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="24" customHeight="1">
+      <c r="A45" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="24" customHeight="1">
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>136</v>
+      <c r="D45" s="1">
+        <v>58</v>
+      </c>
+      <c r="L45" s="1">
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="B46" s="4">
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
+      </c>
+      <c r="E46" s="2">
+        <f>IF(COUNT('Turns'!E36,'Turns'!E37,'Turns'!E42)=3,SUM('Turns'!E36,'Turns'!E37,'Turns'!E42),"Unknown")</f>
+        <v>7.76634472e-05</v>
+      </c>
+      <c r="F46" s="2">
+        <f>IF(COUNT('Turns'!F36,'Turns'!F37,'Turns'!F42)=3,SUM('Turns'!F36,'Turns'!F37,'Turns'!F42),"Unknown")</f>
+        <v>8.828e-05</v>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="24" customHeight="1">
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
@@ -1809,259 +2024,1297 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D49" s="4">
-        <v>2503</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24" customHeight="1">
-      <c r="A50" t="s">
-        <v>140</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="34" customHeight="1">
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" s="4">
+        <v>581</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D50" s="5">
-        <v>2293</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.03448764e-05</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.586e-05</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+      <c r="M50" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="D51" s="5">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="E51" s="2">
         <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>9.3780284e-06</v>
       </c>
       <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!B17),D51*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C22),D51*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.066e-05</v>
       </c>
       <c r="G51" s="5">
         <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H51" s="5">
         <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="60" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="D52" s="5">
+        <v>48</v>
+      </c>
+      <c r="E52" s="2">
+        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.445504e-06</v>
+      </c>
+      <c r="F52" s="2">
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B22),D52*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="G52" s="5">
+        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="34" customHeight="1">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="5">
-        <v>207</v>
-      </c>
-      <c r="E53" s="2">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.5526545e-05</v>
-      </c>
-      <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>5.175e-05</v>
-      </c>
-      <c r="G53" s="5">
-        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H53" s="5">
-        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>151</v>
+      </c>
+      <c r="D53" s="1">
+        <v>48</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="24" customHeight="1">
       <c r="A54" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="4">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
-      <c r="A56" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" s="5">
-        <v>276</v>
-      </c>
-      <c r="E56" s="2">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000291369888</v>
-      </c>
-      <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!E17),D56*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0003312</v>
-      </c>
-      <c r="G56" s="5">
-        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="H56" s="5">
-        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>33.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="229" customHeight="1">
+        <v>134</v>
+      </c>
+      <c r="D54" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="24" customHeight="1">
+      <c r="A55" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="1">
+        <v>48</v>
+      </c>
+      <c r="L55" s="1">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="4">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="4">
+        <v>12080</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
+        <v>164</v>
+      </c>
+      <c r="D57" s="5">
+        <v>12000</v>
+      </c>
+      <c r="E57" s="2">
+        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.012668256</v>
+      </c>
+      <c r="F57" s="2">
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!F22),D57*'Reference data'!F22/1000000,"Unknown"))</f>
+        <v>0.0144</v>
+      </c>
+      <c r="G57" s="5">
+        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1267.0</v>
+      </c>
+      <c r="H57" s="5">
+        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="34" customHeight="1">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>165</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="24" customHeight="1">
       <c r="A59" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="5">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2">
+        <f>IF(AND(ISNUMBER(F59),ISNUMBER('Reference data'!$B$3)),F59*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.445504e-05</v>
+      </c>
+      <c r="F59" s="2">
+        <f>IF(D59=0,0,IF(ISNUMBER('Reference data'!E22),D59*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>9.6e-05</v>
+      </c>
+      <c r="G59" s="5">
+        <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H59" s="5">
+        <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="47" customHeight="1">
+      <c r="A60" t="s">
+        <v>162</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>138</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>134</v>
+      </c>
+      <c r="D61" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="24" customHeight="1">
+      <c r="A62" t="s">
+        <v>162</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>135</v>
+      </c>
+      <c r="D62" s="1">
+        <v>80</v>
+      </c>
+      <c r="L62" s="1">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A63" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="4">
+        <v>1</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A60" s="4" t="s">
+      <c r="E63" s="2">
+        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E57,'Turns'!E59)=4,SUM('Turns'!E51,'Turns'!E52,'Turns'!E57,'Turns'!E59),"Unknown")</f>
+        <v>0.0127705345724</v>
+      </c>
+      <c r="F63" s="2">
+        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F57,'Turns'!F59)=4,SUM('Turns'!F51,'Turns'!F52,'Turns'!F57,'Turns'!F59),"Unknown")</f>
+        <v>0.01451626</v>
+      </c>
+      <c r="G63" s="5">
+        <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1277.0</v>
+      </c>
+      <c r="H63" s="5">
+        <f>IF(ISNUMBER(F63),ROUND(F63*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1452.0</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B64" s="4">
+        <v>1</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="24" customHeight="1">
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>144</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="34" customHeight="1">
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>146</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A67" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="4">
+        <v>1</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="4">
+        <v>717</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="24" customHeight="1">
+      <c r="A68" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" s="5">
+        <v>661</v>
+      </c>
+      <c r="E68" s="2">
+        <f>IF(AND(ISNUMBER(F68),ISNUMBER('Reference data'!$B$3)),F68*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.16301628e-05</v>
+      </c>
+      <c r="F68" s="2">
+        <f>IF(D68=0,0,IF(ISNUMBER('Reference data'!C22),D68*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.322e-05</v>
+      </c>
+      <c r="G68" s="5">
+        <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H68" s="5">
+        <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="24" customHeight="1">
+      <c r="A69" t="s">
+        <v>172</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>128</v>
+      </c>
+      <c r="D69" s="5">
+        <v>56</v>
+      </c>
+      <c r="E69" s="2">
+        <f>IF(AND(ISNUMBER(F69),ISNUMBER('Reference data'!$B$3)),F69*'Reference data'!$B$3,"Unknown")</f>
+        <v>9.853088e-06</v>
+      </c>
+      <c r="F69" s="2">
+        <f>IF(D69=0,0,IF(ISNUMBER('Reference data'!B22),D69*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>1.12e-05</v>
+      </c>
+      <c r="G69" s="5">
+        <f>IF(ISNUMBER(E69),ROUND(E69*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H69" s="5">
+        <f>IF(ISNUMBER(F69),ROUND(F69*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="34" customHeight="1">
+      <c r="A70" t="s">
+        <v>172</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="1">
+        <v>56</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="24" customHeight="1">
+      <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>134</v>
+      </c>
+      <c r="D71" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="24" customHeight="1">
+      <c r="A72" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" s="1">
+        <v>56</v>
+      </c>
+      <c r="L72" s="1">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A73" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" s="4">
+        <v>1</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D73" s="4">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="24" customHeight="1">
+      <c r="A74" t="s">
+        <v>172</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" s="5">
+        <v>600</v>
+      </c>
+      <c r="E74" s="2">
+        <f>IF(AND(ISNUMBER(F74),ISNUMBER('Reference data'!$B$3)),F74*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0006334128</v>
+      </c>
+      <c r="F74" s="2">
+        <f>IF(D74=0,0,IF(ISNUMBER('Reference data'!F22),D74*'Reference data'!F22/1000000,"Unknown"))</f>
+        <v>0.00072</v>
+      </c>
+      <c r="G74" s="5">
+        <f>IF(ISNUMBER(E74),ROUND(E74*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>63.0</v>
+      </c>
+      <c r="H74" s="5">
+        <f>IF(ISNUMBER(F74),ROUND(F74*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="34" customHeight="1">
+      <c r="A75" t="s">
+        <v>172</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>165</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="24" customHeight="1">
+      <c r="A76" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" s="5">
+        <v>61</v>
+      </c>
+      <c r="E76" s="2">
+        <f>IF(AND(ISNUMBER(F76),ISNUMBER('Reference data'!$B$3)),F76*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.4396968e-05</v>
+      </c>
+      <c r="F76" s="2">
+        <f>IF(D76=0,0,IF(ISNUMBER('Reference data'!E22),D76*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>7.32e-05</v>
+      </c>
+      <c r="G76" s="5">
+        <f>IF(ISNUMBER(E76),ROUND(E76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H76" s="5">
+        <f>IF(ISNUMBER(F76),ROUND(F76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="47" customHeight="1">
+      <c r="A77" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>138</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="24" customHeight="1">
+      <c r="A78" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="24" customHeight="1">
+      <c r="A79" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>135</v>
+      </c>
+      <c r="D79" s="1">
+        <v>61</v>
+      </c>
+      <c r="L79" s="1">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A80" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B80" s="4">
+        <v>1</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E60" s="2">
-        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56)=4,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56),"Unknown")</f>
-        <v>0.0003777691534</v>
-      </c>
-      <c r="F60" s="2">
-        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56)=4,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56),"Unknown")</f>
-        <v>0.00042941</v>
-      </c>
-      <c r="G60" s="5">
-        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
-      </c>
-      <c r="H60" s="5">
-        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>111</v>
+      <c r="E80" s="2">
+        <f>IF(COUNT('Turns'!E68,'Turns'!E69,'Turns'!E74,'Turns'!E76)=4,SUM('Turns'!E68,'Turns'!E69,'Turns'!E74,'Turns'!E76),"Unknown")</f>
+        <v>0.0007192930188</v>
+      </c>
+      <c r="F80" s="2">
+        <f>IF(COUNT('Turns'!F68,'Turns'!F69,'Turns'!F74,'Turns'!F76)=4,SUM('Turns'!F68,'Turns'!F69,'Turns'!F74,'Turns'!F76),"Unknown")</f>
+        <v>0.00081762</v>
+      </c>
+      <c r="G80" s="5">
+        <f>IF(ISNUMBER(E80),ROUND(E80*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="H80" s="5">
+        <f>IF(ISNUMBER(F80),ROUND(F80*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B81" s="4">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="24" customHeight="1">
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>144</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="24" customHeight="1">
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>146</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A84" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B84" s="4">
+        <v>1</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="4">
+        <v>820</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="24" customHeight="1">
+      <c r="A85" t="s">
+        <v>179</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85" s="5">
+        <v>778</v>
+      </c>
+      <c r="E85" s="2">
+        <f>IF(AND(ISNUMBER(F85),ISNUMBER('Reference data'!$B$3)),F85*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.36887544e-05</v>
+      </c>
+      <c r="F85" s="2">
+        <f>IF(D85=0,0,IF(ISNUMBER('Reference data'!C22),D85*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.556e-05</v>
+      </c>
+      <c r="G85" s="5">
+        <f>IF(ISNUMBER(E85),ROUND(E85*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H85" s="5">
+        <f>IF(ISNUMBER(F85),ROUND(F85*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="24" customHeight="1">
+      <c r="A86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="5">
+        <v>42</v>
+      </c>
+      <c r="E86" s="2">
+        <f>IF(AND(ISNUMBER(F86),ISNUMBER('Reference data'!$B$3)),F86*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.389816e-06</v>
+      </c>
+      <c r="F86" s="2">
+        <f>IF(D86=0,0,IF(ISNUMBER('Reference data'!B22),D86*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="G86" s="5">
+        <f>IF(ISNUMBER(E86),ROUND(E86*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H86" s="5">
+        <f>IF(ISNUMBER(F86),ROUND(F86*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="24" customHeight="1">
+      <c r="A87" t="s">
+        <v>179</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" s="1">
+        <v>42</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="24" customHeight="1">
+      <c r="A88" t="s">
+        <v>179</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="24" customHeight="1">
+      <c r="A89" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>135</v>
+      </c>
+      <c r="D89" s="1">
+        <v>42</v>
+      </c>
+      <c r="L89" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A90" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" s="4">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="4">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="24" customHeight="1">
+      <c r="A91" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" s="5">
+        <v>600</v>
+      </c>
+      <c r="E91" s="2">
+        <f>IF(AND(ISNUMBER(F91),ISNUMBER('Reference data'!$B$3)),F91*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0006334128</v>
+      </c>
+      <c r="F91" s="2">
+        <f>IF(D91=0,0,IF(ISNUMBER('Reference data'!F22),D91*'Reference data'!F22/1000000,"Unknown"))</f>
+        <v>0.00072</v>
+      </c>
+      <c r="G91" s="5">
+        <f>IF(ISNUMBER(E91),ROUND(E91*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>63.0</v>
+      </c>
+      <c r="H91" s="5">
+        <f>IF(ISNUMBER(F91),ROUND(F91*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="24" customHeight="1">
+      <c r="A92" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>165</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="24" customHeight="1">
+      <c r="A93" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" s="5">
+        <v>60</v>
+      </c>
+      <c r="E93" s="2">
+        <f>IF(AND(ISNUMBER(F93),ISNUMBER('Reference data'!$B$3)),F93*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.334128e-05</v>
+      </c>
+      <c r="F93" s="2">
+        <f>IF(D93=0,0,IF(ISNUMBER('Reference data'!E22),D93*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>7.2e-05</v>
+      </c>
+      <c r="G93" s="5">
+        <f>IF(ISNUMBER(E93),ROUND(E93*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H93" s="5">
+        <f>IF(ISNUMBER(F93),ROUND(F93*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="47" customHeight="1">
+      <c r="A94" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="24" customHeight="1">
+      <c r="A95" t="s">
+        <v>179</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>134</v>
+      </c>
+      <c r="D95" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="24" customHeight="1">
+      <c r="A96" t="s">
+        <v>179</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>135</v>
+      </c>
+      <c r="D96" s="1">
+        <v>60</v>
+      </c>
+      <c r="L96" s="1">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A97" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" s="4">
+        <v>1</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E97" s="2">
+        <f>IF(COUNT('Turns'!E85,'Turns'!E86,'Turns'!E91,'Turns'!E93)=4,SUM('Turns'!E85,'Turns'!E86,'Turns'!E91,'Turns'!E93),"Unknown")</f>
+        <v>0.0007178326504</v>
+      </c>
+      <c r="F97" s="2">
+        <f>IF(COUNT('Turns'!F85,'Turns'!F86,'Turns'!F91,'Turns'!F93)=4,SUM('Turns'!F85,'Turns'!F86,'Turns'!F91,'Turns'!F93),"Unknown")</f>
+        <v>0.00081596</v>
+      </c>
+      <c r="G97" s="5">
+        <f>IF(ISNUMBER(E97),ROUND(E97*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="H97" s="5">
+        <f>IF(ISNUMBER(F97),ROUND(F97*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B98" s="4">
+        <v>1</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="24" customHeight="1">
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>144</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="24" customHeight="1">
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>146</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B101" s="4">
+        <v>1</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D101" s="4">
+        <v>920</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="24" customHeight="1">
+      <c r="A102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>150</v>
+      </c>
+      <c r="D102" s="5">
+        <v>880</v>
+      </c>
+      <c r="E102" s="2">
+        <f>IF(AND(ISNUMBER(F102),ISNUMBER('Reference data'!$B$3)),F102*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.5483424e-05</v>
+      </c>
+      <c r="F102" s="2">
+        <f>IF(D102=0,0,IF(ISNUMBER('Reference data'!C22),D102*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.76e-05</v>
+      </c>
+      <c r="G102" s="5">
+        <f>IF(ISNUMBER(E102),ROUND(E102*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H102" s="5">
+        <f>IF(ISNUMBER(F102),ROUND(F102*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="24" customHeight="1">
+      <c r="A103" t="s">
+        <v>186</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>128</v>
+      </c>
+      <c r="D103" s="5">
+        <v>40</v>
+      </c>
+      <c r="E103" s="2">
+        <f>IF(AND(ISNUMBER(F103),ISNUMBER('Reference data'!$B$3)),F103*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.03792e-06</v>
+      </c>
+      <c r="F103" s="2">
+        <f>IF(D103=0,0,IF(ISNUMBER('Reference data'!B22),D103*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>8e-06</v>
+      </c>
+      <c r="G103" s="5">
+        <f>IF(ISNUMBER(E103),ROUND(E103*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H103" s="5">
+        <f>IF(ISNUMBER(F103),ROUND(F103*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="24" customHeight="1">
+      <c r="A104" t="s">
+        <v>186</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>151</v>
+      </c>
+      <c r="D104" s="1">
+        <v>40</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="24" customHeight="1">
+      <c r="A105" t="s">
+        <v>186</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>134</v>
+      </c>
+      <c r="D105" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="24" customHeight="1">
+      <c r="A106" t="s">
+        <v>186</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>135</v>
+      </c>
+      <c r="D106" s="1">
+        <v>40</v>
+      </c>
+      <c r="L106" s="1">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A107" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B107" s="4">
+        <v>1</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="24" customHeight="1">
+      <c r="A108" t="s">
+        <v>186</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108" s="5">
+        <v>1800</v>
+      </c>
+      <c r="E108" s="2">
+        <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0019002384</v>
+      </c>
+      <c r="F108" s="2">
+        <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!F22),D108*'Reference data'!F22/1000000,"Unknown"))</f>
+        <v>0.00216</v>
+      </c>
+      <c r="G108" s="5">
+        <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>190.0</v>
+      </c>
+      <c r="H108" s="5">
+        <f>IF(ISNUMBER(F108),ROUND(F108*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>216.0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="34" customHeight="1">
+      <c r="A109" t="s">
+        <v>186</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>165</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="24" customHeight="1">
+      <c r="A110" t="s">
+        <v>186</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>137</v>
+      </c>
+      <c r="D110" s="5">
+        <v>71</v>
+      </c>
+      <c r="E110" s="2">
+        <f>IF(AND(ISNUMBER(F110),ISNUMBER('Reference data'!$B$3)),F110*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.4953848e-05</v>
+      </c>
+      <c r="F110" s="2">
+        <f>IF(D110=0,0,IF(ISNUMBER('Reference data'!E22),D110*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>8.52e-05</v>
+      </c>
+      <c r="G110" s="5">
+        <f>IF(ISNUMBER(E110),ROUND(E110*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H110" s="5">
+        <f>IF(ISNUMBER(F110),ROUND(F110*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="47" customHeight="1">
+      <c r="A111" t="s">
+        <v>186</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>138</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="24" customHeight="1">
+      <c r="A112" t="s">
+        <v>186</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>134</v>
+      </c>
+      <c r="D112" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="24" customHeight="1">
+      <c r="A113" t="s">
+        <v>186</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>135</v>
+      </c>
+      <c r="D113" s="1">
+        <v>71</v>
+      </c>
+      <c r="L113" s="1">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A114" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B114" s="4">
+        <v>1</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E114" s="2">
+        <f>IF(COUNT('Turns'!E102,'Turns'!E103,'Turns'!E108,'Turns'!E110)=4,SUM('Turns'!E102,'Turns'!E103,'Turns'!E108,'Turns'!E110),"Unknown")</f>
+        <v>0.001997713592</v>
+      </c>
+      <c r="F114" s="2">
+        <f>IF(COUNT('Turns'!F102,'Turns'!F103,'Turns'!F108,'Turns'!F110)=4,SUM('Turns'!F102,'Turns'!F103,'Turns'!F108,'Turns'!F110),"Unknown")</f>
+        <v>0.0022708</v>
+      </c>
+      <c r="G114" s="5">
+        <f>IF(ISNUMBER(E114),ROUND(E114*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>200.0</v>
+      </c>
+      <c r="H114" s="5">
+        <f>IF(ISNUMBER(F114),ROUND(F114*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>227.0</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE60">
+  <conditionalFormatting sqref="A2:AE114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2075,7 +3328,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AE28"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -2182,177 +3435,244 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D29,'Turns'!D51)=3,SUM('Turns'!D5,'Turns'!D29,'Turns'!D51),"Unknown")</f>
-        <v>9.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D22,'Turns'!D37,'Turns'!D52,'Turns'!D69,'Turns'!D86,'Turns'!D103)=7,SUM('Turns'!D5,'Turns'!D22,'Turns'!D37,'Turns'!D52,'Turns'!D69,'Turns'!D86,'Turns'!D103),"Unknown")</f>
+        <v>545.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E29,'Turns'!E51)=3,SUM('Turns'!E5,'Turns'!E29,'Turns'!E51),"Unknown")</f>
-        <v>1.583532e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E22,'Turns'!E37,'Turns'!E52,'Turns'!E69,'Turns'!E86,'Turns'!E103)=7,SUM('Turns'!E5,'Turns'!E22,'Turns'!E37,'Turns'!E52,'Turns'!E69,'Turns'!E86,'Turns'!E103),"Unknown")</f>
+        <v>9.589166e-05</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F29,'Turns'!F51)=3,SUM('Turns'!F5,'Turns'!F29,'Turns'!F51),"Unknown")</f>
-        <v>1.8e-06</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F22,'Turns'!F37,'Turns'!F52,'Turns'!F69,'Turns'!F86,'Turns'!F103)=7,SUM('Turns'!F5,'Turns'!F22,'Turns'!F37,'Turns'!F52,'Turns'!F69,'Turns'!F86,'Turns'!F103),"Unknown")</f>
+        <v>0.000109</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D28,'Turns'!D50)=2,SUM('Turns'!D28,'Turns'!D50),"Unknown")</f>
-        <v>4392.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D36,'Turns'!D51,'Turns'!D68,'Turns'!D85,'Turns'!D102)=6,SUM('Turns'!D21,'Turns'!D36,'Turns'!D51,'Turns'!D68,'Turns'!D85,'Turns'!D102),"Unknown")</f>
+        <v>3591.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E50)=2,SUM('Turns'!E28,'Turns'!E50),"Unknown")</f>
-        <v>7.72763616e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E36,'Turns'!E51,'Turns'!E68,'Turns'!E85,'Turns'!E102)=6,SUM('Turns'!E21,'Turns'!E36,'Turns'!E51,'Turns'!E68,'Turns'!E85,'Turns'!E102),"Unknown")</f>
+        <v>6.31829268e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F50)=2,SUM('Turns'!F28,'Turns'!F50),"Unknown")</f>
-        <v>8.784e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F36,'Turns'!F51,'Turns'!F68,'Turns'!F85,'Turns'!F102)=6,SUM('Turns'!F21,'Turns'!F36,'Turns'!F51,'Turns'!F68,'Turns'!F85,'Turns'!F102),"Unknown")</f>
+        <v>7.182e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D31,'Turns'!D53)=3,SUM('Turns'!D9,'Turns'!D31,'Turns'!D53),"Unknown")</f>
-        <v>2500.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E31,'Turns'!E53)=3,SUM('Turns'!E9,'Turns'!E31,'Turns'!E53),"Unknown")</f>
-        <v>0.0005498375</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F31,'Turns'!F53)=3,SUM('Turns'!F9,'Turns'!F31,'Turns'!F53),"Unknown")</f>
-        <v>0.000625</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D35,'Turns'!D56)=3,SUM('Turns'!D13,'Turns'!D35,'Turns'!D56),"Unknown")</f>
-        <v>405.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D59,'Turns'!D76,'Turns'!D93,'Turns'!D110)=7,SUM('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D59,'Turns'!D76,'Turns'!D93,'Turns'!D110),"Unknown")</f>
+        <v>446.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E35,'Turns'!E56)=3,SUM('Turns'!E13,'Turns'!E35,'Turns'!E56),"Unknown")</f>
-        <v>0.00042755364</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E59,'Turns'!E76,'Turns'!E93,'Turns'!E110)=7,SUM('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E59,'Turns'!E76,'Turns'!E93,'Turns'!E110),"Unknown")</f>
+        <v>0.000470836848</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F35,'Turns'!F56)=3,SUM('Turns'!F13,'Turns'!F35,'Turns'!F56),"Unknown")</f>
-        <v>0.000486</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F59,'Turns'!F76,'Turns'!F93,'Turns'!F110)=7,SUM('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F59,'Turns'!F76,'Turns'!F93,'Turns'!F110),"Unknown")</f>
+        <v>0.0005352</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D34)=2,SUM('Turns'!D12,'Turns'!D34),"Unknown")</f>
-        <v>83.0</v>
+        <f>IF(COUNT('Turns'!D57,'Turns'!D74,'Turns'!D91,'Turns'!D108)=4,SUM('Turns'!D57,'Turns'!D74,'Turns'!D91,'Turns'!D108),"Unknown")</f>
+        <v>15000.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E34)=2,SUM('Turns'!E12,'Turns'!E34),"Unknown")</f>
-        <v>8.7622104e-05</v>
+        <f>IF(COUNT('Turns'!E57,'Turns'!E74,'Turns'!E91,'Turns'!E108)=4,SUM('Turns'!E57,'Turns'!E74,'Turns'!E91,'Turns'!E108),"Unknown")</f>
+        <v>0.01583532</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F34)=2,SUM('Turns'!F12,'Turns'!F34),"Unknown")</f>
-        <v>9.96e-05</v>
+        <f>IF(COUNT('Turns'!F57,'Turns'!F74,'Turns'!F91,'Turns'!F108)=4,SUM('Turns'!F57,'Turns'!F74,'Turns'!F91,'Turns'!F108),"Unknown")</f>
+        <v>0.018</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E39,'Turns'!E60)=3,SUM('Turns'!E17,'Turns'!E39,'Turns'!E60),"Unknown")</f>
-        <v>0.0011438731376</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114)=7,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E63,'Turns'!E80,'Turns'!E97,'Turns'!E114),"Unknown")</f>
+        <v>0.0164652314348</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F39,'Turns'!F60)=3,SUM('Turns'!F17,'Turns'!F39,'Turns'!F60),"Unknown")</f>
-        <v>0.00130024</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114)=7,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F63,'Turns'!F80,'Turns'!F97,'Turns'!F114),"Unknown")</f>
+        <v>0.01871602</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>114.0</v>
+        <v>1647.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>1872.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>7627.606</v>
+        <v>167.023</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
+      <c r="J3" s="2">
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>257.0</v>
+      </c>
+      <c r="K3" s="2">
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>4.5218636e-05</v>
+      </c>
+      <c r="L3" s="2">
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>5.14e-05</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>58.0</v>
+      </c>
+      <c r="T3" s="2">
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="U3" s="2">
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00010644854</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000121</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
       <c r="AD3" s="1">
-        <v>0.322</v>
+        <v>129.34</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F4" s="1">
+        <v>257</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="J4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
+        <v>257.0</v>
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>4.5218636e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
+        <v>5.14e-05</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -2364,999 +3684,1731 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2099.0</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000461643565</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00052475</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>64.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>58.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>6.7564032e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>6.1229904e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>7.68e-05</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.96e-05</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>29.0</v>
+        <v>0</v>
       </c>
       <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>3.0614952e-05</v>
+        <v>0</v>
       </c>
       <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000560350393</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.00010644854</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00063695</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.000121</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>56.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>64.0</v>
+        <v>12.0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AD4" s="1">
-        <v>2064.382</v>
+        <v>127.41</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2102</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="I5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000461643565</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00052475</v>
-      </c>
-      <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>64.0</v>
-      </c>
-      <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>6.7564032e-05</v>
-      </c>
-      <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>7.68e-05</v>
-      </c>
-      <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>3.0614952e-05</v>
-      </c>
-      <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.48e-05</v>
-      </c>
-      <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000560350393</v>
-      </c>
-      <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00063695</v>
-      </c>
-      <c r="AA5" s="5">
-        <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>56.0</v>
-      </c>
-      <c r="AB5" s="5">
-        <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>64.0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>2056.78</v>
+        <v>1.428</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="AD6" s="1">
-        <v>5.491</v>
+        <v>0.449</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="I7" t="s">
-        <v>161</v>
+        <v>49</v>
+      </c>
+      <c r="J7" s="2">
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>51.0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>8.973348e-06</v>
+      </c>
+      <c r="L7" s="2">
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>1.02e-05</v>
+      </c>
+      <c r="M7" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>315.0</v>
+      </c>
+      <c r="N7" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>5.542362e-06</v>
+      </c>
+      <c r="O7" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>6.3e-06</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>58.0</v>
+      </c>
+      <c r="T7" s="2">
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="U7" s="2">
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>7.5745614e-05</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>8.61e-05</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>1.293</v>
+        <v>3.765</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F8" s="1">
+        <v>366</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H8" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>208</v>
+      </c>
+      <c r="J8" s="2">
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>51.0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>8.973348e-06</v>
+      </c>
+      <c r="L8" s="2">
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>1.02e-05</v>
+      </c>
+      <c r="M8" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>315.0</v>
+      </c>
+      <c r="N8" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>5.542362e-06</v>
+      </c>
+      <c r="O8" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>6.3e-06</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>58.0</v>
+      </c>
+      <c r="T8" s="2">
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="U8" s="2">
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>7.5745614e-05</v>
+      </c>
+      <c r="Z8" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>8.61e-05</v>
+      </c>
+      <c r="AA8" s="5">
+        <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AB8" s="5">
+        <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="AD8" s="1">
-        <v>5.499</v>
+        <v>2.957</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="B9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="I9" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="AD9" s="1">
-        <v>0.756</v>
+        <v>1.183</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="H10" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="AD10" s="1">
-        <v>5.763</v>
+        <v>0.372</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="B11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="H11" t="s">
-        <v>121</v>
+        <v>210</v>
       </c>
       <c r="I11" t="s">
-        <v>166</v>
+        <v>49</v>
+      </c>
+      <c r="J11" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>51.0</v>
+      </c>
+      <c r="K11" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>8.973348e-06</v>
+      </c>
+      <c r="L11" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>1.02e-05</v>
+      </c>
+      <c r="M11" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>424.0</v>
+      </c>
+      <c r="N11" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>7.4601952e-06</v>
+      </c>
+      <c r="O11" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>8.48e-06</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>58.0</v>
+      </c>
+      <c r="T11" s="2">
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="U11" s="2">
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>7.76634472e-05</v>
+      </c>
+      <c r="Z11" s="2">
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>8.828e-05</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>1.347</v>
+        <v>2.641</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F12" s="1">
+        <v>475</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="H12" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>210</v>
       </c>
       <c r="J12" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>51.0</v>
       </c>
       <c r="K12" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>8.973348e-06</v>
       </c>
       <c r="L12" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>1.02e-05</v>
       </c>
       <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>2099.0</v>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>424.0</v>
       </c>
       <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.69314852e-05</v>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>7.4601952e-06</v>
       </c>
       <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.198e-05</v>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>8.48e-06</v>
       </c>
       <c r="P12" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>194.0</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.266739e-05</v>
+        <v>0</v>
       </c>
       <c r="R12" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>4.85e-05</v>
+        <v>0</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>65.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>58.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>6.861972e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>6.1229904e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>7.8e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>6.96e-05</v>
       </c>
       <c r="V12" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>54.0</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>5.7007152e-05</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>6.48e-05</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0002057535912</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>7.76634472e-05</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00023388</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>8.828e-05</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>9.0</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="AD12" s="1">
-        <v>1884.096</v>
+        <v>1.867</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="B13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2296</v>
+        <v>141</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="I13" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K13" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L13" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>2099.0</v>
-      </c>
-      <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.69314852e-05</v>
-      </c>
-      <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.198e-05</v>
-      </c>
-      <c r="P13" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>194.0</v>
-      </c>
-      <c r="Q13" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>4.266739e-05</v>
-      </c>
-      <c r="R13" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>4.85e-05</v>
-      </c>
-      <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
-        <v>65.0</v>
-      </c>
-      <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>6.861972e-05</v>
-      </c>
-      <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>7.8e-05</v>
-      </c>
-      <c r="V13" s="2">
-        <f>IF(COUNT('Turns'!D34)=1,SUM('Turns'!D34),"Unknown")</f>
-        <v>54.0</v>
-      </c>
-      <c r="W13" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>5.7007152e-05</v>
-      </c>
-      <c r="X13" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>6.48e-05</v>
-      </c>
-      <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>0.0002057535912</v>
-      </c>
-      <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>0.00023388</v>
-      </c>
-      <c r="AA13" s="5">
-        <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
-      </c>
-      <c r="AB13" s="5">
-        <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="AD13" s="1">
-        <v>1878.87</v>
+        <v>1.222</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="AD14" s="1">
-        <v>8.138999999999999</v>
+        <v>0.324</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="B15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="H15" t="s">
-        <v>131</v>
+        <v>212</v>
       </c>
       <c r="I15" t="s">
-        <v>168</v>
+        <v>49</v>
+      </c>
+      <c r="J15" s="2">
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="K15" s="2">
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>8.445504e-06</v>
+      </c>
+      <c r="L15" s="2">
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="M15" s="2">
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <v>533.0</v>
+      </c>
+      <c r="N15" s="2">
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>9.3780284e-06</v>
+      </c>
+      <c r="O15" s="2">
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <v>1.066e-05</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <f>IF(COUNT('Turns'!D59)=1,SUM('Turns'!D59),"Unknown")</f>
+        <v>80.0</v>
+      </c>
+      <c r="T15" s="2">
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>8.445504e-05</v>
+      </c>
+      <c r="U15" s="2">
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>9.6e-05</v>
+      </c>
+      <c r="V15" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>12000.0</v>
+      </c>
+      <c r="W15" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>0.012668256</v>
+      </c>
+      <c r="X15" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>0.0144</v>
+      </c>
+      <c r="Y15" s="2">
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>0.0127705345724</v>
+      </c>
+      <c r="Z15" s="2">
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>0.01451626</v>
+      </c>
+      <c r="AA15" s="5">
+        <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1277.0</v>
+      </c>
+      <c r="AB15" s="5">
+        <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1452.0</v>
       </c>
       <c r="AD15" s="1">
-        <v>3.649</v>
+        <v>2.766</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F16" s="1">
+        <v>581</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>212</v>
+      </c>
+      <c r="J16" s="2">
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="K16" s="2">
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>8.445504e-06</v>
+      </c>
+      <c r="L16" s="2">
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="M16" s="2">
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <v>533.0</v>
+      </c>
+      <c r="N16" s="2">
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>9.3780284e-06</v>
+      </c>
+      <c r="O16" s="2">
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <v>1.066e-05</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <f>IF(COUNT('Turns'!D59)=1,SUM('Turns'!D59),"Unknown")</f>
+        <v>80.0</v>
+      </c>
+      <c r="T16" s="2">
+        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
+        <v>8.445504e-05</v>
+      </c>
+      <c r="U16" s="2">
+        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
+        <v>9.6e-05</v>
+      </c>
+      <c r="V16" s="2">
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>12000.0</v>
+      </c>
+      <c r="W16" s="2">
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>0.012668256</v>
+      </c>
+      <c r="X16" s="2">
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>0.0144</v>
+      </c>
+      <c r="Y16" s="2">
+        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
+        <v>0.0127705345724</v>
+      </c>
+      <c r="Z16" s="2">
+        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
+        <v>0.01451626</v>
+      </c>
+      <c r="AA16" s="5">
+        <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1277.0</v>
+      </c>
+      <c r="AB16" s="5">
+        <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1452.0</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="AD16" s="1">
-        <v>8.26</v>
+        <v>1.952</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="B17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="I17" t="s">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c r="AD17" s="1">
-        <v>1.781</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="AD18" s="1">
-        <v>7.58</v>
+        <v>0.556</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="B19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="H19" t="s">
-        <v>137</v>
+        <v>216</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>49</v>
+      </c>
+      <c r="J19" s="2">
+        <f>IF(COUNT('Turns'!D69)=1,SUM('Turns'!D69),"Unknown")</f>
+        <v>56.0</v>
+      </c>
+      <c r="K19" s="2">
+        <f>IF(COUNT('Turns'!E69)=1,SUM('Turns'!E69),"Unknown")</f>
+        <v>9.853088e-06</v>
+      </c>
+      <c r="L19" s="2">
+        <f>IF(COUNT('Turns'!F69)=1,SUM('Turns'!F69),"Unknown")</f>
+        <v>1.12e-05</v>
+      </c>
+      <c r="M19" s="2">
+        <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
+        <v>661.0</v>
+      </c>
+      <c r="N19" s="2">
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>1.16301628e-05</v>
+      </c>
+      <c r="O19" s="2">
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>1.322e-05</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>61.0</v>
+      </c>
+      <c r="T19" s="2">
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>6.4396968e-05</v>
+      </c>
+      <c r="U19" s="2">
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>7.32e-05</v>
+      </c>
+      <c r="V19" s="2">
+        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
+        <v>600.0</v>
+      </c>
+      <c r="W19" s="2">
+        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
+        <v>0.0006334128</v>
+      </c>
+      <c r="X19" s="2">
+        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
+        <v>0.00072</v>
+      </c>
+      <c r="Y19" s="2">
+        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
+        <v>0.0007192930188</v>
+      </c>
+      <c r="Z19" s="2">
+        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
+        <v>0.00081762</v>
+      </c>
+      <c r="AA19" s="5">
+        <f>IF(ISNUMBER(Y19),ROUND(Y19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="AB19" s="5">
+        <f>IF(ISNUMBER(Z19),ROUND(Z19*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
       </c>
       <c r="AD19" s="1">
-        <v>2.078</v>
+        <v>4.663</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F20" s="1">
+        <v>717</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="H20" t="s">
         <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="J20" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D69)=1,SUM('Turns'!D69),"Unknown")</f>
+        <v>56.0</v>
       </c>
       <c r="K20" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E69)=1,SUM('Turns'!E69),"Unknown")</f>
+        <v>9.853088e-06</v>
       </c>
       <c r="L20" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F69)=1,SUM('Turns'!F69),"Unknown")</f>
+        <v>1.12e-05</v>
       </c>
       <c r="M20" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2293.0</v>
+        <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
+        <v>661.0</v>
       </c>
       <c r="N20" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>4.03448764e-05</v>
+        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
+        <v>1.16301628e-05</v>
       </c>
       <c r="O20" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.586e-05</v>
+        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
+        <v>1.322e-05</v>
       </c>
       <c r="P20" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>207.0</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>4.5526545e-05</v>
+        <v>0</v>
       </c>
       <c r="R20" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>5.175e-05</v>
+        <v>0</v>
       </c>
       <c r="S20" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>276.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="T20" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>0.000291369888</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>6.4396968e-05</v>
       </c>
       <c r="U20" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>0.0003312</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>7.32e-05</v>
       </c>
       <c r="V20" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D74)=1,SUM('Turns'!D74),"Unknown")</f>
+        <v>600.0</v>
       </c>
       <c r="W20" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E74)=1,SUM('Turns'!E74),"Unknown")</f>
+        <v>0.0006334128</v>
       </c>
       <c r="X20" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F74)=1,SUM('Turns'!F74),"Unknown")</f>
+        <v>0.00072</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0003777691534</v>
+        <f>IF(COUNT('Turns'!E80)=1,SUM('Turns'!E80),"Unknown")</f>
+        <v>0.0007192930188</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00042941</v>
+        <f>IF(COUNT('Turns'!F80)=1,SUM('Turns'!F80),"Unknown")</f>
+        <v>0.00081762</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>72.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="AD20" s="1">
-        <v>3654.439</v>
+        <v>2.59</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="54" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H21" t="s">
+        <v>217</v>
+      </c>
+      <c r="I21" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>1.589</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="54" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2503</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="C22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I21" t="s">
-        <v>173</v>
-      </c>
-      <c r="J21" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K21" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L21" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>2293.0</v>
-      </c>
-      <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>4.03448764e-05</v>
-      </c>
-      <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>4.586e-05</v>
-      </c>
-      <c r="P21" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>207.0</v>
-      </c>
-      <c r="Q21" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>4.5526545e-05</v>
-      </c>
-      <c r="R21" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>5.175e-05</v>
-      </c>
-      <c r="S21" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>276.0</v>
-      </c>
-      <c r="T21" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>0.000291369888</v>
-      </c>
-      <c r="U21" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>0.0003312</v>
-      </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0003777691534</v>
-      </c>
-      <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00042941</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
-      </c>
-      <c r="AB21" s="5">
-        <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>43.0</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>3648.979</v>
-      </c>
-      <c r="AE21" s="1" t="s">
-        <v>158</v>
+      <c r="G22" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="I22" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="54" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="2">
+        <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
+        <v>42.0</v>
+      </c>
+      <c r="K23" s="2">
+        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
+        <v>7.389816e-06</v>
+      </c>
+      <c r="L23" s="2">
+        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="M23" s="2">
+        <f>IF(COUNT('Turns'!D85)=1,SUM('Turns'!D85),"Unknown")</f>
+        <v>778.0</v>
+      </c>
+      <c r="N23" s="2">
+        <f>IF(COUNT('Turns'!E85)=1,SUM('Turns'!E85),"Unknown")</f>
+        <v>1.36887544e-05</v>
+      </c>
+      <c r="O23" s="2">
+        <f>IF(COUNT('Turns'!F85)=1,SUM('Turns'!F85),"Unknown")</f>
+        <v>1.556e-05</v>
+      </c>
+      <c r="P23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <v>60.0</v>
+      </c>
+      <c r="T23" s="2">
+        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <v>6.334128e-05</v>
+      </c>
+      <c r="U23" s="2">
+        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <v>7.2e-05</v>
+      </c>
+      <c r="V23" s="2">
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
+        <v>600.0</v>
+      </c>
+      <c r="W23" s="2">
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
+        <v>0.0006334128</v>
+      </c>
+      <c r="X23" s="2">
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
+        <v>0.00072</v>
+      </c>
+      <c r="Y23" s="2">
+        <f>IF(COUNT('Turns'!E97)=1,SUM('Turns'!E97),"Unknown")</f>
+        <v>0.0007178326504</v>
+      </c>
+      <c r="Z23" s="2">
+        <f>IF(COUNT('Turns'!F97)=1,SUM('Turns'!F97),"Unknown")</f>
+        <v>0.00081596</v>
+      </c>
+      <c r="AA23" s="5">
+        <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="AB23" s="5">
+        <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>3.514</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="54" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="1">
+        <v>820</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" t="s">
+        <v>218</v>
+      </c>
+      <c r="J24" s="2">
+        <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
+        <v>42.0</v>
+      </c>
+      <c r="K24" s="2">
+        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
+        <v>7.389816e-06</v>
+      </c>
+      <c r="L24" s="2">
+        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
+        <v>8.4e-06</v>
+      </c>
+      <c r="M24" s="2">
+        <f>IF(COUNT('Turns'!D85)=1,SUM('Turns'!D85),"Unknown")</f>
+        <v>778.0</v>
+      </c>
+      <c r="N24" s="2">
+        <f>IF(COUNT('Turns'!E85)=1,SUM('Turns'!E85),"Unknown")</f>
+        <v>1.36887544e-05</v>
+      </c>
+      <c r="O24" s="2">
+        <f>IF(COUNT('Turns'!F85)=1,SUM('Turns'!F85),"Unknown")</f>
+        <v>1.556e-05</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <v>60.0</v>
+      </c>
+      <c r="T24" s="2">
+        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <v>6.334128e-05</v>
+      </c>
+      <c r="U24" s="2">
+        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <v>7.2e-05</v>
+      </c>
+      <c r="V24" s="2">
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
+        <v>600.0</v>
+      </c>
+      <c r="W24" s="2">
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
+        <v>0.0006334128</v>
+      </c>
+      <c r="X24" s="2">
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
+        <v>0.00072</v>
+      </c>
+      <c r="Y24" s="2">
+        <f>IF(COUNT('Turns'!E97)=1,SUM('Turns'!E97),"Unknown")</f>
+        <v>0.0007178326504</v>
+      </c>
+      <c r="Z24" s="2">
+        <f>IF(COUNT('Turns'!F97)=1,SUM('Turns'!F97),"Unknown")</f>
+        <v>0.00081596</v>
+      </c>
+      <c r="AA24" s="5">
+        <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="AB24" s="5">
+        <f>IF(ISNUMBER(Z24),ROUND(Z24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>82.0</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>2.592</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="54" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>1.177</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="54" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H26" t="s">
+        <v>183</v>
+      </c>
+      <c r="I26" t="s">
+        <v>219</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="54" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" t="s">
+        <v>220</v>
+      </c>
+      <c r="I27" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="2">
+        <f>IF(COUNT('Turns'!D103)=1,SUM('Turns'!D103),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="K27" s="2">
+        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
+        <v>7.03792e-06</v>
+      </c>
+      <c r="L27" s="2">
+        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
+        <v>8e-06</v>
+      </c>
+      <c r="M27" s="2">
+        <f>IF(COUNT('Turns'!D102)=1,SUM('Turns'!D102),"Unknown")</f>
+        <v>880.0</v>
+      </c>
+      <c r="N27" s="2">
+        <f>IF(COUNT('Turns'!E102)=1,SUM('Turns'!E102),"Unknown")</f>
+        <v>1.5483424e-05</v>
+      </c>
+      <c r="O27" s="2">
+        <f>IF(COUNT('Turns'!F102)=1,SUM('Turns'!F102),"Unknown")</f>
+        <v>1.76e-05</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f>IF(COUNT('Turns'!D110)=1,SUM('Turns'!D110),"Unknown")</f>
+        <v>71.0</v>
+      </c>
+      <c r="T27" s="2">
+        <f>IF(COUNT('Turns'!E110)=1,SUM('Turns'!E110),"Unknown")</f>
+        <v>7.4953848e-05</v>
+      </c>
+      <c r="U27" s="2">
+        <f>IF(COUNT('Turns'!F110)=1,SUM('Turns'!F110),"Unknown")</f>
+        <v>8.52e-05</v>
+      </c>
+      <c r="V27" s="2">
+        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
+        <v>1800.0</v>
+      </c>
+      <c r="W27" s="2">
+        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
+        <v>0.0019002384</v>
+      </c>
+      <c r="X27" s="2">
+        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
+        <v>0.00216</v>
+      </c>
+      <c r="Y27" s="2">
+        <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
+        <v>0.001997713592</v>
+      </c>
+      <c r="Z27" s="2">
+        <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
+        <v>0.0022708</v>
+      </c>
+      <c r="AA27" s="5">
+        <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>200.0</v>
+      </c>
+      <c r="AB27" s="5">
+        <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>227.0</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>2.19</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="54" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="1">
+        <v>920</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" t="s">
+        <v>220</v>
+      </c>
+      <c r="J28" s="2">
+        <f>IF(COUNT('Turns'!D103)=1,SUM('Turns'!D103),"Unknown")</f>
+        <v>40.0</v>
+      </c>
+      <c r="K28" s="2">
+        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
+        <v>7.03792e-06</v>
+      </c>
+      <c r="L28" s="2">
+        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
+        <v>8e-06</v>
+      </c>
+      <c r="M28" s="2">
+        <f>IF(COUNT('Turns'!D102)=1,SUM('Turns'!D102),"Unknown")</f>
+        <v>880.0</v>
+      </c>
+      <c r="N28" s="2">
+        <f>IF(COUNT('Turns'!E102)=1,SUM('Turns'!E102),"Unknown")</f>
+        <v>1.5483424e-05</v>
+      </c>
+      <c r="O28" s="2">
+        <f>IF(COUNT('Turns'!F102)=1,SUM('Turns'!F102),"Unknown")</f>
+        <v>1.76e-05</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <f>IF(COUNT('Turns'!D110)=1,SUM('Turns'!D110),"Unknown")</f>
+        <v>71.0</v>
+      </c>
+      <c r="T28" s="2">
+        <f>IF(COUNT('Turns'!E110)=1,SUM('Turns'!E110),"Unknown")</f>
+        <v>7.4953848e-05</v>
+      </c>
+      <c r="U28" s="2">
+        <f>IF(COUNT('Turns'!F110)=1,SUM('Turns'!F110),"Unknown")</f>
+        <v>8.52e-05</v>
+      </c>
+      <c r="V28" s="2">
+        <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
+        <v>1800.0</v>
+      </c>
+      <c r="W28" s="2">
+        <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
+        <v>0.0019002384</v>
+      </c>
+      <c r="X28" s="2">
+        <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
+        <v>0.00216</v>
+      </c>
+      <c r="Y28" s="2">
+        <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
+        <v>0.001997713592</v>
+      </c>
+      <c r="Z28" s="2">
+        <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
+        <v>0.0022708</v>
+      </c>
+      <c r="AA28" s="5">
+        <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>200.0</v>
+      </c>
+      <c r="AB28" s="5">
+        <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>227.0</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>1.437</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE21">
+  <conditionalFormatting sqref="A2:AE28">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -3370,7 +5422,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -3755,6 +5807,731 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.00</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.075</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="F33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="72" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="72" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E39" s="2">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="72" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="72" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="72" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="F43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="72" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="D44" s="2">
+        <v>25.00</v>
+      </c>
+      <c r="E44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="F44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="72" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.40</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
